--- a/assets_output/04_bivariate_analysis_placements.xlsx
+++ b/assets_output/04_bivariate_analysis_placements.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R124"/>
+  <dimension ref="A1:R127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,165 +818,138 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>277</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>Died</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C25" t="n">
         <v>1.9</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Table 4.3: Placement outcomes by pathway type and level</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>pathway_type</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>Homelessness</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="n"/>
-      <c r="D27" s="1" t="n"/>
-      <c r="E27" s="1" t="n"/>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>Substance Misuse</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="n"/>
-      <c r="H27" s="1" t="n"/>
-      <c r="I27" s="1" t="n"/>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>All</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>pathway_level</t>
+          <t>pathway_type</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Homelessness</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n"/>
+      <c r="D28" s="1" t="n"/>
+      <c r="E28" s="1" t="n"/>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H28" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I28" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J28" s="1" t="inlineStr"/>
+          <t>Substance Misuse</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="n"/>
+      <c r="H28" s="1" t="n"/>
+      <c r="I28" s="1" t="n"/>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>pl_outcome</t>
-        </is>
-      </c>
+          <t>pathway_level</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" s="1" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Internal move: forwards</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>924</v>
-      </c>
-      <c r="C30" t="n">
-        <v>301</v>
-      </c>
-      <c r="D30" t="n">
-        <v>88</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>212</v>
-      </c>
-      <c r="G30" t="n">
-        <v>37</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1562</v>
+          <t>pl_outcome</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Independent accommodation</t>
+          <t>Internal move: forwards</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>153</v>
+        <v>924</v>
       </c>
       <c r="C31" t="n">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="D31" t="n">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="E31" t="n">
-        <v>738</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>48</v>
+        <v>212</v>
       </c>
       <c r="G31" t="n">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -985,32 +958,32 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1225</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Internal move: sideways</t>
+          <t>Independent accommodation</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>705</v>
+        <v>153</v>
       </c>
       <c r="C32" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D32" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="E32" t="n">
-        <v>33</v>
+        <v>738</v>
       </c>
       <c r="F32" t="n">
-        <v>342</v>
+        <v>48</v>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1019,32 +992,32 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1164</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: sideways</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>362</v>
+        <v>705</v>
       </c>
       <c r="C33" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D33" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E33" t="n">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="F33" t="n">
-        <v>168</v>
+        <v>342</v>
       </c>
       <c r="G33" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1053,32 +1026,32 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>744</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>362</v>
       </c>
       <c r="C34" t="n">
-        <v>218</v>
+        <v>70</v>
       </c>
       <c r="D34" t="n">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="E34" t="n">
-        <v>191</v>
+        <v>92</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="G34" t="n">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1087,32 +1060,32 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>653</v>
+        <v>744</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Insecure outcome</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>85</v>
+        <v>218</v>
       </c>
       <c r="D35" t="n">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="E35" t="n">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="F35" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1121,32 +1094,32 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>638</v>
+        <v>653</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Insecure outcome</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>48</v>
+        <v>284</v>
       </c>
       <c r="C36" t="n">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E36" t="n">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="F36" t="n">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1155,1524 +1128,1440 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>117</v>
+        <v>638</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>48</v>
+      </c>
+      <c r="C37" t="n">
+        <v>19</v>
+      </c>
+      <c r="D37" t="n">
+        <v>11</v>
+      </c>
+      <c r="E37" t="n">
+        <v>23</v>
+      </c>
+      <c r="F37" t="n">
+        <v>14</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr"/>
+      <c r="B38" t="n">
+        <v>68</v>
+      </c>
+      <c r="C38" t="n">
+        <v>38</v>
+      </c>
+      <c r="D38" t="n">
+        <v>25</v>
+      </c>
+      <c r="E38" t="n">
+        <v>78</v>
+      </c>
+      <c r="F38" t="n">
+        <v>51</v>
+      </c>
+      <c r="G38" t="n">
+        <v>17</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>2476</v>
-      </c>
-      <c r="C37" t="n">
-        <v>843</v>
-      </c>
-      <c r="D37" t="n">
-        <v>413</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1190</v>
-      </c>
-      <c r="F37" t="n">
-        <v>880</v>
-      </c>
-      <c r="G37" t="n">
-        <v>301</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="n">
-        <v>6103</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="B39" t="n">
+        <v>2544</v>
+      </c>
+      <c r="C39" t="n">
+        <v>881</v>
+      </c>
+      <c r="D39" t="n">
+        <v>438</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1268</v>
+      </c>
+      <c r="F39" t="n">
+        <v>931</v>
+      </c>
+      <c r="G39" t="n">
+        <v>318</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>6380</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Table 4.4: Placement outcomes (as row percentages) by pathway type and level</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pathway_type</t>
-        </is>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>Homelessness</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="n"/>
-      <c r="D40" s="1" t="n"/>
-      <c r="E40" s="1" t="n"/>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>Substance Misuse</t>
-        </is>
-      </c>
-      <c r="G40" s="1" t="n"/>
-      <c r="H40" s="1" t="n"/>
-      <c r="I40" s="1" t="n"/>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>pathway_level</t>
-        </is>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H41" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I41" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J41" s="1" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>pl_outcome</t>
+          <t>pathway_type</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>Homelessness</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="n"/>
+      <c r="D42" s="1" t="n"/>
+      <c r="E42" s="1" t="n"/>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>Substance Misuse</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="n"/>
+      <c r="H42" s="1" t="n"/>
+      <c r="I42" s="1" t="n"/>
+      <c r="J42" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Internal move: forwards</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="C43" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="D43" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
-        <v>25.6</v>
-      </c>
+          <t>pathway_level</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I43" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" s="1" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Independent accommodation</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="C44" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="D44" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E44" t="n">
-        <v>62</v>
-      </c>
-      <c r="F44" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G44" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="n">
-        <v>20.1</v>
+          <t>pl_outcome</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Internal move: sideways</t>
+          <t>Internal move: forwards</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28.5</v>
+        <v>36.3</v>
       </c>
       <c r="C45" t="n">
-        <v>8.1</v>
+        <v>34.2</v>
       </c>
       <c r="D45" t="n">
-        <v>2.9</v>
+        <v>20.1</v>
       </c>
       <c r="E45" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>38.9</v>
+        <v>22.8</v>
       </c>
       <c r="G45" t="n">
-        <v>1.3</v>
+        <v>11.6</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>19.1</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Independent accommodation</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>14.6</v>
+        <v>6</v>
       </c>
       <c r="C46" t="n">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>7.5</v>
+        <v>27.4</v>
       </c>
       <c r="E46" t="n">
-        <v>7.7</v>
+        <v>58.2</v>
       </c>
       <c r="F46" t="n">
-        <v>19.1</v>
+        <v>5.2</v>
       </c>
       <c r="G46" t="n">
-        <v>7</v>
+        <v>26.4</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>12.2</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Internal move: sideways</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>27.7</v>
       </c>
       <c r="C47" t="n">
-        <v>25.9</v>
+        <v>7.7</v>
       </c>
       <c r="D47" t="n">
-        <v>28.1</v>
+        <v>2.7</v>
       </c>
       <c r="E47" t="n">
-        <v>16.1</v>
+        <v>2.6</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>36.7</v>
       </c>
       <c r="G47" t="n">
-        <v>42.5</v>
+        <v>1.3</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>10.7</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Insecure outcome</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>11.5</v>
+        <v>14.2</v>
       </c>
       <c r="C48" t="n">
-        <v>10.1</v>
+        <v>7.9</v>
       </c>
       <c r="D48" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="E48" t="n">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="F48" t="n">
-        <v>10.9</v>
+        <v>18</v>
       </c>
       <c r="G48" t="n">
-        <v>8.300000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>10.5</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>2.3</v>
+        <v>24.7</v>
       </c>
       <c r="D49" t="n">
-        <v>2.7</v>
+        <v>26.5</v>
       </c>
       <c r="E49" t="n">
-        <v>1.9</v>
+        <v>15.1</v>
       </c>
       <c r="F49" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.7</v>
+        <v>40.3</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>1.9</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Insecure outcome</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>100</v>
+        <v>11.2</v>
       </c>
       <c r="C50" t="n">
-        <v>100</v>
+        <v>9.6</v>
       </c>
       <c r="D50" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="E50" t="n">
-        <v>100</v>
+        <v>8.9</v>
       </c>
       <c r="F50" t="n">
-        <v>100</v>
+        <v>10.3</v>
       </c>
       <c r="G50" t="n">
-        <v>100</v>
+        <v>7.9</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>100</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Table 4.5: Placement outcomes by calendar year</t>
-        </is>
-      </c>
+      <c r="A52" s="1" t="inlineStr"/>
+      <c r="B52" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C52" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D52" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E52" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>pl_outcome</t>
-        </is>
-      </c>
-      <c r="B53" s="1" t="n">
-        <v>2017</v>
-      </c>
-      <c r="C53" s="1" t="n">
-        <v>2018</v>
-      </c>
-      <c r="D53" s="1" t="n">
-        <v>2019</v>
-      </c>
-      <c r="E53" s="1" t="n">
-        <v>2020</v>
-      </c>
-      <c r="F53" s="1" t="n">
-        <v>2021</v>
-      </c>
-      <c r="G53" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="H53" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="I53" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="J53" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
           <t>All</t>
         </is>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>Internal move: forwards</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>60</v>
-      </c>
-      <c r="C54" t="n">
-        <v>341</v>
-      </c>
-      <c r="D54" t="n">
-        <v>298</v>
-      </c>
-      <c r="E54" t="n">
-        <v>228</v>
-      </c>
-      <c r="F54" t="n">
-        <v>196</v>
-      </c>
-      <c r="G54" t="n">
-        <v>166</v>
-      </c>
-      <c r="H54" t="n">
-        <v>112</v>
-      </c>
-      <c r="I54" t="n">
-        <v>120</v>
-      </c>
-      <c r="J54" t="n">
-        <v>41</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1562</v>
+      <c r="B53" t="n">
+        <v>100</v>
+      </c>
+      <c r="C53" t="n">
+        <v>100</v>
+      </c>
+      <c r="D53" t="n">
+        <v>100</v>
+      </c>
+      <c r="E53" t="n">
+        <v>100</v>
+      </c>
+      <c r="F53" t="n">
+        <v>100</v>
+      </c>
+      <c r="G53" t="n">
+        <v>100</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>Independent accommodation</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>40</v>
-      </c>
-      <c r="C55" t="n">
-        <v>198</v>
-      </c>
-      <c r="D55" t="n">
-        <v>189</v>
-      </c>
-      <c r="E55" t="n">
-        <v>229</v>
-      </c>
-      <c r="F55" t="n">
-        <v>162</v>
-      </c>
-      <c r="G55" t="n">
-        <v>156</v>
-      </c>
-      <c r="H55" t="n">
-        <v>96</v>
-      </c>
-      <c r="I55" t="n">
-        <v>118</v>
-      </c>
-      <c r="J55" t="n">
-        <v>37</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1225</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Table 4.5: Placement outcomes by calendar year</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Internal move: sideways</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>33</v>
-      </c>
-      <c r="C56" t="n">
-        <v>189</v>
-      </c>
-      <c r="D56" t="n">
-        <v>206</v>
-      </c>
-      <c r="E56" t="n">
-        <v>170</v>
-      </c>
-      <c r="F56" t="n">
-        <v>189</v>
-      </c>
-      <c r="G56" t="n">
-        <v>116</v>
-      </c>
-      <c r="H56" t="n">
-        <v>130</v>
-      </c>
-      <c r="I56" t="n">
-        <v>100</v>
-      </c>
-      <c r="J56" t="n">
-        <v>31</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1164</v>
+          <t>pl_outcome</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F56" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G56" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J56" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K56" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: forwards</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="C57" t="n">
-        <v>51</v>
+        <v>341</v>
       </c>
       <c r="D57" t="n">
-        <v>85</v>
+        <v>298</v>
       </c>
       <c r="E57" t="n">
-        <v>72</v>
+        <v>228</v>
       </c>
       <c r="F57" t="n">
-        <v>95</v>
+        <v>196</v>
       </c>
       <c r="G57" t="n">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="H57" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="I57" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="J57" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="K57" t="n">
-        <v>744</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Independent accommodation</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C58" t="n">
-        <v>124</v>
+        <v>198</v>
       </c>
       <c r="D58" t="n">
-        <v>126</v>
+        <v>189</v>
       </c>
       <c r="E58" t="n">
-        <v>81</v>
+        <v>229</v>
       </c>
       <c r="F58" t="n">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="G58" t="n">
-        <v>66</v>
+        <v>156</v>
       </c>
       <c r="H58" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="I58" t="n">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="J58" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="K58" t="n">
-        <v>653</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Insecure outcome</t>
+          <t>Internal move: sideways</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C59" t="n">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="D59" t="n">
-        <v>87</v>
+        <v>206</v>
       </c>
       <c r="E59" t="n">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="F59" t="n">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="G59" t="n">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="H59" t="n">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="I59" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="K59" t="n">
-        <v>638</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C60" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D60" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E60" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="F60" t="n">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="G60" t="n">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="H60" t="n">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="I60" t="n">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="J60" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="K60" t="n">
-        <v>117</v>
+        <v>744</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>190</v>
+        <v>28</v>
       </c>
       <c r="C61" t="n">
-        <v>1016</v>
+        <v>124</v>
       </c>
       <c r="D61" t="n">
-        <v>1008</v>
+        <v>126</v>
       </c>
       <c r="E61" t="n">
-        <v>878</v>
+        <v>81</v>
       </c>
       <c r="F61" t="n">
-        <v>835</v>
+        <v>78</v>
       </c>
       <c r="G61" t="n">
-        <v>717</v>
+        <v>66</v>
       </c>
       <c r="H61" t="n">
-        <v>624</v>
+        <v>73</v>
       </c>
       <c r="I61" t="n">
-        <v>619</v>
+        <v>62</v>
       </c>
       <c r="J61" t="n">
-        <v>216</v>
+        <v>15</v>
       </c>
       <c r="K61" t="n">
-        <v>6103</v>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>Insecure outcome</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>13</v>
+      </c>
+      <c r="C62" t="n">
+        <v>96</v>
+      </c>
+      <c r="D62" t="n">
+        <v>87</v>
+      </c>
+      <c r="E62" t="n">
+        <v>82</v>
+      </c>
+      <c r="F62" t="n">
+        <v>95</v>
+      </c>
+      <c r="G62" t="n">
+        <v>86</v>
+      </c>
+      <c r="H62" t="n">
+        <v>72</v>
+      </c>
+      <c r="I62" t="n">
+        <v>67</v>
+      </c>
+      <c r="J62" t="n">
+        <v>40</v>
+      </c>
+      <c r="K62" t="n">
+        <v>638</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Table 4.6: Placement outcomes (as row percentages) by calendar year</t>
-        </is>
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="n">
+        <v>17</v>
+      </c>
+      <c r="D63" t="n">
+        <v>17</v>
+      </c>
+      <c r="E63" t="n">
+        <v>16</v>
+      </c>
+      <c r="F63" t="n">
+        <v>20</v>
+      </c>
+      <c r="G63" t="n">
+        <v>13</v>
+      </c>
+      <c r="H63" t="n">
+        <v>14</v>
+      </c>
+      <c r="I63" t="n">
+        <v>15</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K63" t="n">
+        <v>117</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>pl_outcome</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>2017</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>2018</v>
-      </c>
-      <c r="D64" s="1" t="n">
-        <v>2019</v>
-      </c>
-      <c r="E64" s="1" t="n">
-        <v>2020</v>
-      </c>
-      <c r="F64" s="1" t="n">
-        <v>2021</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="H64" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="I64" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="J64" s="1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
           <t>All</t>
         </is>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>Internal move: forwards</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="C65" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="D65" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E65" t="n">
-        <v>26</v>
-      </c>
-      <c r="F65" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G65" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="H65" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="I65" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="J65" t="n">
-        <v>19</v>
-      </c>
-      <c r="K65" t="n">
-        <v>25.6</v>
+      <c r="B64" t="n">
+        <v>190</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1016</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E64" t="n">
+        <v>878</v>
+      </c>
+      <c r="F64" t="n">
+        <v>835</v>
+      </c>
+      <c r="G64" t="n">
+        <v>717</v>
+      </c>
+      <c r="H64" t="n">
+        <v>624</v>
+      </c>
+      <c r="I64" t="n">
+        <v>619</v>
+      </c>
+      <c r="J64" t="n">
+        <v>216</v>
+      </c>
+      <c r="K64" t="n">
+        <v>6103</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t>Independent accommodation</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="C66" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="D66" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="E66" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="F66" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="G66" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H66" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="I66" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="J66" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="K66" t="n">
-        <v>20.1</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Table 4.6: Placement outcomes (as row percentages) by calendar year</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>Internal move: sideways</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="C67" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="D67" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="E67" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F67" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G67" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="H67" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="I67" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="J67" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K67" t="n">
-        <v>19.1</v>
+          <t>pl_outcome</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F67" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G67" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H67" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="I67" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J67" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K67" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: forwards</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>7.4</v>
+        <v>31.6</v>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>33.6</v>
       </c>
       <c r="D68" t="n">
-        <v>8.4</v>
+        <v>29.6</v>
       </c>
       <c r="E68" t="n">
-        <v>8.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="F68" t="n">
-        <v>11.4</v>
+        <v>23.5</v>
       </c>
       <c r="G68" t="n">
-        <v>15.9</v>
+        <v>23.2</v>
       </c>
       <c r="H68" t="n">
-        <v>20.4</v>
+        <v>17.9</v>
       </c>
       <c r="I68" t="n">
-        <v>22.1</v>
+        <v>19.4</v>
       </c>
       <c r="J68" t="n">
-        <v>22.7</v>
+        <v>19</v>
       </c>
       <c r="K68" t="n">
-        <v>12.2</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Independent accommodation</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>14.7</v>
+        <v>21.1</v>
       </c>
       <c r="C69" t="n">
-        <v>12.2</v>
+        <v>19.5</v>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>18.8</v>
       </c>
       <c r="E69" t="n">
-        <v>9.199999999999999</v>
+        <v>26.1</v>
       </c>
       <c r="F69" t="n">
-        <v>9.300000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="G69" t="n">
-        <v>9.199999999999999</v>
+        <v>21.8</v>
       </c>
       <c r="H69" t="n">
-        <v>11.7</v>
+        <v>15.4</v>
       </c>
       <c r="I69" t="n">
-        <v>10</v>
+        <v>19.1</v>
       </c>
       <c r="J69" t="n">
-        <v>6.9</v>
+        <v>17.1</v>
       </c>
       <c r="K69" t="n">
-        <v>10.7</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>Insecure outcome</t>
+          <t>Internal move: sideways</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6.8</v>
+        <v>17.4</v>
       </c>
       <c r="C70" t="n">
-        <v>9.4</v>
+        <v>18.6</v>
       </c>
       <c r="D70" t="n">
-        <v>8.6</v>
+        <v>20.4</v>
       </c>
       <c r="E70" t="n">
-        <v>9.300000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="F70" t="n">
-        <v>11.4</v>
+        <v>22.6</v>
       </c>
       <c r="G70" t="n">
-        <v>12</v>
+        <v>16.2</v>
       </c>
       <c r="H70" t="n">
-        <v>11.5</v>
+        <v>20.8</v>
       </c>
       <c r="I70" t="n">
-        <v>10.8</v>
+        <v>16.2</v>
       </c>
       <c r="J70" t="n">
-        <v>18.5</v>
+        <v>14.4</v>
       </c>
       <c r="K70" t="n">
-        <v>10.5</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="C71" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
-        <v>1.7</v>
+        <v>8.4</v>
       </c>
       <c r="E71" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>2.4</v>
+        <v>11.4</v>
       </c>
       <c r="G71" t="n">
-        <v>1.8</v>
+        <v>15.9</v>
       </c>
       <c r="H71" t="n">
-        <v>2.2</v>
+        <v>20.4</v>
       </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>22.1</v>
       </c>
       <c r="J71" t="n">
-        <v>1.4</v>
+        <v>22.7</v>
       </c>
       <c r="K71" t="n">
-        <v>1.9</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>100</v>
+        <v>14.7</v>
       </c>
       <c r="C72" t="n">
-        <v>100</v>
+        <v>12.2</v>
       </c>
       <c r="D72" t="n">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="n">
-        <v>100</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>100</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>100</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>100</v>
+        <v>11.7</v>
       </c>
       <c r="I72" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>100</v>
+        <v>6.9</v>
       </c>
       <c r="K72" t="n">
-        <v>100</v>
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>Insecure outcome</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C73" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D73" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="E73" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F73" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G73" t="n">
+        <v>12</v>
+      </c>
+      <c r="H73" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I73" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J73" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="K73" t="n">
+        <v>10.5</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Table 4.7: Placement outcomes by level and pathway</t>
-        </is>
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I74" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1.9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>pathway_level</t>
-        </is>
-      </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="n"/>
-      <c r="D75" s="1" t="n"/>
-      <c r="E75" s="1" t="n"/>
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G75" s="1" t="n"/>
-      <c r="H75" s="1" t="n"/>
-      <c r="I75" s="1" t="n"/>
-      <c r="J75" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K75" s="1" t="n"/>
-      <c r="L75" s="1" t="n"/>
-      <c r="M75" s="1" t="n"/>
-      <c r="N75" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O75" s="1" t="n"/>
-      <c r="P75" s="1" t="n"/>
-      <c r="Q75" s="1" t="n"/>
-      <c r="R75" s="1" t="inlineStr">
-        <is>
           <t>All</t>
         </is>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>pathway_short</t>
-        </is>
-      </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D76" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="E76" s="1" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="F76" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="G76" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H76" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="I76" s="1" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="J76" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L76" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="M76" s="1" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="N76" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="O76" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="P76" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="Q76" s="1" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="R76" s="1" t="inlineStr"/>
+      <c r="B75" t="n">
+        <v>100</v>
+      </c>
+      <c r="C75" t="n">
+        <v>100</v>
+      </c>
+      <c r="D75" t="n">
+        <v>100</v>
+      </c>
+      <c r="E75" t="n">
+        <v>100</v>
+      </c>
+      <c r="F75" t="n">
+        <v>100</v>
+      </c>
+      <c r="G75" t="n">
+        <v>100</v>
+      </c>
+      <c r="H75" t="n">
+        <v>100</v>
+      </c>
+      <c r="I75" t="n">
+        <v>100</v>
+      </c>
+      <c r="J75" t="n">
+        <v>100</v>
+      </c>
+      <c r="K75" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="inlineStr">
-        <is>
-          <t>pl_outcome</t>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Table 4.7: Placement outcomes by level and pathway</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>Internal move: forwards</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>139</v>
-      </c>
-      <c r="C78" t="n">
-        <v>462</v>
-      </c>
-      <c r="D78" t="n">
-        <v>323</v>
-      </c>
-      <c r="E78" t="n">
-        <v>212</v>
-      </c>
-      <c r="F78" t="n">
-        <v>140</v>
-      </c>
-      <c r="G78" t="n">
-        <v>84</v>
-      </c>
-      <c r="H78" t="n">
-        <v>77</v>
-      </c>
-      <c r="I78" t="n">
-        <v>37</v>
-      </c>
-      <c r="J78" t="n">
-        <v>28</v>
-      </c>
-      <c r="K78" t="n">
-        <v>48</v>
-      </c>
-      <c r="L78" t="n">
-        <v>12</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>1562</v>
+          <t>pathway_level</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="n"/>
+      <c r="D78" s="1" t="n"/>
+      <c r="E78" s="1" t="n"/>
+      <c r="F78" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G78" s="1" t="n"/>
+      <c r="H78" s="1" t="n"/>
+      <c r="I78" s="1" t="n"/>
+      <c r="J78" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K78" s="1" t="n"/>
+      <c r="L78" s="1" t="n"/>
+      <c r="M78" s="1" t="n"/>
+      <c r="N78" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O78" s="1" t="n"/>
+      <c r="P78" s="1" t="n"/>
+      <c r="Q78" s="1" t="n"/>
+      <c r="R78" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>Independent accommodation</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>11</v>
-      </c>
-      <c r="C79" t="n">
-        <v>66</v>
-      </c>
-      <c r="D79" t="n">
-        <v>76</v>
-      </c>
-      <c r="E79" t="n">
-        <v>48</v>
-      </c>
-      <c r="F79" t="n">
-        <v>31</v>
-      </c>
-      <c r="G79" t="n">
-        <v>29</v>
-      </c>
-      <c r="H79" t="n">
-        <v>22</v>
-      </c>
-      <c r="I79" t="n">
-        <v>84</v>
-      </c>
-      <c r="J79" t="n">
-        <v>75</v>
-      </c>
-      <c r="K79" t="n">
-        <v>32</v>
-      </c>
-      <c r="L79" t="n">
-        <v>13</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>144</v>
-      </c>
-      <c r="O79" t="n">
-        <v>382</v>
-      </c>
-      <c r="P79" t="n">
-        <v>212</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1225</v>
-      </c>
+          <t>pathway_short</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="E79" s="1" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="F79" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G79" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H79" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="I79" s="1" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="J79" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K79" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L79" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="M79" s="1" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="N79" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O79" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P79" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="Q79" s="1" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="R79" s="1" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>Internal move: sideways</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>71</v>
-      </c>
-      <c r="C80" t="n">
-        <v>326</v>
-      </c>
-      <c r="D80" t="n">
-        <v>308</v>
-      </c>
-      <c r="E80" t="n">
-        <v>342</v>
-      </c>
-      <c r="F80" t="n">
-        <v>37</v>
-      </c>
-      <c r="G80" t="n">
-        <v>8</v>
-      </c>
-      <c r="H80" t="n">
-        <v>23</v>
-      </c>
-      <c r="I80" t="n">
-        <v>4</v>
-      </c>
-      <c r="J80" t="n">
-        <v>7</v>
-      </c>
-      <c r="K80" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" t="n">
-        <v>4</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>8</v>
-      </c>
-      <c r="O80" t="n">
-        <v>19</v>
-      </c>
-      <c r="P80" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
-        <v>1164</v>
+          <t>pl_outcome</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: forwards</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>32</v>
+        <v>139</v>
       </c>
       <c r="C81" t="n">
-        <v>215</v>
+        <v>462</v>
       </c>
       <c r="D81" t="n">
-        <v>115</v>
+        <v>323</v>
       </c>
       <c r="E81" t="n">
-        <v>168</v>
+        <v>212</v>
       </c>
       <c r="F81" t="n">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="G81" t="n">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="H81" t="n">
+        <v>77</v>
+      </c>
+      <c r="I81" t="n">
+        <v>37</v>
+      </c>
+      <c r="J81" t="n">
+        <v>28</v>
+      </c>
+      <c r="K81" t="n">
+        <v>48</v>
+      </c>
+      <c r="L81" t="n">
         <v>12</v>
       </c>
-      <c r="I81" t="n">
-        <v>21</v>
-      </c>
-      <c r="J81" t="n">
-        <v>19</v>
-      </c>
-      <c r="K81" t="n">
-        <v>8</v>
-      </c>
-      <c r="L81" t="n">
-        <v>4</v>
-      </c>
       <c r="M81" t="n">
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>744</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Independent accommodation</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F82" t="n">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="G82" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="H82" t="n">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="I82" t="n">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="J82" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="K82" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="L82" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>31</v>
+        <v>144</v>
       </c>
       <c r="O82" t="n">
-        <v>110</v>
+        <v>382</v>
       </c>
       <c r="P82" t="n">
-        <v>50</v>
+        <v>212</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>653</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>Insecure outcome</t>
+          <t>Internal move: sideways</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="C83" t="n">
-        <v>139</v>
+        <v>326</v>
       </c>
       <c r="D83" t="n">
-        <v>114</v>
+        <v>308</v>
       </c>
       <c r="E83" t="n">
-        <v>96</v>
+        <v>342</v>
       </c>
       <c r="F83" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G83" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H83" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="J83" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="K83" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
         <v>4</v>
@@ -2681,1343 +2570,1517 @@
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="O83" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="P83" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>638</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C84" t="n">
-        <v>29</v>
+        <v>215</v>
       </c>
       <c r="D84" t="n">
+        <v>115</v>
+      </c>
+      <c r="E84" t="n">
+        <v>168</v>
+      </c>
+      <c r="F84" t="n">
+        <v>36</v>
+      </c>
+      <c r="G84" t="n">
+        <v>22</v>
+      </c>
+      <c r="H84" t="n">
+        <v>12</v>
+      </c>
+      <c r="I84" t="n">
+        <v>21</v>
+      </c>
+      <c r="J84" t="n">
+        <v>19</v>
+      </c>
+      <c r="K84" t="n">
+        <v>8</v>
+      </c>
+      <c r="L84" t="n">
+        <v>4</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>22</v>
+      </c>
+      <c r="O84" t="n">
+        <v>53</v>
+      </c>
+      <c r="P84" t="n">
         <v>17</v>
       </c>
-      <c r="E84" t="n">
-        <v>14</v>
-      </c>
-      <c r="F84" t="n">
-        <v>6</v>
-      </c>
-      <c r="G84" t="n">
-        <v>7</v>
-      </c>
-      <c r="H84" t="n">
-        <v>6</v>
-      </c>
-      <c r="I84" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>9</v>
-      </c>
-      <c r="L84" t="n">
-        <v>2</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="n">
-        <v>1</v>
-      </c>
-      <c r="O84" t="n">
-        <v>11</v>
-      </c>
-      <c r="P84" t="n">
-        <v>11</v>
-      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>117</v>
+        <v>744</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>1237</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>953</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>377</v>
+        <v>89</v>
       </c>
       <c r="G85" t="n">
-        <v>227</v>
+        <v>55</v>
       </c>
       <c r="H85" t="n">
-        <v>239</v>
+        <v>74</v>
       </c>
       <c r="I85" t="n">
-        <v>301</v>
+        <v>128</v>
       </c>
       <c r="J85" t="n">
-        <v>194</v>
+        <v>46</v>
       </c>
       <c r="K85" t="n">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="L85" t="n">
-        <v>65</v>
-      </c>
-      <c r="M85" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
       <c r="N85" t="n">
-        <v>232</v>
+        <v>31</v>
       </c>
       <c r="O85" t="n">
-        <v>641</v>
+        <v>110</v>
       </c>
       <c r="P85" t="n">
-        <v>317</v>
-      </c>
-      <c r="Q85" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
       <c r="R85" t="n">
-        <v>6103</v>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>Insecure outcome</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>31</v>
+      </c>
+      <c r="C86" t="n">
+        <v>139</v>
+      </c>
+      <c r="D86" t="n">
+        <v>114</v>
+      </c>
+      <c r="E86" t="n">
+        <v>96</v>
+      </c>
+      <c r="F86" t="n">
+        <v>38</v>
+      </c>
+      <c r="G86" t="n">
+        <v>22</v>
+      </c>
+      <c r="H86" t="n">
+        <v>25</v>
+      </c>
+      <c r="I86" t="n">
+        <v>25</v>
+      </c>
+      <c r="J86" t="n">
+        <v>19</v>
+      </c>
+      <c r="K86" t="n">
+        <v>12</v>
+      </c>
+      <c r="L86" t="n">
+        <v>4</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>26</v>
+      </c>
+      <c r="O86" t="n">
+        <v>66</v>
+      </c>
+      <c r="P86" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>638</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Table 4.8: Placement outcomes (as row percentages) by level and pathway</t>
-        </is>
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>2</v>
+      </c>
+      <c r="C87" t="n">
+        <v>29</v>
+      </c>
+      <c r="D87" t="n">
+        <v>17</v>
+      </c>
+      <c r="E87" t="n">
+        <v>14</v>
+      </c>
+      <c r="F87" t="n">
+        <v>6</v>
+      </c>
+      <c r="G87" t="n">
+        <v>7</v>
+      </c>
+      <c r="H87" t="n">
+        <v>6</v>
+      </c>
+      <c r="I87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>9</v>
+      </c>
+      <c r="L87" t="n">
+        <v>2</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>11</v>
+      </c>
+      <c r="P87" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>117</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>pathway_level</t>
-        </is>
-      </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="n"/>
-      <c r="D88" s="1" t="n"/>
-      <c r="E88" s="1" t="n"/>
-      <c r="F88" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G88" s="1" t="n"/>
-      <c r="H88" s="1" t="n"/>
-      <c r="I88" s="1" t="n"/>
-      <c r="J88" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K88" s="1" t="n"/>
-      <c r="L88" s="1" t="n"/>
-      <c r="M88" s="1" t="n"/>
-      <c r="N88" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O88" s="1" t="n"/>
-      <c r="P88" s="1" t="n"/>
-      <c r="Q88" s="1" t="n"/>
-      <c r="R88" s="1" t="inlineStr">
-        <is>
           <t>All</t>
         </is>
       </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="inlineStr">
-        <is>
-          <t>pathway_short</t>
-        </is>
-      </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="G89" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H89" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="I89" s="1" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="J89" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L89" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="M89" s="1" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="N89" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="O89" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="P89" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="Q89" s="1" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="R89" s="1" t="inlineStr"/>
+      <c r="B88" t="n">
+        <v>286</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1237</v>
+      </c>
+      <c r="D88" t="n">
+        <v>953</v>
+      </c>
+      <c r="E88" t="n">
+        <v>880</v>
+      </c>
+      <c r="F88" t="n">
+        <v>377</v>
+      </c>
+      <c r="G88" t="n">
+        <v>227</v>
+      </c>
+      <c r="H88" t="n">
+        <v>239</v>
+      </c>
+      <c r="I88" t="n">
+        <v>301</v>
+      </c>
+      <c r="J88" t="n">
+        <v>194</v>
+      </c>
+      <c r="K88" t="n">
+        <v>154</v>
+      </c>
+      <c r="L88" t="n">
+        <v>65</v>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="n">
+        <v>232</v>
+      </c>
+      <c r="O88" t="n">
+        <v>641</v>
+      </c>
+      <c r="P88" t="n">
+        <v>317</v>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="n">
+        <v>6103</v>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="inlineStr">
-        <is>
-          <t>pl_outcome</t>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Table 4.8: Placement outcomes (as row percentages) by level and pathway</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>Internal move: forwards</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="C91" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="D91" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="E91" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="F91" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="G91" t="n">
-        <v>37</v>
-      </c>
-      <c r="H91" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="I91" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="J91" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K91" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="L91" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="n">
-        <v>25.6</v>
+          <t>pathway_level</t>
+        </is>
+      </c>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="n"/>
+      <c r="D91" s="1" t="n"/>
+      <c r="E91" s="1" t="n"/>
+      <c r="F91" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G91" s="1" t="n"/>
+      <c r="H91" s="1" t="n"/>
+      <c r="I91" s="1" t="n"/>
+      <c r="J91" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K91" s="1" t="n"/>
+      <c r="L91" s="1" t="n"/>
+      <c r="M91" s="1" t="n"/>
+      <c r="N91" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O91" s="1" t="n"/>
+      <c r="P91" s="1" t="n"/>
+      <c r="Q91" s="1" t="n"/>
+      <c r="R91" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>Independent accommodation</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C92" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D92" t="n">
-        <v>8</v>
-      </c>
-      <c r="E92" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F92" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="G92" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H92" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I92" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="J92" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="K92" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="L92" t="n">
-        <v>20</v>
-      </c>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="O92" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="P92" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="n">
-        <v>20.1</v>
-      </c>
+          <t>pathway_short</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="E92" s="1" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="F92" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G92" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H92" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="I92" s="1" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="J92" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K92" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L92" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="M92" s="1" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="N92" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O92" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P92" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="Q92" s="1" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="R92" s="1" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>Internal move: sideways</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="C93" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="D93" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E93" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="F93" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="G93" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H93" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J93" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L93" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O93" t="n">
-        <v>3</v>
-      </c>
-      <c r="P93" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="n">
-        <v>19.1</v>
+          <t>pl_outcome</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: forwards</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>11.2</v>
+        <v>48.6</v>
       </c>
       <c r="C94" t="n">
-        <v>17.4</v>
+        <v>37.3</v>
       </c>
       <c r="D94" t="n">
-        <v>12.1</v>
+        <v>33.9</v>
       </c>
       <c r="E94" t="n">
-        <v>19.1</v>
+        <v>24.1</v>
       </c>
       <c r="F94" t="n">
-        <v>9.5</v>
+        <v>37.1</v>
       </c>
       <c r="G94" t="n">
-        <v>9.699999999999999</v>
+        <v>37</v>
       </c>
       <c r="H94" t="n">
-        <v>5</v>
+        <v>32.2</v>
       </c>
       <c r="I94" t="n">
-        <v>7</v>
+        <v>12.3</v>
       </c>
       <c r="J94" t="n">
-        <v>9.800000000000001</v>
+        <v>14.4</v>
       </c>
       <c r="K94" t="n">
-        <v>5.2</v>
+        <v>31.2</v>
       </c>
       <c r="L94" t="n">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="n">
-        <v>12.2</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Independent accommodation</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="F95" t="n">
-        <v>23.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G95" t="n">
-        <v>24.2</v>
+        <v>12.8</v>
       </c>
       <c r="H95" t="n">
-        <v>31</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>42.5</v>
+        <v>27.9</v>
       </c>
       <c r="J95" t="n">
-        <v>23.7</v>
+        <v>38.7</v>
       </c>
       <c r="K95" t="n">
-        <v>28.6</v>
+        <v>20.8</v>
       </c>
       <c r="L95" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="n">
-        <v>13.4</v>
+        <v>62.1</v>
       </c>
       <c r="O95" t="n">
-        <v>17.2</v>
+        <v>59.6</v>
       </c>
       <c r="P95" t="n">
-        <v>15.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="n">
-        <v>10.7</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>Insecure outcome</t>
+          <t>Internal move: sideways</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>10.8</v>
+        <v>24.8</v>
       </c>
       <c r="C96" t="n">
-        <v>11.2</v>
+        <v>26.4</v>
       </c>
       <c r="D96" t="n">
-        <v>12</v>
+        <v>32.3</v>
       </c>
       <c r="E96" t="n">
-        <v>10.9</v>
+        <v>38.9</v>
       </c>
       <c r="F96" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G96" t="n">
-        <v>9.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="H96" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="I96" t="n">
-        <v>8.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="K96" t="n">
-        <v>7.8</v>
+        <v>0.6</v>
       </c>
       <c r="L96" t="n">
         <v>6.2</v>
       </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="n">
-        <v>11.2</v>
+        <v>3.4</v>
       </c>
       <c r="O96" t="n">
-        <v>10.3</v>
+        <v>3</v>
       </c>
       <c r="P96" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="n">
-        <v>10.5</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7</v>
+        <v>11.2</v>
       </c>
       <c r="C97" t="n">
-        <v>2.3</v>
+        <v>17.4</v>
       </c>
       <c r="D97" t="n">
-        <v>1.8</v>
+        <v>12.1</v>
       </c>
       <c r="E97" t="n">
-        <v>1.6</v>
+        <v>19.1</v>
       </c>
       <c r="F97" t="n">
-        <v>1.6</v>
+        <v>9.5</v>
       </c>
       <c r="G97" t="n">
-        <v>3.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H97" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>7</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K97" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="L97" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="n">
-        <v>0.4</v>
+        <v>9.5</v>
       </c>
       <c r="O97" t="n">
-        <v>1.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P97" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="n">
-        <v>1.9</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>100</v>
+        <v>23.6</v>
       </c>
       <c r="G98" t="n">
-        <v>100</v>
+        <v>24.2</v>
       </c>
       <c r="H98" t="n">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="I98" t="n">
-        <v>100</v>
+        <v>42.5</v>
       </c>
       <c r="J98" t="n">
-        <v>100</v>
+        <v>23.7</v>
       </c>
       <c r="K98" t="n">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="L98" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="n">
-        <v>100</v>
+        <v>13.4</v>
       </c>
       <c r="O98" t="n">
-        <v>100</v>
+        <v>17.2</v>
       </c>
       <c r="P98" t="n">
-        <v>100</v>
+        <v>15.8</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="n">
-        <v>100</v>
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>Insecure outcome</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C99" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D99" t="n">
+        <v>12</v>
+      </c>
+      <c r="E99" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F99" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G99" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H99" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I99" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J99" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K99" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L99" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="O99" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="P99" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="n">
+        <v>10.5</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Table 4.9: Placement outcomes from level 3-4 by shared vs. self-contained</t>
-        </is>
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C100" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G100" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L100" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O100" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P100" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="n">
+        <v>1.9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>Self-contained</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="n"/>
-      <c r="D101" s="1" t="n"/>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="F101" s="1" t="n"/>
-      <c r="G101" s="1" t="n"/>
-      <c r="H101" s="1" t="inlineStr">
-        <is>
           <t>All</t>
         </is>
       </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="inlineStr">
-        <is>
-          <t>pathway_short</t>
-        </is>
-      </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>M/F</t>
-        </is>
-      </c>
-      <c r="H102" s="1" t="inlineStr"/>
+      <c r="B101" t="n">
+        <v>100</v>
+      </c>
+      <c r="C101" t="n">
+        <v>100</v>
+      </c>
+      <c r="D101" t="n">
+        <v>100</v>
+      </c>
+      <c r="E101" t="n">
+        <v>100</v>
+      </c>
+      <c r="F101" t="n">
+        <v>100</v>
+      </c>
+      <c r="G101" t="n">
+        <v>100</v>
+      </c>
+      <c r="H101" t="n">
+        <v>100</v>
+      </c>
+      <c r="I101" t="n">
+        <v>100</v>
+      </c>
+      <c r="J101" t="n">
+        <v>100</v>
+      </c>
+      <c r="K101" t="n">
+        <v>100</v>
+      </c>
+      <c r="L101" t="n">
+        <v>100</v>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="n">
+        <v>100</v>
+      </c>
+      <c r="O101" t="n">
+        <v>100</v>
+      </c>
+      <c r="P101" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="inlineStr">
-        <is>
-          <t>pl_outcome</t>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Table 4.9: Placement outcomes from level 3-4 by shared vs. self-contained</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>Independent accommodation</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>200</v>
-      </c>
-      <c r="C104" t="n">
-        <v>352</v>
-      </c>
-      <c r="D104" t="n">
-        <v>223</v>
-      </c>
-      <c r="E104" t="n">
-        <v>19</v>
-      </c>
-      <c r="F104" t="n">
-        <v>62</v>
-      </c>
-      <c r="G104" t="n">
-        <v>2</v>
-      </c>
-      <c r="H104" t="n">
-        <v>858</v>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>Self-contained</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="n"/>
+      <c r="D104" s="1" t="n"/>
+      <c r="E104" s="1" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="F104" s="1" t="n"/>
+      <c r="G104" s="1" t="n"/>
+      <c r="H104" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>65</v>
-      </c>
-      <c r="C105" t="n">
-        <v>130</v>
-      </c>
-      <c r="D105" t="n">
-        <v>70</v>
-      </c>
-      <c r="E105" t="n">
-        <v>12</v>
-      </c>
-      <c r="F105" t="n">
-        <v>24</v>
-      </c>
-      <c r="G105" t="n">
-        <v>6</v>
-      </c>
-      <c r="H105" t="n">
-        <v>307</v>
-      </c>
+          <t>pathway_short</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="E105" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F105" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>M/F</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>Insecure outcome</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>40</v>
-      </c>
-      <c r="C106" t="n">
-        <v>58</v>
-      </c>
-      <c r="D106" t="n">
-        <v>24</v>
-      </c>
-      <c r="E106" t="n">
-        <v>5</v>
-      </c>
-      <c r="F106" t="n">
-        <v>20</v>
-      </c>
-      <c r="G106" t="n">
-        <v>1</v>
-      </c>
-      <c r="H106" t="n">
-        <v>148</v>
+          <t>pl_outcome</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Independent accommodation</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="C107" t="n">
-        <v>50</v>
+        <v>352</v>
       </c>
       <c r="D107" t="n">
-        <v>20</v>
+        <v>223</v>
       </c>
       <c r="E107" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F107" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H107" t="n">
-        <v>123</v>
+        <v>858</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>Internal move: forwards</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="C108" t="n">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="D108" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="E108" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G108" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H108" t="n">
-        <v>88</v>
+        <v>307</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>Internal move: sideways</t>
+          <t>Insecure outcome</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C109" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="D109" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G109" t="n">
         <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>45</v>
+        <v>148</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B110" t="n">
+        <v>35</v>
+      </c>
+      <c r="C110" t="n">
+        <v>50</v>
+      </c>
+      <c r="D110" t="n">
+        <v>20</v>
+      </c>
+      <c r="E110" t="n">
+        <v>6</v>
+      </c>
+      <c r="F110" t="n">
+        <v>11</v>
+      </c>
+      <c r="G110" t="n">
         <v>1</v>
       </c>
-      <c r="C110" t="n">
-        <v>19</v>
-      </c>
-      <c r="D110" t="n">
-        <v>13</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" t="n">
-        <v>1</v>
-      </c>
-      <c r="G110" t="n">
-        <v>0</v>
-      </c>
       <c r="H110" t="n">
-        <v>34</v>
+        <v>123</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Internal move: forwards</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>380</v>
+        <v>27</v>
       </c>
       <c r="C111" t="n">
-        <v>672</v>
+        <v>46</v>
       </c>
       <c r="D111" t="n">
-        <v>368</v>
+        <v>9</v>
       </c>
       <c r="E111" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>123</v>
+        <v>2</v>
       </c>
       <c r="G111" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H111" t="n">
-        <v>1603</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>Internal move: sideways</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>12</v>
+      </c>
+      <c r="C112" t="n">
+        <v>17</v>
+      </c>
+      <c r="D112" t="n">
+        <v>9</v>
+      </c>
+      <c r="E112" t="n">
+        <v>3</v>
+      </c>
+      <c r="F112" t="n">
+        <v>3</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Table 4.10: Placement outcomes (as row percentages) from level 3-4 by shared vs. self-contained</t>
-        </is>
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="n">
+        <v>19</v>
+      </c>
+      <c r="D113" t="n">
+        <v>13</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>shared</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>Self-contained %</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="n"/>
-      <c r="D114" s="1" t="n"/>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>Shared %</t>
-        </is>
-      </c>
-      <c r="F114" s="1" t="n"/>
-      <c r="G114" s="1" t="n"/>
-      <c r="H114" s="1" t="inlineStr">
-        <is>
-          <t>All %</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="1" t="inlineStr">
-        <is>
-          <t>pathway_short</t>
-        </is>
-      </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>F %</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>M %</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>M/F %</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>F %</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>M %</t>
-        </is>
-      </c>
-      <c r="G115" s="1" t="inlineStr">
-        <is>
-          <t>M/F %</t>
-        </is>
-      </c>
-      <c r="H115" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> %</t>
-        </is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>380</v>
+      </c>
+      <c r="C114" t="n">
+        <v>672</v>
+      </c>
+      <c r="D114" t="n">
+        <v>368</v>
+      </c>
+      <c r="E114" t="n">
+        <v>46</v>
+      </c>
+      <c r="F114" t="n">
+        <v>123</v>
+      </c>
+      <c r="G114" t="n">
+        <v>14</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1603</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="inlineStr">
-        <is>
-          <t>pl_outcome</t>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Table 4.10: Placement outcomes (as row percentages) from level 3-4 by shared vs. self-contained</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>Independent accommodation</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="C117" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="D117" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="E117" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="F117" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="G117" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="H117" t="n">
-        <v>53.5</v>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>Self-contained %</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="n"/>
+      <c r="D117" s="1" t="n"/>
+      <c r="E117" s="1" t="inlineStr">
+        <is>
+          <t>Shared %</t>
+        </is>
+      </c>
+      <c r="F117" s="1" t="n"/>
+      <c r="G117" s="1" t="n"/>
+      <c r="H117" s="1" t="inlineStr">
+        <is>
+          <t>All %</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="C118" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="D118" t="n">
-        <v>19</v>
-      </c>
-      <c r="E118" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="F118" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G118" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="H118" t="n">
-        <v>19.2</v>
+          <t>pathway_short</t>
+        </is>
+      </c>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t>F %</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t>M %</t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="inlineStr">
+        <is>
+          <t>M/F %</t>
+        </is>
+      </c>
+      <c r="E118" s="1" t="inlineStr">
+        <is>
+          <t>F %</t>
+        </is>
+      </c>
+      <c r="F118" s="1" t="inlineStr">
+        <is>
+          <t>M %</t>
+        </is>
+      </c>
+      <c r="G118" s="1" t="inlineStr">
+        <is>
+          <t>M/F %</t>
+        </is>
+      </c>
+      <c r="H118" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> %</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>Insecure outcome</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="C119" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="D119" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E119" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F119" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="G119" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="H119" t="n">
-        <v>9.199999999999999</v>
+          <t>pl_outcome</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Independent accommodation</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>9.199999999999999</v>
+        <v>52.6</v>
       </c>
       <c r="C120" t="n">
-        <v>7.4</v>
+        <v>52.4</v>
       </c>
       <c r="D120" t="n">
-        <v>5.4</v>
+        <v>60.6</v>
       </c>
       <c r="E120" t="n">
-        <v>13</v>
+        <v>41.3</v>
       </c>
       <c r="F120" t="n">
-        <v>8.9</v>
+        <v>50.4</v>
       </c>
       <c r="G120" t="n">
-        <v>7.1</v>
+        <v>14.3</v>
       </c>
       <c r="H120" t="n">
-        <v>7.7</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>Internal move: forwards</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>7.1</v>
+        <v>17.1</v>
       </c>
       <c r="C121" t="n">
-        <v>6.8</v>
+        <v>19.3</v>
       </c>
       <c r="D121" t="n">
-        <v>2.4</v>
+        <v>19</v>
       </c>
       <c r="E121" t="n">
-        <v>2.2</v>
+        <v>26.1</v>
       </c>
       <c r="F121" t="n">
-        <v>1.6</v>
+        <v>19.5</v>
       </c>
       <c r="G121" t="n">
-        <v>21.4</v>
+        <v>42.9</v>
       </c>
       <c r="H121" t="n">
-        <v>5.5</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>Internal move: sideways</t>
+          <t>Insecure outcome</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3.2</v>
+        <v>10.5</v>
       </c>
       <c r="C122" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="D122" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="E122" t="n">
-        <v>6.5</v>
+        <v>10.9</v>
       </c>
       <c r="F122" t="n">
-        <v>2.4</v>
+        <v>16.3</v>
       </c>
       <c r="G122" t="n">
         <v>7.1</v>
       </c>
       <c r="H122" t="n">
-        <v>2.8</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C123" t="n">
-        <v>2.8</v>
+        <v>7.4</v>
       </c>
       <c r="D123" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F123" t="n">
-        <v>0.8</v>
+        <v>8.9</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="H123" t="n">
-        <v>2.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
+          <t>Internal move: forwards</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C124" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D124" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E124" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G124" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H124" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>Internal move: sideways</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C125" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D125" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E125" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F125" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G125" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>Died</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C126" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D126" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B124" t="n">
+      <c r="B127" t="n">
         <v>100</v>
       </c>
-      <c r="C124" t="n">
+      <c r="C127" t="n">
         <v>100</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D127" t="n">
         <v>100</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E127" t="n">
         <v>100</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F127" t="n">
         <v>100</v>
       </c>
-      <c r="G124" t="n">
+      <c r="G127" t="n">
         <v>100</v>
       </c>
-      <c r="H124" t="n">
+      <c r="H127" t="n">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="J75:M75"/>
+    <mergeCell ref="J91:M91"/>
     <mergeCell ref="A9:A14"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="N88:Q88"/>
-    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="N78:Q78"/>
     <mergeCell ref="B3:B6"/>
-    <mergeCell ref="E114:G114"/>
-    <mergeCell ref="F88:I88"/>
-    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="E104:G104"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="E101:G101"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="N75:Q75"/>
-    <mergeCell ref="J88:M88"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="N91:Q91"/>
+    <mergeCell ref="B104:D104"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="A3:A8"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="F75:I75"/>
-    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="J78:M78"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="F42:I42"/>
+    <mergeCell ref="E117:G117"/>
+    <mergeCell ref="F91:I91"/>
+    <mergeCell ref="B78:E78"/>
     <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B117:D117"/>
+    <mergeCell ref="F28:I28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets_output/04_bivariate_analysis_placements.xlsx
+++ b/assets_output/04_bivariate_analysis_placements.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="52">
   <si>
     <t>Table 4.1: Placements in different pathway levels</t>
   </si>
@@ -94,13 +94,13 @@
     <t>Table 4.3: Placement outcomes by pathway type and level</t>
   </si>
   <si>
-    <t>Table 4.4: Placement outcomes (as row percentages) by pathway type and level</t>
+    <t>Table 4.4: Placement outcomes (as column percentages) by pathway type and level</t>
   </si>
   <si>
     <t>Table 4.5: Placement outcomes by calendar year</t>
   </si>
   <si>
-    <t>Table 4.6: Placement outcomes (as row percentages) by calendar year</t>
+    <t>Table 4.6: Placement outcomes (as column percentages) by calendar year</t>
   </si>
   <si>
     <t>Table 4.7: Placement outcomes by level and pathway</t>
@@ -121,13 +121,10 @@
     <t>SU</t>
   </si>
   <si>
-    <t>Table 4.8: Placement outcomes (as row percentages) by level and pathway</t>
+    <t>Table 4.8: Placement outcomes (as column percentages) by level and pathway</t>
   </si>
   <si>
     <t>Table 4.9: Placement outcomes from level 3-4 by shared vs. self-contained</t>
-  </si>
-  <si>
-    <t>shared</t>
   </si>
   <si>
     <t>Self-contained</t>
@@ -136,7 +133,7 @@
     <t>Shared</t>
   </si>
   <si>
-    <t>Table 4.10: Placement outcomes (as row percentages) from level 3-4 by shared vs. self-contained</t>
+    <t>Table 4.10: Placement outcomes (as column percentages) from level 3-4 by shared vs. self-contained</t>
   </si>
   <si>
     <t>Self-contained %</t>
@@ -146,6 +143,15 @@
   </si>
   <si>
     <t>All %</t>
+  </si>
+  <si>
+    <t>Table 4.13: Placement outcomes from level 3-4 by shared vs. self-contained and pathway</t>
+  </si>
+  <si>
+    <t>shared</t>
+  </si>
+  <si>
+    <t>Table 4.14: Placement outcomes (as column percentages) from level 3-4 by shared vs. self-contained and pathway</t>
   </si>
   <si>
     <t>F %</t>
@@ -160,7 +166,10 @@
     <t xml:space="preserve"> %</t>
   </si>
   <si>
-    <t>Table 4.11: Placement outcomes by duration</t>
+    <t>Table 4.15: Placement outcomes by duration</t>
+  </si>
+  <si>
+    <t>Table 4.16: Placement outcomes (as column percentages) by duration</t>
   </si>
 </sst>
 </file>
@@ -518,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U146"/>
+  <dimension ref="A1:W264"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2794,1545 +2803,8145 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="1:21">
+    <row r="97" spans="1:18">
       <c r="A97" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K97" s="1"/>
+      <c r="L97" s="1"/>
+      <c r="M97" s="1"/>
+      <c r="N97" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O97" s="1"/>
+      <c r="P97" s="1"/>
+      <c r="Q97" s="1"/>
+      <c r="R97" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18">
+      <c r="A98" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M98" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O98" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q98" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R98" s="1"/>
+    </row>
+    <row r="99" spans="1:18">
+      <c r="A99" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B97" s="1">
-        <v>0</v>
-      </c>
-      <c r="C97" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="D97" s="1">
-        <v>1</v>
-      </c>
-      <c r="E97" s="1">
+    </row>
+    <row r="100" spans="1:18">
+      <c r="A100" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B100">
+        <v>47.3</v>
+      </c>
+      <c r="C100">
+        <v>36.8</v>
+      </c>
+      <c r="D100">
+        <v>33.2</v>
+      </c>
+      <c r="E100">
+        <v>23</v>
+      </c>
+      <c r="F100">
+        <v>35.7</v>
+      </c>
+      <c r="G100">
+        <v>35.9</v>
+      </c>
+      <c r="H100">
+        <v>31.7</v>
+      </c>
+      <c r="I100">
+        <v>11.7</v>
+      </c>
+      <c r="J100">
+        <v>13.3</v>
+      </c>
+      <c r="K100">
+        <v>31</v>
+      </c>
+      <c r="L100">
+        <v>18.2</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="R100">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18">
+      <c r="A101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B101">
+        <v>3.7</v>
+      </c>
+      <c r="C101">
+        <v>5.3</v>
+      </c>
+      <c r="D101">
+        <v>7.8</v>
+      </c>
+      <c r="E101">
+        <v>5.2</v>
+      </c>
+      <c r="F101">
+        <v>7.9</v>
+      </c>
+      <c r="G101">
+        <v>12.4</v>
+      </c>
+      <c r="H101">
+        <v>9.1</v>
+      </c>
+      <c r="I101">
+        <v>26.6</v>
+      </c>
+      <c r="J101">
+        <v>35.5</v>
+      </c>
+      <c r="K101">
+        <v>20.6</v>
+      </c>
+      <c r="L101">
+        <v>19.7</v>
+      </c>
+      <c r="N101">
+        <v>58.8</v>
+      </c>
+      <c r="O101">
+        <v>56.6</v>
+      </c>
+      <c r="P101">
+        <v>66</v>
+      </c>
+      <c r="R101">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18">
+      <c r="A102" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B102">
+        <v>24.1</v>
+      </c>
+      <c r="C102">
+        <v>26</v>
+      </c>
+      <c r="D102">
+        <v>31.7</v>
+      </c>
+      <c r="E102">
+        <v>37.1</v>
+      </c>
+      <c r="F102">
+        <v>9.4</v>
+      </c>
+      <c r="G102">
+        <v>3.4</v>
+      </c>
+      <c r="H102">
+        <v>9.5</v>
+      </c>
+      <c r="I102">
+        <v>1.3</v>
+      </c>
+      <c r="J102">
+        <v>3.3</v>
+      </c>
+      <c r="K102">
+        <v>0.6</v>
+      </c>
+      <c r="L102">
+        <v>6.1</v>
+      </c>
+      <c r="N102">
+        <v>3.3</v>
+      </c>
+      <c r="O102">
+        <v>2.8</v>
+      </c>
+      <c r="P102">
+        <v>1.9</v>
+      </c>
+      <c r="R102">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18">
+      <c r="A103" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B103">
+        <v>10.9</v>
+      </c>
+      <c r="C103">
+        <v>17.1</v>
+      </c>
+      <c r="D103">
+        <v>11.8</v>
+      </c>
+      <c r="E103">
+        <v>18.2</v>
+      </c>
+      <c r="F103">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G103">
+        <v>9.4</v>
+      </c>
+      <c r="H103">
+        <v>4.9</v>
+      </c>
+      <c r="I103">
+        <v>6.6</v>
+      </c>
+      <c r="J103">
+        <v>9</v>
+      </c>
+      <c r="K103">
+        <v>5.2</v>
+      </c>
+      <c r="L103">
+        <v>6.1</v>
+      </c>
+      <c r="N103">
+        <v>9</v>
+      </c>
+      <c r="O103">
+        <v>7.9</v>
+      </c>
+      <c r="P103">
+        <v>5.3</v>
+      </c>
+      <c r="R103">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18">
+      <c r="A104" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>22.7</v>
+      </c>
+      <c r="G104">
+        <v>23.5</v>
+      </c>
+      <c r="H104">
+        <v>30.5</v>
+      </c>
+      <c r="I104">
+        <v>40.5</v>
+      </c>
+      <c r="J104">
+        <v>21.8</v>
+      </c>
+      <c r="K104">
+        <v>28.4</v>
+      </c>
+      <c r="L104">
+        <v>39.4</v>
+      </c>
+      <c r="N104">
+        <v>12.7</v>
+      </c>
+      <c r="O104">
+        <v>16.3</v>
+      </c>
+      <c r="P104">
+        <v>15.6</v>
+      </c>
+      <c r="R104">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18">
+      <c r="A105" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B105">
+        <v>10.5</v>
+      </c>
+      <c r="C105">
+        <v>11.1</v>
+      </c>
+      <c r="D105">
+        <v>11.7</v>
+      </c>
+      <c r="E105">
+        <v>10.4</v>
+      </c>
+      <c r="F105">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G105">
+        <v>9.4</v>
+      </c>
+      <c r="H105">
+        <v>10.3</v>
+      </c>
+      <c r="I105">
+        <v>7.9</v>
+      </c>
+      <c r="J105">
+        <v>9</v>
+      </c>
+      <c r="K105">
+        <v>7.7</v>
+      </c>
+      <c r="L105">
+        <v>6.1</v>
+      </c>
+      <c r="N105">
+        <v>10.6</v>
+      </c>
+      <c r="O105">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="P105">
+        <v>6.5</v>
+      </c>
+      <c r="R105">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18">
+      <c r="A106" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B106">
+        <v>2.7</v>
+      </c>
+      <c r="C106">
         <v>1.5</v>
       </c>
-      <c r="F97" s="1">
-        <v>2</v>
-      </c>
-      <c r="G97" s="1">
+      <c r="D106">
+        <v>2.1</v>
+      </c>
+      <c r="E106">
+        <v>4.6</v>
+      </c>
+      <c r="F106">
+        <v>3.8</v>
+      </c>
+      <c r="G106">
+        <v>3</v>
+      </c>
+      <c r="H106">
+        <v>1.6</v>
+      </c>
+      <c r="I106">
+        <v>4.7</v>
+      </c>
+      <c r="J106">
+        <v>8.1</v>
+      </c>
+      <c r="K106">
+        <v>0.6</v>
+      </c>
+      <c r="L106">
+        <v>1.5</v>
+      </c>
+      <c r="N106">
+        <v>5.3</v>
+      </c>
+      <c r="O106">
+        <v>5</v>
+      </c>
+      <c r="P106">
+        <v>1.2</v>
+      </c>
+      <c r="R106">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18">
+      <c r="A107" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B107">
+        <v>0.7</v>
+      </c>
+      <c r="C107">
+        <v>2.3</v>
+      </c>
+      <c r="D107">
+        <v>1.7</v>
+      </c>
+      <c r="E107">
+        <v>1.5</v>
+      </c>
+      <c r="F107">
+        <v>1.5</v>
+      </c>
+      <c r="G107">
+        <v>3</v>
+      </c>
+      <c r="H107">
         <v>2.5</v>
       </c>
-      <c r="H97" s="1">
+      <c r="I107">
+        <v>0.6</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>5.8</v>
+      </c>
+      <c r="L107">
         <v>3</v>
       </c>
-      <c r="I97" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="J97" s="1">
-        <v>4</v>
-      </c>
-      <c r="K97" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="L97" s="1">
-        <v>5</v>
-      </c>
-      <c r="M97" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="N97" s="1">
-        <v>6</v>
-      </c>
-      <c r="O97" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="P97" s="1">
-        <v>7</v>
-      </c>
-      <c r="Q97" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="R97" s="1">
+      <c r="N107">
+        <v>0.4</v>
+      </c>
+      <c r="O107">
+        <v>1.6</v>
+      </c>
+      <c r="P107">
+        <v>3.4</v>
+      </c>
+      <c r="R107">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18">
+      <c r="A108" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="S97" s="1">
-        <v>12.5</v>
-      </c>
-      <c r="T97" s="1">
-        <v>20</v>
-      </c>
-      <c r="U97" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:21">
-      <c r="A98" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B98">
-        <v>24.5</v>
-      </c>
-      <c r="C98">
-        <v>29</v>
-      </c>
-      <c r="D98">
-        <v>27.8</v>
-      </c>
-      <c r="E98">
-        <v>18.9</v>
-      </c>
-      <c r="F98">
-        <v>14.5</v>
-      </c>
-      <c r="G98">
-        <v>10.8</v>
-      </c>
-      <c r="H98">
-        <v>12.5</v>
-      </c>
-      <c r="I98">
-        <v>11.5</v>
-      </c>
-      <c r="J98">
-        <v>16.7</v>
-      </c>
-      <c r="K98">
-        <v>7.7</v>
-      </c>
-      <c r="M98">
-        <v>14.3</v>
-      </c>
-      <c r="N98">
-        <v>20</v>
-      </c>
-      <c r="U98">
-        <v>24.8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:21">
-      <c r="A99" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B99">
-        <v>6.6</v>
-      </c>
-      <c r="C99">
-        <v>13</v>
-      </c>
-      <c r="D99">
-        <v>27.4</v>
-      </c>
-      <c r="E99">
-        <v>40.4</v>
-      </c>
-      <c r="F99">
-        <v>46.1</v>
-      </c>
-      <c r="G99">
-        <v>55.4</v>
-      </c>
-      <c r="H99">
-        <v>52.3</v>
-      </c>
-      <c r="I99">
-        <v>46.2</v>
-      </c>
-      <c r="J99">
-        <v>33.3</v>
-      </c>
-      <c r="K99">
-        <v>53.8</v>
-      </c>
-      <c r="L99">
-        <v>37.5</v>
-      </c>
-      <c r="M99">
-        <v>42.9</v>
-      </c>
-      <c r="N99">
-        <v>60</v>
-      </c>
-      <c r="O99">
-        <v>33.3</v>
-      </c>
-      <c r="P99">
-        <v>50</v>
-      </c>
-      <c r="U99">
-        <v>19.4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:21">
-      <c r="A100" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B100">
-        <v>26.7</v>
-      </c>
-      <c r="C100">
-        <v>20.8</v>
-      </c>
-      <c r="D100">
-        <v>12</v>
-      </c>
-      <c r="E100">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="F100">
-        <v>4.8</v>
-      </c>
-      <c r="G100">
-        <v>7</v>
-      </c>
-      <c r="H100">
-        <v>2.3</v>
-      </c>
-      <c r="I100">
-        <v>1.9</v>
-      </c>
-      <c r="J100">
-        <v>5.6</v>
-      </c>
-      <c r="K100">
-        <v>7.7</v>
-      </c>
-      <c r="L100">
-        <v>25</v>
-      </c>
-      <c r="U100">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:21">
-      <c r="A101" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B101">
-        <v>15.3</v>
-      </c>
-      <c r="C101">
-        <v>12.4</v>
-      </c>
-      <c r="D101">
-        <v>8.4</v>
-      </c>
-      <c r="E101">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="F101">
-        <v>5.9</v>
-      </c>
-      <c r="G101">
-        <v>7</v>
-      </c>
-      <c r="H101">
-        <v>5.7</v>
-      </c>
-      <c r="I101">
-        <v>13.5</v>
-      </c>
-      <c r="J101">
-        <v>13.9</v>
-      </c>
-      <c r="K101">
-        <v>7.7</v>
-      </c>
-      <c r="L101">
-        <v>12.5</v>
-      </c>
-      <c r="U101">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="102" spans="1:21">
-      <c r="A102" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B102">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="C102">
-        <v>10.3</v>
-      </c>
-      <c r="D102">
-        <v>11.5</v>
-      </c>
-      <c r="E102">
-        <v>10.9</v>
-      </c>
-      <c r="F102">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="G102">
-        <v>9.1</v>
-      </c>
-      <c r="H102">
-        <v>13.6</v>
-      </c>
-      <c r="I102">
-        <v>15.4</v>
-      </c>
-      <c r="J102">
-        <v>22.2</v>
-      </c>
-      <c r="K102">
-        <v>23.1</v>
-      </c>
-      <c r="L102">
-        <v>12.5</v>
-      </c>
-      <c r="M102">
-        <v>28.6</v>
-      </c>
-      <c r="O102">
-        <v>66.7</v>
-      </c>
-      <c r="R102">
+      <c r="B108">
         <v>100</v>
       </c>
-      <c r="U102">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:21">
-      <c r="A103" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B103">
-        <v>12.8</v>
-      </c>
-      <c r="C103">
-        <v>9.9</v>
-      </c>
-      <c r="D103">
-        <v>7.4</v>
-      </c>
-      <c r="E103">
-        <v>7.8</v>
-      </c>
-      <c r="F103">
-        <v>11.9</v>
-      </c>
-      <c r="G103">
-        <v>5.9</v>
-      </c>
-      <c r="H103">
-        <v>9.1</v>
-      </c>
-      <c r="I103">
-        <v>9.6</v>
-      </c>
-      <c r="J103">
-        <v>5.6</v>
-      </c>
-      <c r="Q103">
+      <c r="C108">
         <v>100</v>
       </c>
-      <c r="S103">
+      <c r="D108">
         <v>100</v>
       </c>
-      <c r="U103">
-        <v>10.1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:21">
-      <c r="A104" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B104">
-        <v>3.6</v>
-      </c>
-      <c r="C104">
-        <v>2.9</v>
-      </c>
-      <c r="D104">
-        <v>3.1</v>
-      </c>
-      <c r="E104">
-        <v>2.8</v>
-      </c>
-      <c r="F104">
-        <v>4.5</v>
-      </c>
-      <c r="G104">
-        <v>3.2</v>
-      </c>
-      <c r="H104">
-        <v>1.1</v>
-      </c>
-      <c r="J104">
-        <v>2.8</v>
-      </c>
-      <c r="L104">
-        <v>12.5</v>
-      </c>
-      <c r="U104">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:21">
-      <c r="A105" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B105">
-        <v>1.4</v>
-      </c>
-      <c r="C105">
-        <v>1.6</v>
-      </c>
-      <c r="D105">
-        <v>2.6</v>
-      </c>
-      <c r="E105">
-        <v>2.2</v>
-      </c>
-      <c r="F105">
-        <v>3</v>
-      </c>
-      <c r="G105">
-        <v>1.6</v>
-      </c>
-      <c r="H105">
-        <v>3.4</v>
-      </c>
-      <c r="I105">
-        <v>1.9</v>
-      </c>
-      <c r="M105">
-        <v>14.3</v>
-      </c>
-      <c r="N105">
-        <v>20</v>
-      </c>
-      <c r="P105">
-        <v>50</v>
-      </c>
-      <c r="T105">
+      <c r="E108">
         <v>100</v>
       </c>
-      <c r="U105">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="106" spans="1:21">
-      <c r="A106" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B106">
+      <c r="F108">
         <v>100</v>
       </c>
-      <c r="C106">
+      <c r="G108">
         <v>100</v>
       </c>
-      <c r="D106">
+      <c r="H108">
         <v>100</v>
       </c>
-      <c r="E106">
+      <c r="I108">
         <v>100</v>
       </c>
-      <c r="F106">
+      <c r="J108">
         <v>100</v>
       </c>
-      <c r="G106">
+      <c r="K108">
         <v>100</v>
       </c>
-      <c r="H106">
+      <c r="L108">
         <v>100</v>
       </c>
-      <c r="I106">
+      <c r="N108">
         <v>100</v>
       </c>
-      <c r="J106">
+      <c r="O108">
         <v>100</v>
       </c>
-      <c r="K106">
+      <c r="P108">
         <v>100</v>
       </c>
-      <c r="L106">
+      <c r="R108">
         <v>100</v>
       </c>
-      <c r="M106">
-        <v>100</v>
-      </c>
-      <c r="N106">
-        <v>100</v>
-      </c>
-      <c r="O106">
-        <v>100</v>
-      </c>
-      <c r="P106">
-        <v>100</v>
-      </c>
-      <c r="Q106">
-        <v>100</v>
-      </c>
-      <c r="R106">
-        <v>100</v>
-      </c>
-      <c r="S106">
-        <v>100</v>
-      </c>
-      <c r="T106">
-        <v>100</v>
-      </c>
-      <c r="U106">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="108" spans="1:21">
-      <c r="A108" t="s">
+    </row>
+    <row r="110" spans="1:18">
+      <c r="A110" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="109" spans="1:21">
-      <c r="A109" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
-      <c r="E109" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F109" s="1"/>
-      <c r="G109" s="1"/>
-      <c r="H109" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="110" spans="1:21">
-      <c r="A110" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H110" s="1"/>
-    </row>
-    <row r="111" spans="1:21">
+    <row r="111" spans="1:18">
       <c r="A111" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="112" spans="1:21">
+      <c r="B111" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18">
       <c r="A112" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B112">
-        <v>200</v>
+        <v>775</v>
       </c>
       <c r="C112">
-        <v>352</v>
+        <v>83</v>
       </c>
       <c r="D112">
-        <v>223</v>
-      </c>
-      <c r="E112">
-        <v>19</v>
-      </c>
-      <c r="F112">
-        <v>62</v>
-      </c>
-      <c r="G112">
-        <v>2</v>
-      </c>
-      <c r="H112">
         <v>858</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:4">
       <c r="A113" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B113">
-        <v>65</v>
+        <v>265</v>
       </c>
       <c r="C113">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="D113">
-        <v>70</v>
-      </c>
-      <c r="E113">
-        <v>12</v>
-      </c>
-      <c r="F113">
-        <v>24</v>
-      </c>
-      <c r="G113">
-        <v>6</v>
-      </c>
-      <c r="H113">
         <v>307</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:4">
       <c r="A114" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B114">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="C114">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="D114">
-        <v>24</v>
-      </c>
-      <c r="E114">
-        <v>5</v>
-      </c>
-      <c r="F114">
-        <v>20</v>
-      </c>
-      <c r="G114">
-        <v>1</v>
-      </c>
-      <c r="H114">
         <v>148</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:4">
       <c r="A115" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B115">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="C115">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="D115">
-        <v>20</v>
-      </c>
-      <c r="E115">
-        <v>6</v>
-      </c>
-      <c r="F115">
-        <v>11</v>
-      </c>
-      <c r="G115">
-        <v>1</v>
-      </c>
-      <c r="H115">
         <v>123</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:4">
       <c r="A116" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B116">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="C116">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="D116">
-        <v>9</v>
-      </c>
-      <c r="E116">
-        <v>1</v>
-      </c>
-      <c r="F116">
-        <v>2</v>
-      </c>
-      <c r="G116">
-        <v>3</v>
-      </c>
-      <c r="H116">
         <v>88</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:4">
       <c r="A117" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B117">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C117">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D117">
-        <v>5</v>
-      </c>
-      <c r="E117">
-        <v>6</v>
-      </c>
-      <c r="F117">
-        <v>12</v>
-      </c>
-      <c r="G117">
-        <v>0</v>
-      </c>
-      <c r="H117">
         <v>70</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:4">
       <c r="A118" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B118">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="C118">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D118">
-        <v>9</v>
-      </c>
-      <c r="E118">
-        <v>3</v>
-      </c>
-      <c r="F118">
-        <v>3</v>
-      </c>
-      <c r="G118">
-        <v>1</v>
-      </c>
-      <c r="H118">
         <v>45</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:4">
       <c r="A119" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B119">
+        <v>33</v>
+      </c>
+      <c r="C119">
         <v>1</v>
       </c>
-      <c r="C119">
-        <v>19</v>
-      </c>
       <c r="D119">
-        <v>13</v>
-      </c>
-      <c r="E119">
-        <v>0</v>
-      </c>
-      <c r="F119">
-        <v>1</v>
-      </c>
-      <c r="G119">
-        <v>0</v>
-      </c>
-      <c r="H119">
         <v>34</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:4">
       <c r="A120" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B120">
-        <v>404</v>
+        <v>1472</v>
       </c>
       <c r="C120">
-        <v>695</v>
+        <v>201</v>
       </c>
       <c r="D120">
-        <v>373</v>
-      </c>
-      <c r="E120">
-        <v>52</v>
-      </c>
-      <c r="F120">
-        <v>135</v>
-      </c>
-      <c r="G120">
-        <v>14</v>
-      </c>
-      <c r="H120">
         <v>1673</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:4">
       <c r="A122" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="123" spans="1:8">
-      <c r="A123" s="1" t="s">
+      <c r="C123" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B124">
+        <v>52.6</v>
+      </c>
+      <c r="C124">
+        <v>41.3</v>
+      </c>
+      <c r="D124">
+        <v>51.3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B125">
+        <v>18</v>
+      </c>
+      <c r="C125">
+        <v>20.9</v>
+      </c>
+      <c r="D125">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B126">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="C126">
+        <v>12.9</v>
+      </c>
+      <c r="D126">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B127">
+        <v>7.1</v>
+      </c>
+      <c r="C127">
+        <v>9</v>
+      </c>
+      <c r="D127">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B128">
+        <v>5.6</v>
+      </c>
+      <c r="C128">
+        <v>3</v>
+      </c>
+      <c r="D128">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B129">
+        <v>3.5</v>
+      </c>
+      <c r="C129">
+        <v>9</v>
+      </c>
+      <c r="D129">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B130">
+        <v>2.6</v>
+      </c>
+      <c r="C130">
+        <v>3.5</v>
+      </c>
+      <c r="D130">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B131">
+        <v>2.2</v>
+      </c>
+      <c r="C131">
+        <v>0.5</v>
+      </c>
+      <c r="D131">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B132">
+        <v>100</v>
+      </c>
+      <c r="C132">
+        <v>100</v>
+      </c>
+      <c r="D132">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
-      <c r="E123" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F123" s="1"/>
-      <c r="G123" s="1"/>
-      <c r="H123" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8">
-      <c r="A124" s="1" t="s">
+      <c r="C135" s="1"/>
+      <c r="D135" s="1"/>
+      <c r="E135" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F135" s="1"/>
+      <c r="G135" s="1"/>
+      <c r="H135" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H124" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8">
-      <c r="A125" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8">
-      <c r="A126" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B126">
-        <v>49.5</v>
-      </c>
-      <c r="C126">
-        <v>50.6</v>
-      </c>
-      <c r="D126">
-        <v>59.8</v>
-      </c>
-      <c r="E126">
-        <v>36.5</v>
-      </c>
-      <c r="F126">
-        <v>45.9</v>
-      </c>
-      <c r="G126">
-        <v>14.3</v>
-      </c>
-      <c r="H126">
-        <v>51.3</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8">
-      <c r="A127" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B127">
-        <v>16.1</v>
-      </c>
-      <c r="C127">
-        <v>18.7</v>
-      </c>
-      <c r="D127">
-        <v>18.8</v>
-      </c>
-      <c r="E127">
-        <v>23.1</v>
-      </c>
-      <c r="F127">
-        <v>17.8</v>
-      </c>
-      <c r="G127">
-        <v>42.9</v>
-      </c>
-      <c r="H127">
-        <v>18.4</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8">
-      <c r="A128" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B128">
-        <v>9.9</v>
-      </c>
-      <c r="C128">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="D128">
-        <v>6.4</v>
-      </c>
-      <c r="E128">
-        <v>9.6</v>
-      </c>
-      <c r="F128">
-        <v>14.8</v>
-      </c>
-      <c r="G128">
-        <v>7.1</v>
-      </c>
-      <c r="H128">
-        <v>8.800000000000001</v>
-      </c>
-    </row>
-    <row r="129" spans="1:21">
-      <c r="A129" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B129">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="C129">
-        <v>7.2</v>
-      </c>
-      <c r="D129">
-        <v>5.4</v>
-      </c>
-      <c r="E129">
-        <v>11.5</v>
-      </c>
-      <c r="F129">
-        <v>8.1</v>
-      </c>
-      <c r="G129">
-        <v>7.1</v>
-      </c>
-      <c r="H129">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="130" spans="1:21">
-      <c r="A130" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B130">
-        <v>6.7</v>
-      </c>
-      <c r="C130">
-        <v>6.6</v>
-      </c>
-      <c r="D130">
-        <v>2.4</v>
-      </c>
-      <c r="E130">
-        <v>1.9</v>
-      </c>
-      <c r="F130">
-        <v>1.5</v>
-      </c>
-      <c r="G130">
-        <v>21.4</v>
-      </c>
-      <c r="H130">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="131" spans="1:21">
-      <c r="A131" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B131">
-        <v>5.9</v>
-      </c>
-      <c r="C131">
-        <v>3.3</v>
-      </c>
-      <c r="D131">
-        <v>1.3</v>
-      </c>
-      <c r="E131">
-        <v>11.5</v>
-      </c>
-      <c r="F131">
-        <v>8.9</v>
-      </c>
-      <c r="G131">
-        <v>0</v>
-      </c>
-      <c r="H131">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="132" spans="1:21">
-      <c r="A132" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B132">
-        <v>3</v>
-      </c>
-      <c r="C132">
-        <v>2.4</v>
-      </c>
-      <c r="D132">
-        <v>2.4</v>
-      </c>
-      <c r="E132">
-        <v>5.8</v>
-      </c>
-      <c r="F132">
-        <v>2.2</v>
-      </c>
-      <c r="G132">
-        <v>7.1</v>
-      </c>
-      <c r="H132">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="133" spans="1:21">
-      <c r="A133" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B133">
-        <v>0.2</v>
-      </c>
-      <c r="C133">
-        <v>2.7</v>
-      </c>
-      <c r="D133">
-        <v>3.5</v>
-      </c>
-      <c r="E133">
-        <v>0</v>
-      </c>
-      <c r="F133">
-        <v>0.7</v>
-      </c>
-      <c r="G133">
-        <v>0</v>
-      </c>
-      <c r="H133">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="134" spans="1:21">
-      <c r="A134" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B134">
-        <v>100</v>
-      </c>
-      <c r="C134">
-        <v>100</v>
-      </c>
-      <c r="D134">
-        <v>100</v>
-      </c>
-      <c r="E134">
-        <v>100</v>
-      </c>
-      <c r="F134">
-        <v>100</v>
-      </c>
-      <c r="G134">
-        <v>100</v>
-      </c>
-      <c r="H134">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="136" spans="1:21">
-      <c r="A136" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="137" spans="1:21">
+      <c r="B136" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H136" s="1"/>
+    </row>
+    <row r="137" spans="1:8">
       <c r="A137" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B137" s="1">
-        <v>0</v>
-      </c>
-      <c r="C137" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="D137" s="1">
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B138">
+        <v>200</v>
+      </c>
+      <c r="C138">
+        <v>352</v>
+      </c>
+      <c r="D138">
+        <v>223</v>
+      </c>
+      <c r="E138">
+        <v>19</v>
+      </c>
+      <c r="F138">
+        <v>62</v>
+      </c>
+      <c r="G138">
+        <v>2</v>
+      </c>
+      <c r="H138">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B139">
+        <v>65</v>
+      </c>
+      <c r="C139">
+        <v>130</v>
+      </c>
+      <c r="D139">
+        <v>70</v>
+      </c>
+      <c r="E139">
+        <v>12</v>
+      </c>
+      <c r="F139">
+        <v>24</v>
+      </c>
+      <c r="G139">
+        <v>6</v>
+      </c>
+      <c r="H139">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B140">
+        <v>40</v>
+      </c>
+      <c r="C140">
+        <v>58</v>
+      </c>
+      <c r="D140">
+        <v>24</v>
+      </c>
+      <c r="E140">
+        <v>5</v>
+      </c>
+      <c r="F140">
+        <v>20</v>
+      </c>
+      <c r="G140">
         <v>1</v>
       </c>
-      <c r="E137" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="F137" s="1">
-        <v>2</v>
-      </c>
-      <c r="G137" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="H137" s="1">
-        <v>3</v>
-      </c>
-      <c r="I137" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="J137" s="1">
-        <v>4</v>
-      </c>
-      <c r="K137" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="L137" s="1">
-        <v>5</v>
-      </c>
-      <c r="M137" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="N137" s="1">
-        <v>6</v>
-      </c>
-      <c r="O137" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="P137" s="1">
-        <v>7</v>
-      </c>
-      <c r="Q137" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="R137" s="1">
-        <v>8</v>
-      </c>
-      <c r="S137" s="1">
-        <v>12.5</v>
-      </c>
-      <c r="T137" s="1">
-        <v>20</v>
-      </c>
-      <c r="U137" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="138" spans="1:21">
-      <c r="A138" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B138">
-        <v>481</v>
-      </c>
-      <c r="C138">
-        <v>613</v>
-      </c>
-      <c r="D138">
-        <v>281</v>
-      </c>
-      <c r="E138">
-        <v>102</v>
-      </c>
-      <c r="F138">
-        <v>39</v>
-      </c>
-      <c r="G138">
-        <v>20</v>
-      </c>
-      <c r="H138">
-        <v>11</v>
-      </c>
-      <c r="I138">
-        <v>6</v>
-      </c>
-      <c r="J138">
-        <v>6</v>
-      </c>
-      <c r="K138">
-        <v>1</v>
-      </c>
-      <c r="M138">
-        <v>1</v>
-      </c>
-      <c r="N138">
-        <v>1</v>
-      </c>
-      <c r="U138">
-        <v>1562</v>
-      </c>
-    </row>
-    <row r="139" spans="1:21">
-      <c r="A139" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B139">
-        <v>129</v>
-      </c>
-      <c r="C139">
-        <v>274</v>
-      </c>
-      <c r="D139">
-        <v>277</v>
-      </c>
-      <c r="E139">
-        <v>218</v>
-      </c>
-      <c r="F139">
-        <v>124</v>
-      </c>
-      <c r="G139">
-        <v>103</v>
-      </c>
-      <c r="H139">
-        <v>46</v>
-      </c>
-      <c r="I139">
-        <v>24</v>
-      </c>
-      <c r="J139">
-        <v>12</v>
-      </c>
-      <c r="K139">
-        <v>7</v>
-      </c>
-      <c r="L139">
-        <v>3</v>
-      </c>
-      <c r="M139">
-        <v>3</v>
-      </c>
-      <c r="N139">
-        <v>3</v>
-      </c>
-      <c r="O139">
-        <v>1</v>
-      </c>
-      <c r="P139">
-        <v>1</v>
-      </c>
-      <c r="U139">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="140" spans="1:21">
-      <c r="A140" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B140">
-        <v>524</v>
-      </c>
-      <c r="C140">
-        <v>440</v>
-      </c>
-      <c r="D140">
-        <v>121</v>
-      </c>
-      <c r="E140">
-        <v>45</v>
-      </c>
-      <c r="F140">
-        <v>13</v>
-      </c>
-      <c r="G140">
-        <v>13</v>
-      </c>
       <c r="H140">
-        <v>2</v>
-      </c>
-      <c r="I140">
-        <v>1</v>
-      </c>
-      <c r="J140">
-        <v>2</v>
-      </c>
-      <c r="K140">
-        <v>1</v>
-      </c>
-      <c r="L140">
-        <v>2</v>
-      </c>
-      <c r="U140">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="141" spans="1:21">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
       <c r="A141" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B141">
-        <v>301</v>
+        <v>35</v>
       </c>
       <c r="C141">
-        <v>263</v>
+        <v>50</v>
       </c>
       <c r="D141">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="E141">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F141">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G141">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H141">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B142">
+        <v>27</v>
+      </c>
+      <c r="C142">
+        <v>46</v>
+      </c>
+      <c r="D142">
+        <v>9</v>
+      </c>
+      <c r="E142">
+        <v>1</v>
+      </c>
+      <c r="F142">
+        <v>2</v>
+      </c>
+      <c r="G142">
+        <v>3</v>
+      </c>
+      <c r="H142">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B143">
+        <v>24</v>
+      </c>
+      <c r="C143">
+        <v>23</v>
+      </c>
+      <c r="D143">
         <v>5</v>
       </c>
-      <c r="I141">
-        <v>7</v>
-      </c>
-      <c r="J141">
-        <v>5</v>
-      </c>
-      <c r="K141">
+      <c r="E143">
+        <v>6</v>
+      </c>
+      <c r="F143">
+        <v>12</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B144">
+        <v>12</v>
+      </c>
+      <c r="C144">
+        <v>17</v>
+      </c>
+      <c r="D144">
+        <v>9</v>
+      </c>
+      <c r="E144">
+        <v>3</v>
+      </c>
+      <c r="F144">
+        <v>3</v>
+      </c>
+      <c r="G144">
         <v>1</v>
       </c>
-      <c r="L141">
-        <v>1</v>
-      </c>
-      <c r="U141">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="142" spans="1:21">
-      <c r="A142" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B142">
-        <v>181</v>
-      </c>
-      <c r="C142">
-        <v>218</v>
-      </c>
-      <c r="D142">
-        <v>116</v>
-      </c>
-      <c r="E142">
-        <v>59</v>
-      </c>
-      <c r="F142">
-        <v>25</v>
-      </c>
-      <c r="G142">
-        <v>17</v>
-      </c>
-      <c r="H142">
-        <v>12</v>
-      </c>
-      <c r="I142">
-        <v>8</v>
-      </c>
-      <c r="J142">
-        <v>8</v>
-      </c>
-      <c r="K142">
-        <v>3</v>
-      </c>
-      <c r="L142">
-        <v>1</v>
-      </c>
-      <c r="M142">
-        <v>2</v>
-      </c>
-      <c r="O142">
-        <v>2</v>
-      </c>
-      <c r="R142">
-        <v>1</v>
-      </c>
-      <c r="U142">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="143" spans="1:21">
-      <c r="A143" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B143">
-        <v>251</v>
-      </c>
-      <c r="C143">
-        <v>210</v>
-      </c>
-      <c r="D143">
-        <v>75</v>
-      </c>
-      <c r="E143">
-        <v>42</v>
-      </c>
-      <c r="F143">
-        <v>32</v>
-      </c>
-      <c r="G143">
-        <v>11</v>
-      </c>
-      <c r="H143">
-        <v>8</v>
-      </c>
-      <c r="I143">
-        <v>5</v>
-      </c>
-      <c r="J143">
-        <v>2</v>
-      </c>
-      <c r="Q143">
-        <v>1</v>
-      </c>
-      <c r="S143">
-        <v>1</v>
-      </c>
-      <c r="U143">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="144" spans="1:21">
-      <c r="A144" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B144">
-        <v>71</v>
-      </c>
-      <c r="C144">
-        <v>62</v>
-      </c>
-      <c r="D144">
-        <v>31</v>
-      </c>
-      <c r="E144">
-        <v>15</v>
-      </c>
-      <c r="F144">
-        <v>12</v>
-      </c>
-      <c r="G144">
-        <v>6</v>
-      </c>
       <c r="H144">
-        <v>1</v>
-      </c>
-      <c r="J144">
-        <v>1</v>
-      </c>
-      <c r="L144">
-        <v>1</v>
-      </c>
-      <c r="U144">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="145" spans="1:21">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
       <c r="A145" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B145">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C145">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D145">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E145">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F145">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G145">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>3</v>
-      </c>
-      <c r="I145">
-        <v>1</v>
-      </c>
-      <c r="M145">
-        <v>1</v>
-      </c>
-      <c r="N145">
-        <v>1</v>
-      </c>
-      <c r="P145">
-        <v>1</v>
-      </c>
-      <c r="T145">
-        <v>1</v>
-      </c>
-      <c r="U145">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="146" spans="1:21">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
       <c r="A146" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B146">
+        <v>404</v>
+      </c>
+      <c r="C146">
+        <v>695</v>
+      </c>
+      <c r="D146">
+        <v>373</v>
+      </c>
+      <c r="E146">
+        <v>52</v>
+      </c>
+      <c r="F146">
+        <v>135</v>
+      </c>
+      <c r="G146">
+        <v>14</v>
+      </c>
+      <c r="H146">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
+      <c r="E149" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F149" s="1"/>
+      <c r="G149" s="1"/>
+      <c r="H149" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B152">
+        <v>49.5</v>
+      </c>
+      <c r="C152">
+        <v>50.6</v>
+      </c>
+      <c r="D152">
+        <v>59.8</v>
+      </c>
+      <c r="E152">
+        <v>36.5</v>
+      </c>
+      <c r="F152">
+        <v>45.9</v>
+      </c>
+      <c r="G152">
+        <v>14.3</v>
+      </c>
+      <c r="H152">
+        <v>51.3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B153">
+        <v>16.1</v>
+      </c>
+      <c r="C153">
+        <v>18.7</v>
+      </c>
+      <c r="D153">
+        <v>18.8</v>
+      </c>
+      <c r="E153">
+        <v>23.1</v>
+      </c>
+      <c r="F153">
+        <v>17.8</v>
+      </c>
+      <c r="G153">
+        <v>42.9</v>
+      </c>
+      <c r="H153">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B154">
+        <v>9.9</v>
+      </c>
+      <c r="C154">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="D154">
+        <v>6.4</v>
+      </c>
+      <c r="E154">
+        <v>9.6</v>
+      </c>
+      <c r="F154">
+        <v>14.8</v>
+      </c>
+      <c r="G154">
+        <v>7.1</v>
+      </c>
+      <c r="H154">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B155">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="C155">
+        <v>7.2</v>
+      </c>
+      <c r="D155">
+        <v>5.4</v>
+      </c>
+      <c r="E155">
+        <v>11.5</v>
+      </c>
+      <c r="F155">
+        <v>8.1</v>
+      </c>
+      <c r="G155">
+        <v>7.1</v>
+      </c>
+      <c r="H155">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B156">
+        <v>6.7</v>
+      </c>
+      <c r="C156">
+        <v>6.6</v>
+      </c>
+      <c r="D156">
+        <v>2.4</v>
+      </c>
+      <c r="E156">
+        <v>1.9</v>
+      </c>
+      <c r="F156">
+        <v>1.5</v>
+      </c>
+      <c r="G156">
+        <v>21.4</v>
+      </c>
+      <c r="H156">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B157">
+        <v>5.9</v>
+      </c>
+      <c r="C157">
+        <v>3.3</v>
+      </c>
+      <c r="D157">
+        <v>1.3</v>
+      </c>
+      <c r="E157">
+        <v>11.5</v>
+      </c>
+      <c r="F157">
+        <v>8.9</v>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B158">
+        <v>3</v>
+      </c>
+      <c r="C158">
+        <v>2.4</v>
+      </c>
+      <c r="D158">
+        <v>2.4</v>
+      </c>
+      <c r="E158">
+        <v>5.8</v>
+      </c>
+      <c r="F158">
+        <v>2.2</v>
+      </c>
+      <c r="G158">
+        <v>7.1</v>
+      </c>
+      <c r="H158">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B159">
+        <v>0.2</v>
+      </c>
+      <c r="C159">
+        <v>2.7</v>
+      </c>
+      <c r="D159">
+        <v>3.5</v>
+      </c>
+      <c r="E159">
+        <v>0</v>
+      </c>
+      <c r="F159">
+        <v>0.7</v>
+      </c>
+      <c r="G159">
+        <v>0</v>
+      </c>
+      <c r="H159">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
+      <c r="A160" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B160">
+        <v>100</v>
+      </c>
+      <c r="C160">
+        <v>100</v>
+      </c>
+      <c r="D160">
+        <v>100</v>
+      </c>
+      <c r="E160">
+        <v>100</v>
+      </c>
+      <c r="F160">
+        <v>100</v>
+      </c>
+      <c r="G160">
+        <v>100</v>
+      </c>
+      <c r="H160">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="162" spans="1:23">
+      <c r="A162" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="163" spans="1:23">
+      <c r="A163" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D163" s="1">
+        <v>0</v>
+      </c>
+      <c r="E163" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F163" s="1">
+        <v>1</v>
+      </c>
+      <c r="G163" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H163" s="1">
+        <v>2</v>
+      </c>
+      <c r="I163" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="J163" s="1">
+        <v>3</v>
+      </c>
+      <c r="K163" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="L163" s="1">
+        <v>4</v>
+      </c>
+      <c r="M163" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="N163" s="1">
+        <v>5</v>
+      </c>
+      <c r="O163" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="P163" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q163" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="R163" s="1">
+        <v>7</v>
+      </c>
+      <c r="S163" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="T163" s="1">
+        <v>8</v>
+      </c>
+      <c r="U163" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="V163" s="1">
+        <v>20</v>
+      </c>
+      <c r="W163" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:23">
+      <c r="A164" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D164">
+        <v>13</v>
+      </c>
+      <c r="E164">
+        <v>16</v>
+      </c>
+      <c r="F164">
+        <v>16</v>
+      </c>
+      <c r="G164">
+        <v>3</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
+      </c>
+      <c r="N164">
+        <v>0</v>
+      </c>
+      <c r="O164">
+        <v>0</v>
+      </c>
+      <c r="P164">
+        <v>0</v>
+      </c>
+      <c r="Q164">
+        <v>0</v>
+      </c>
+      <c r="R164">
+        <v>0</v>
+      </c>
+      <c r="S164">
+        <v>0</v>
+      </c>
+      <c r="T164">
+        <v>0</v>
+      </c>
+      <c r="U164">
+        <v>0</v>
+      </c>
+      <c r="V164">
+        <v>0</v>
+      </c>
+      <c r="W164">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="165" spans="1:23">
+      <c r="A165" s="1"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D165">
+        <v>32</v>
+      </c>
+      <c r="E165">
+        <v>64</v>
+      </c>
+      <c r="F165">
+        <v>26</v>
+      </c>
+      <c r="G165">
+        <v>16</v>
+      </c>
+      <c r="H165">
+        <v>6</v>
+      </c>
+      <c r="I165">
+        <v>2</v>
+      </c>
+      <c r="J165">
+        <v>6</v>
+      </c>
+      <c r="K165">
+        <v>0</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+      <c r="M165">
+        <v>0</v>
+      </c>
+      <c r="N165">
+        <v>0</v>
+      </c>
+      <c r="O165">
+        <v>1</v>
+      </c>
+      <c r="P165">
+        <v>0</v>
+      </c>
+      <c r="Q165">
+        <v>0</v>
+      </c>
+      <c r="R165">
+        <v>0</v>
+      </c>
+      <c r="S165">
+        <v>0</v>
+      </c>
+      <c r="T165">
+        <v>0</v>
+      </c>
+      <c r="U165">
+        <v>0</v>
+      </c>
+      <c r="V165">
+        <v>0</v>
+      </c>
+      <c r="W165">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="166" spans="1:23">
+      <c r="A166" s="1"/>
+      <c r="B166" s="1"/>
+      <c r="C166" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D166">
+        <v>129</v>
+      </c>
+      <c r="E166">
+        <v>94</v>
+      </c>
+      <c r="F166">
+        <v>30</v>
+      </c>
+      <c r="G166">
+        <v>18</v>
+      </c>
+      <c r="H166">
+        <v>7</v>
+      </c>
+      <c r="I166">
+        <v>3</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>2</v>
+      </c>
+      <c r="L166">
+        <v>1</v>
+      </c>
+      <c r="M166">
+        <v>0</v>
+      </c>
+      <c r="N166">
+        <v>0</v>
+      </c>
+      <c r="O166">
+        <v>0</v>
+      </c>
+      <c r="P166">
+        <v>0</v>
+      </c>
+      <c r="Q166">
+        <v>0</v>
+      </c>
+      <c r="R166">
+        <v>0</v>
+      </c>
+      <c r="S166">
+        <v>0</v>
+      </c>
+      <c r="T166">
+        <v>0</v>
+      </c>
+      <c r="U166">
+        <v>0</v>
+      </c>
+      <c r="V166">
+        <v>0</v>
+      </c>
+      <c r="W166">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="167" spans="1:23">
+      <c r="A167" s="1"/>
+      <c r="B167" s="1"/>
+      <c r="C167" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="E167">
+        <v>0</v>
+      </c>
+      <c r="F167">
+        <v>0</v>
+      </c>
+      <c r="G167">
+        <v>0</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>0</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167">
+        <v>0</v>
+      </c>
+      <c r="N167">
+        <v>0</v>
+      </c>
+      <c r="O167">
+        <v>0</v>
+      </c>
+      <c r="P167">
+        <v>0</v>
+      </c>
+      <c r="Q167">
+        <v>0</v>
+      </c>
+      <c r="R167">
+        <v>0</v>
+      </c>
+      <c r="S167">
+        <v>0</v>
+      </c>
+      <c r="T167">
+        <v>0</v>
+      </c>
+      <c r="U167">
+        <v>0</v>
+      </c>
+      <c r="V167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:23">
+      <c r="A168" s="1"/>
+      <c r="B168" s="1"/>
+      <c r="C168" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D168">
+        <v>297</v>
+      </c>
+      <c r="E168">
+        <v>357</v>
+      </c>
+      <c r="F168">
+        <v>176</v>
+      </c>
+      <c r="G168">
+        <v>46</v>
+      </c>
+      <c r="H168">
+        <v>23</v>
+      </c>
+      <c r="I168">
+        <v>12</v>
+      </c>
+      <c r="J168">
+        <v>5</v>
+      </c>
+      <c r="K168">
+        <v>3</v>
+      </c>
+      <c r="L168">
+        <v>3</v>
+      </c>
+      <c r="M168">
+        <v>1</v>
+      </c>
+      <c r="N168">
+        <v>0</v>
+      </c>
+      <c r="O168">
+        <v>1</v>
+      </c>
+      <c r="P168">
+        <v>0</v>
+      </c>
+      <c r="Q168">
+        <v>0</v>
+      </c>
+      <c r="R168">
+        <v>0</v>
+      </c>
+      <c r="S168">
+        <v>0</v>
+      </c>
+      <c r="T168">
+        <v>0</v>
+      </c>
+      <c r="U168">
+        <v>0</v>
+      </c>
+      <c r="V168">
+        <v>0</v>
+      </c>
+      <c r="W168">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="169" spans="1:23">
+      <c r="A169" s="1"/>
+      <c r="B169" s="1"/>
+      <c r="C169" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D169">
+        <v>312</v>
+      </c>
+      <c r="E169">
+        <v>258</v>
+      </c>
+      <c r="F169">
+        <v>78</v>
+      </c>
+      <c r="G169">
+        <v>37</v>
+      </c>
+      <c r="H169">
+        <v>9</v>
+      </c>
+      <c r="I169">
+        <v>7</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>1</v>
+      </c>
+      <c r="L169">
+        <v>2</v>
+      </c>
+      <c r="M169">
+        <v>0</v>
+      </c>
+      <c r="N169">
+        <v>1</v>
+      </c>
+      <c r="O169">
+        <v>0</v>
+      </c>
+      <c r="P169">
+        <v>0</v>
+      </c>
+      <c r="Q169">
+        <v>0</v>
+      </c>
+      <c r="R169">
+        <v>0</v>
+      </c>
+      <c r="S169">
+        <v>0</v>
+      </c>
+      <c r="T169">
+        <v>0</v>
+      </c>
+      <c r="U169">
+        <v>0</v>
+      </c>
+      <c r="V169">
+        <v>0</v>
+      </c>
+      <c r="W169">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="170" spans="1:23">
+      <c r="A170" s="1"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D170">
+        <v>18</v>
+      </c>
+      <c r="E170">
+        <v>15</v>
+      </c>
+      <c r="F170">
+        <v>7</v>
+      </c>
+      <c r="G170">
+        <v>3</v>
+      </c>
+      <c r="H170">
+        <v>3</v>
+      </c>
+      <c r="I170">
+        <v>1</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>0</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="M170">
+        <v>0</v>
+      </c>
+      <c r="N170">
+        <v>0</v>
+      </c>
+      <c r="O170">
+        <v>0</v>
+      </c>
+      <c r="P170">
+        <v>0</v>
+      </c>
+      <c r="Q170">
+        <v>0</v>
+      </c>
+      <c r="R170">
+        <v>0</v>
+      </c>
+      <c r="S170">
+        <v>0</v>
+      </c>
+      <c r="T170">
+        <v>0</v>
+      </c>
+      <c r="U170">
+        <v>0</v>
+      </c>
+      <c r="V170">
+        <v>0</v>
+      </c>
+      <c r="W170">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="171" spans="1:23">
+      <c r="A171" s="1"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D171">
+        <v>167</v>
+      </c>
+      <c r="E171">
+        <v>126</v>
+      </c>
+      <c r="F171">
+        <v>35</v>
+      </c>
+      <c r="G171">
+        <v>19</v>
+      </c>
+      <c r="H171">
+        <v>8</v>
+      </c>
+      <c r="I171">
+        <v>2</v>
+      </c>
+      <c r="J171">
+        <v>2</v>
+      </c>
+      <c r="K171">
+        <v>0</v>
+      </c>
+      <c r="L171">
+        <v>1</v>
+      </c>
+      <c r="M171">
+        <v>1</v>
+      </c>
+      <c r="N171">
+        <v>1</v>
+      </c>
+      <c r="O171">
+        <v>0</v>
+      </c>
+      <c r="P171">
+        <v>0</v>
+      </c>
+      <c r="Q171">
+        <v>0</v>
+      </c>
+      <c r="R171">
+        <v>0</v>
+      </c>
+      <c r="S171">
+        <v>0</v>
+      </c>
+      <c r="T171">
+        <v>0</v>
+      </c>
+      <c r="U171">
+        <v>0</v>
+      </c>
+      <c r="V171">
+        <v>0</v>
+      </c>
+      <c r="W171">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="172" spans="1:23">
+      <c r="A172" s="1"/>
+      <c r="B172" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D172">
+        <v>3</v>
+      </c>
+      <c r="E172">
+        <v>6</v>
+      </c>
+      <c r="F172">
+        <v>2</v>
+      </c>
+      <c r="G172">
+        <v>2</v>
+      </c>
+      <c r="H172">
+        <v>4</v>
+      </c>
+      <c r="I172">
+        <v>1</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>0</v>
+      </c>
+      <c r="L172">
+        <v>0</v>
+      </c>
+      <c r="M172">
+        <v>0</v>
+      </c>
+      <c r="N172">
+        <v>0</v>
+      </c>
+      <c r="O172">
+        <v>0</v>
+      </c>
+      <c r="P172">
+        <v>0</v>
+      </c>
+      <c r="Q172">
+        <v>0</v>
+      </c>
+      <c r="R172">
+        <v>0</v>
+      </c>
+      <c r="S172">
+        <v>0</v>
+      </c>
+      <c r="T172">
+        <v>0</v>
+      </c>
+      <c r="U172">
+        <v>0</v>
+      </c>
+      <c r="V172">
+        <v>1</v>
+      </c>
+      <c r="W172">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="173" spans="1:23">
+      <c r="A173" s="1"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D173">
+        <v>19</v>
+      </c>
+      <c r="E173">
+        <v>32</v>
+      </c>
+      <c r="F173">
+        <v>12</v>
+      </c>
+      <c r="G173">
+        <v>10</v>
+      </c>
+      <c r="H173">
+        <v>2</v>
+      </c>
+      <c r="I173">
+        <v>4</v>
+      </c>
+      <c r="J173">
+        <v>1</v>
+      </c>
+      <c r="K173">
+        <v>1</v>
+      </c>
+      <c r="L173">
+        <v>1</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+      <c r="N173">
+        <v>0</v>
+      </c>
+      <c r="O173">
+        <v>0</v>
+      </c>
+      <c r="P173">
+        <v>0</v>
+      </c>
+      <c r="Q173">
+        <v>0</v>
+      </c>
+      <c r="R173">
+        <v>0</v>
+      </c>
+      <c r="S173">
+        <v>0</v>
+      </c>
+      <c r="T173">
+        <v>0</v>
+      </c>
+      <c r="U173">
+        <v>0</v>
+      </c>
+      <c r="V173">
+        <v>0</v>
+      </c>
+      <c r="W173">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="174" spans="1:23">
+      <c r="A174" s="1"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D174">
+        <v>37</v>
+      </c>
+      <c r="E174">
+        <v>22</v>
+      </c>
+      <c r="F174">
+        <v>12</v>
+      </c>
+      <c r="G174">
+        <v>4</v>
+      </c>
+      <c r="H174">
+        <v>5</v>
+      </c>
+      <c r="I174">
+        <v>1</v>
+      </c>
+      <c r="J174">
+        <v>3</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+      <c r="M174">
+        <v>0</v>
+      </c>
+      <c r="N174">
+        <v>0</v>
+      </c>
+      <c r="O174">
+        <v>0</v>
+      </c>
+      <c r="P174">
+        <v>0</v>
+      </c>
+      <c r="Q174">
+        <v>0</v>
+      </c>
+      <c r="R174">
+        <v>0</v>
+      </c>
+      <c r="S174">
+        <v>0</v>
+      </c>
+      <c r="T174">
+        <v>0</v>
+      </c>
+      <c r="U174">
+        <v>1</v>
+      </c>
+      <c r="V174">
+        <v>0</v>
+      </c>
+      <c r="W174">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="175" spans="1:23">
+      <c r="A175" s="1"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D175">
+        <v>78</v>
+      </c>
+      <c r="E175">
+        <v>79</v>
+      </c>
+      <c r="F175">
+        <v>37</v>
+      </c>
+      <c r="G175">
+        <v>10</v>
+      </c>
+      <c r="H175">
+        <v>7</v>
+      </c>
+      <c r="I175">
+        <v>2</v>
+      </c>
+      <c r="J175">
+        <v>2</v>
+      </c>
+      <c r="K175">
+        <v>1</v>
+      </c>
+      <c r="L175">
+        <v>2</v>
+      </c>
+      <c r="M175">
+        <v>0</v>
+      </c>
+      <c r="N175">
+        <v>0</v>
+      </c>
+      <c r="O175">
+        <v>0</v>
+      </c>
+      <c r="P175">
+        <v>0</v>
+      </c>
+      <c r="Q175">
+        <v>0</v>
+      </c>
+      <c r="R175">
+        <v>0</v>
+      </c>
+      <c r="S175">
+        <v>0</v>
+      </c>
+      <c r="T175">
+        <v>0</v>
+      </c>
+      <c r="U175">
+        <v>0</v>
+      </c>
+      <c r="V175">
+        <v>0</v>
+      </c>
+      <c r="W175">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="176" spans="1:23">
+      <c r="A176" s="1"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D176">
+        <v>82</v>
+      </c>
+      <c r="E176">
+        <v>124</v>
+      </c>
+      <c r="F176">
+        <v>52</v>
+      </c>
+      <c r="G176">
+        <v>29</v>
+      </c>
+      <c r="H176">
+        <v>7</v>
+      </c>
+      <c r="I176">
+        <v>3</v>
+      </c>
+      <c r="J176">
+        <v>2</v>
+      </c>
+      <c r="K176">
+        <v>1</v>
+      </c>
+      <c r="L176">
+        <v>1</v>
+      </c>
+      <c r="M176">
+        <v>0</v>
+      </c>
+      <c r="N176">
+        <v>0</v>
+      </c>
+      <c r="O176">
+        <v>0</v>
+      </c>
+      <c r="P176">
+        <v>0</v>
+      </c>
+      <c r="Q176">
+        <v>0</v>
+      </c>
+      <c r="R176">
+        <v>0</v>
+      </c>
+      <c r="S176">
+        <v>0</v>
+      </c>
+      <c r="T176">
+        <v>0</v>
+      </c>
+      <c r="U176">
+        <v>0</v>
+      </c>
+      <c r="V176">
+        <v>0</v>
+      </c>
+      <c r="W176">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="177" spans="1:23">
+      <c r="A177" s="1"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D177">
+        <v>35</v>
+      </c>
+      <c r="E177">
+        <v>24</v>
+      </c>
+      <c r="F177">
+        <v>6</v>
+      </c>
+      <c r="G177">
+        <v>1</v>
+      </c>
+      <c r="H177">
+        <v>0</v>
+      </c>
+      <c r="I177">
+        <v>1</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>0</v>
+      </c>
+      <c r="L177">
+        <v>0</v>
+      </c>
+      <c r="M177">
+        <v>0</v>
+      </c>
+      <c r="N177">
+        <v>1</v>
+      </c>
+      <c r="O177">
+        <v>0</v>
+      </c>
+      <c r="P177">
+        <v>0</v>
+      </c>
+      <c r="Q177">
+        <v>0</v>
+      </c>
+      <c r="R177">
+        <v>0</v>
+      </c>
+      <c r="S177">
+        <v>0</v>
+      </c>
+      <c r="T177">
+        <v>0</v>
+      </c>
+      <c r="U177">
+        <v>0</v>
+      </c>
+      <c r="V177">
+        <v>0</v>
+      </c>
+      <c r="W177">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="178" spans="1:23">
+      <c r="A178" s="1"/>
+      <c r="B178" s="1"/>
+      <c r="C178" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D178">
+        <v>9</v>
+      </c>
+      <c r="E178">
+        <v>9</v>
+      </c>
+      <c r="F178">
+        <v>5</v>
+      </c>
+      <c r="G178">
+        <v>1</v>
+      </c>
+      <c r="H178">
+        <v>1</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>0</v>
+      </c>
+      <c r="L178">
+        <v>0</v>
+      </c>
+      <c r="M178">
+        <v>0</v>
+      </c>
+      <c r="N178">
+        <v>1</v>
+      </c>
+      <c r="O178">
+        <v>0</v>
+      </c>
+      <c r="P178">
+        <v>0</v>
+      </c>
+      <c r="Q178">
+        <v>0</v>
+      </c>
+      <c r="R178">
+        <v>0</v>
+      </c>
+      <c r="S178">
+        <v>0</v>
+      </c>
+      <c r="T178">
+        <v>0</v>
+      </c>
+      <c r="U178">
+        <v>0</v>
+      </c>
+      <c r="V178">
+        <v>0</v>
+      </c>
+      <c r="W178">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="179" spans="1:23">
+      <c r="A179" s="1"/>
+      <c r="B179" s="1"/>
+      <c r="C179" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D179">
+        <v>24</v>
+      </c>
+      <c r="E179">
+        <v>27</v>
+      </c>
+      <c r="F179">
+        <v>11</v>
+      </c>
+      <c r="G179">
+        <v>4</v>
+      </c>
+      <c r="H179">
+        <v>0</v>
+      </c>
+      <c r="I179">
+        <v>1</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>2</v>
+      </c>
+      <c r="L179">
+        <v>1</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
+      </c>
+      <c r="N179">
+        <v>0</v>
+      </c>
+      <c r="O179">
+        <v>0</v>
+      </c>
+      <c r="P179">
+        <v>0</v>
+      </c>
+      <c r="Q179">
+        <v>0</v>
+      </c>
+      <c r="R179">
+        <v>0</v>
+      </c>
+      <c r="S179">
+        <v>0</v>
+      </c>
+      <c r="T179">
+        <v>0</v>
+      </c>
+      <c r="U179">
+        <v>0</v>
+      </c>
+      <c r="V179">
+        <v>0</v>
+      </c>
+      <c r="W179">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="180" spans="1:23">
+      <c r="A180" s="1"/>
+      <c r="B180" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D180">
+        <v>2</v>
+      </c>
+      <c r="E180">
+        <v>1</v>
+      </c>
+      <c r="F180">
+        <v>1</v>
+      </c>
+      <c r="G180">
+        <v>2</v>
+      </c>
+      <c r="H180">
+        <v>2</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="L180">
+        <v>0</v>
+      </c>
+      <c r="M180">
+        <v>0</v>
+      </c>
+      <c r="N180">
+        <v>0</v>
+      </c>
+      <c r="O180">
+        <v>1</v>
+      </c>
+      <c r="P180">
+        <v>1</v>
+      </c>
+      <c r="Q180">
+        <v>0</v>
+      </c>
+      <c r="R180">
+        <v>1</v>
+      </c>
+      <c r="S180">
+        <v>0</v>
+      </c>
+      <c r="T180">
+        <v>0</v>
+      </c>
+      <c r="U180">
+        <v>0</v>
+      </c>
+      <c r="V180">
+        <v>0</v>
+      </c>
+      <c r="W180">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="1:23">
+      <c r="A181" s="1"/>
+      <c r="B181" s="1"/>
+      <c r="C181" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D181">
+        <v>10</v>
+      </c>
+      <c r="E181">
+        <v>32</v>
+      </c>
+      <c r="F181">
+        <v>27</v>
+      </c>
+      <c r="G181">
+        <v>24</v>
+      </c>
+      <c r="H181">
+        <v>9</v>
+      </c>
+      <c r="I181">
+        <v>10</v>
+      </c>
+      <c r="J181">
+        <v>4</v>
+      </c>
+      <c r="K181">
+        <v>1</v>
+      </c>
+      <c r="L181">
+        <v>1</v>
+      </c>
+      <c r="M181">
+        <v>0</v>
+      </c>
+      <c r="N181">
+        <v>1</v>
+      </c>
+      <c r="O181">
+        <v>1</v>
+      </c>
+      <c r="P181">
+        <v>0</v>
+      </c>
+      <c r="Q181">
+        <v>0</v>
+      </c>
+      <c r="R181">
+        <v>0</v>
+      </c>
+      <c r="S181">
+        <v>0</v>
+      </c>
+      <c r="T181">
+        <v>0</v>
+      </c>
+      <c r="U181">
+        <v>0</v>
+      </c>
+      <c r="V181">
+        <v>0</v>
+      </c>
+      <c r="W181">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="182" spans="1:23">
+      <c r="A182" s="1"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D182">
+        <v>4</v>
+      </c>
+      <c r="E182">
+        <v>12</v>
+      </c>
+      <c r="F182">
+        <v>4</v>
+      </c>
+      <c r="G182">
+        <v>5</v>
+      </c>
+      <c r="H182">
+        <v>6</v>
+      </c>
+      <c r="I182">
+        <v>1</v>
+      </c>
+      <c r="J182">
+        <v>1</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>1</v>
+      </c>
+      <c r="M182">
+        <v>0</v>
+      </c>
+      <c r="N182">
+        <v>0</v>
+      </c>
+      <c r="O182">
+        <v>0</v>
+      </c>
+      <c r="P182">
+        <v>0</v>
+      </c>
+      <c r="Q182">
+        <v>0</v>
+      </c>
+      <c r="R182">
+        <v>0</v>
+      </c>
+      <c r="S182">
+        <v>1</v>
+      </c>
+      <c r="T182">
+        <v>0</v>
+      </c>
+      <c r="U182">
+        <v>0</v>
+      </c>
+      <c r="V182">
+        <v>0</v>
+      </c>
+      <c r="W182">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="183" spans="1:23">
+      <c r="A183" s="1"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D183">
+        <v>21</v>
+      </c>
+      <c r="E183">
+        <v>44</v>
+      </c>
+      <c r="F183">
+        <v>16</v>
+      </c>
+      <c r="G183">
+        <v>16</v>
+      </c>
+      <c r="H183">
+        <v>5</v>
+      </c>
+      <c r="I183">
+        <v>2</v>
+      </c>
+      <c r="J183">
+        <v>2</v>
+      </c>
+      <c r="K183">
+        <v>4</v>
+      </c>
+      <c r="L183">
+        <v>1</v>
+      </c>
+      <c r="M183">
+        <v>2</v>
+      </c>
+      <c r="N183">
+        <v>0</v>
+      </c>
+      <c r="O183">
+        <v>2</v>
+      </c>
+      <c r="P183">
+        <v>0</v>
+      </c>
+      <c r="Q183">
+        <v>0</v>
+      </c>
+      <c r="R183">
+        <v>0</v>
+      </c>
+      <c r="S183">
+        <v>0</v>
+      </c>
+      <c r="T183">
+        <v>1</v>
+      </c>
+      <c r="U183">
+        <v>0</v>
+      </c>
+      <c r="V183">
+        <v>0</v>
+      </c>
+      <c r="W183">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="184" spans="1:23">
+      <c r="A184" s="1"/>
+      <c r="B184" s="1"/>
+      <c r="C184" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D184">
+        <v>9</v>
+      </c>
+      <c r="E184">
+        <v>32</v>
+      </c>
+      <c r="F184">
+        <v>21</v>
+      </c>
+      <c r="G184">
+        <v>12</v>
+      </c>
+      <c r="H184">
+        <v>4</v>
+      </c>
+      <c r="I184">
+        <v>3</v>
+      </c>
+      <c r="J184">
+        <v>2</v>
+      </c>
+      <c r="K184">
+        <v>2</v>
+      </c>
+      <c r="L184">
+        <v>2</v>
+      </c>
+      <c r="M184">
+        <v>0</v>
+      </c>
+      <c r="N184">
+        <v>0</v>
+      </c>
+      <c r="O184">
+        <v>0</v>
+      </c>
+      <c r="P184">
+        <v>1</v>
+      </c>
+      <c r="Q184">
+        <v>0</v>
+      </c>
+      <c r="R184">
+        <v>0</v>
+      </c>
+      <c r="S184">
+        <v>0</v>
+      </c>
+      <c r="T184">
+        <v>0</v>
+      </c>
+      <c r="U184">
+        <v>0</v>
+      </c>
+      <c r="V184">
+        <v>0</v>
+      </c>
+      <c r="W184">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="185" spans="1:23">
+      <c r="A185" s="1"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D185">
+        <v>2</v>
+      </c>
+      <c r="E185">
+        <v>3</v>
+      </c>
+      <c r="F185">
+        <v>4</v>
+      </c>
+      <c r="G185">
+        <v>0</v>
+      </c>
+      <c r="H185">
+        <v>2</v>
+      </c>
+      <c r="I185">
+        <v>1</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>0</v>
+      </c>
+      <c r="M185">
+        <v>0</v>
+      </c>
+      <c r="N185">
+        <v>0</v>
+      </c>
+      <c r="O185">
+        <v>0</v>
+      </c>
+      <c r="P185">
+        <v>0</v>
+      </c>
+      <c r="Q185">
+        <v>0</v>
+      </c>
+      <c r="R185">
+        <v>0</v>
+      </c>
+      <c r="S185">
+        <v>0</v>
+      </c>
+      <c r="T185">
+        <v>0</v>
+      </c>
+      <c r="U185">
+        <v>0</v>
+      </c>
+      <c r="V185">
+        <v>0</v>
+      </c>
+      <c r="W185">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="186" spans="1:23">
+      <c r="A186" s="1"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D186">
+        <v>3</v>
+      </c>
+      <c r="E186">
+        <v>8</v>
+      </c>
+      <c r="F186">
+        <v>4</v>
+      </c>
+      <c r="G186">
+        <v>2</v>
+      </c>
+      <c r="H186">
+        <v>1</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
+      </c>
+      <c r="M186">
+        <v>0</v>
+      </c>
+      <c r="N186">
+        <v>0</v>
+      </c>
+      <c r="O186">
+        <v>0</v>
+      </c>
+      <c r="P186">
+        <v>0</v>
+      </c>
+      <c r="Q186">
+        <v>0</v>
+      </c>
+      <c r="R186">
+        <v>0</v>
+      </c>
+      <c r="S186">
+        <v>0</v>
+      </c>
+      <c r="T186">
+        <v>0</v>
+      </c>
+      <c r="U186">
+        <v>0</v>
+      </c>
+      <c r="V186">
+        <v>0</v>
+      </c>
+      <c r="W186">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="187" spans="1:23">
+      <c r="A187" s="1"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D187">
+        <v>8</v>
+      </c>
+      <c r="E187">
+        <v>11</v>
+      </c>
+      <c r="F187">
+        <v>2</v>
+      </c>
+      <c r="G187">
+        <v>5</v>
+      </c>
+      <c r="H187">
+        <v>1</v>
+      </c>
+      <c r="I187">
+        <v>2</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>1</v>
+      </c>
+      <c r="L187">
+        <v>1</v>
+      </c>
+      <c r="M187">
+        <v>0</v>
+      </c>
+      <c r="N187">
+        <v>0</v>
+      </c>
+      <c r="O187">
+        <v>0</v>
+      </c>
+      <c r="P187">
+        <v>0</v>
+      </c>
+      <c r="Q187">
+        <v>0</v>
+      </c>
+      <c r="R187">
+        <v>0</v>
+      </c>
+      <c r="S187">
+        <v>0</v>
+      </c>
+      <c r="T187">
+        <v>0</v>
+      </c>
+      <c r="U187">
+        <v>0</v>
+      </c>
+      <c r="V187">
+        <v>0</v>
+      </c>
+      <c r="W187">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="188" spans="1:23">
+      <c r="A188" s="1"/>
+      <c r="B188" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D188">
+        <v>3</v>
+      </c>
+      <c r="E188">
+        <v>5</v>
+      </c>
+      <c r="F188">
+        <v>5</v>
+      </c>
+      <c r="G188">
+        <v>3</v>
+      </c>
+      <c r="H188">
+        <v>2</v>
+      </c>
+      <c r="I188">
+        <v>2</v>
+      </c>
+      <c r="J188">
+        <v>3</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>0</v>
+      </c>
+      <c r="M188">
+        <v>0</v>
+      </c>
+      <c r="N188">
+        <v>0</v>
+      </c>
+      <c r="O188">
+        <v>0</v>
+      </c>
+      <c r="P188">
+        <v>0</v>
+      </c>
+      <c r="Q188">
+        <v>0</v>
+      </c>
+      <c r="R188">
+        <v>0</v>
+      </c>
+      <c r="S188">
+        <v>0</v>
+      </c>
+      <c r="T188">
+        <v>0</v>
+      </c>
+      <c r="U188">
+        <v>0</v>
+      </c>
+      <c r="V188">
+        <v>0</v>
+      </c>
+      <c r="W188">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="189" spans="1:23">
+      <c r="A189" s="1"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D189">
+        <v>47</v>
+      </c>
+      <c r="E189">
+        <v>109</v>
+      </c>
+      <c r="F189">
+        <v>178</v>
+      </c>
+      <c r="G189">
+        <v>151</v>
+      </c>
+      <c r="H189">
+        <v>97</v>
+      </c>
+      <c r="I189">
+        <v>78</v>
+      </c>
+      <c r="J189">
+        <v>32</v>
+      </c>
+      <c r="K189">
+        <v>22</v>
+      </c>
+      <c r="L189">
+        <v>9</v>
+      </c>
+      <c r="M189">
+        <v>7</v>
+      </c>
+      <c r="N189">
+        <v>2</v>
+      </c>
+      <c r="O189">
+        <v>1</v>
+      </c>
+      <c r="P189">
+        <v>3</v>
+      </c>
+      <c r="Q189">
+        <v>1</v>
+      </c>
+      <c r="R189">
+        <v>1</v>
+      </c>
+      <c r="S189">
+        <v>0</v>
+      </c>
+      <c r="T189">
+        <v>0</v>
+      </c>
+      <c r="U189">
+        <v>0</v>
+      </c>
+      <c r="V189">
+        <v>0</v>
+      </c>
+      <c r="W189">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="190" spans="1:23">
+      <c r="A190" s="1"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D190">
+        <v>14</v>
+      </c>
+      <c r="E190">
+        <v>46</v>
+      </c>
+      <c r="F190">
+        <v>17</v>
+      </c>
+      <c r="G190">
+        <v>12</v>
+      </c>
+      <c r="H190">
+        <v>11</v>
+      </c>
+      <c r="I190">
+        <v>6</v>
+      </c>
+      <c r="J190">
+        <v>4</v>
+      </c>
+      <c r="K190">
+        <v>3</v>
+      </c>
+      <c r="L190">
+        <v>0</v>
+      </c>
+      <c r="M190">
+        <v>0</v>
+      </c>
+      <c r="N190">
+        <v>0</v>
+      </c>
+      <c r="O190">
+        <v>0</v>
+      </c>
+      <c r="P190">
+        <v>0</v>
+      </c>
+      <c r="Q190">
+        <v>0</v>
+      </c>
+      <c r="R190">
+        <v>0</v>
+      </c>
+      <c r="S190">
+        <v>0</v>
+      </c>
+      <c r="T190">
+        <v>0</v>
+      </c>
+      <c r="U190">
+        <v>0</v>
+      </c>
+      <c r="V190">
+        <v>0</v>
+      </c>
+      <c r="W190">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="191" spans="1:23">
+      <c r="A191" s="1"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D191">
+        <v>22</v>
+      </c>
+      <c r="E191">
+        <v>52</v>
+      </c>
+      <c r="F191">
+        <v>47</v>
+      </c>
+      <c r="G191">
+        <v>28</v>
+      </c>
+      <c r="H191">
+        <v>12</v>
+      </c>
+      <c r="I191">
+        <v>12</v>
+      </c>
+      <c r="J191">
+        <v>7</v>
+      </c>
+      <c r="K191">
+        <v>3</v>
+      </c>
+      <c r="L191">
+        <v>4</v>
+      </c>
+      <c r="M191">
+        <v>1</v>
+      </c>
+      <c r="N191">
+        <v>1</v>
+      </c>
+      <c r="O191">
+        <v>0</v>
+      </c>
+      <c r="P191">
+        <v>0</v>
+      </c>
+      <c r="Q191">
+        <v>2</v>
+      </c>
+      <c r="R191">
+        <v>0</v>
+      </c>
+      <c r="S191">
+        <v>0</v>
+      </c>
+      <c r="T191">
+        <v>0</v>
+      </c>
+      <c r="U191">
+        <v>0</v>
+      </c>
+      <c r="V191">
+        <v>0</v>
+      </c>
+      <c r="W191">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="192" spans="1:23">
+      <c r="A192" s="1"/>
+      <c r="B192" s="1"/>
+      <c r="C192" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D192">
+        <v>0</v>
+      </c>
+      <c r="E192">
+        <v>0</v>
+      </c>
+      <c r="F192">
+        <v>0</v>
+      </c>
+      <c r="G192">
+        <v>0</v>
+      </c>
+      <c r="H192">
+        <v>0</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <v>0</v>
+      </c>
+      <c r="M192">
+        <v>0</v>
+      </c>
+      <c r="N192">
+        <v>0</v>
+      </c>
+      <c r="O192">
+        <v>0</v>
+      </c>
+      <c r="P192">
+        <v>0</v>
+      </c>
+      <c r="Q192">
+        <v>0</v>
+      </c>
+      <c r="R192">
+        <v>0</v>
+      </c>
+      <c r="S192">
+        <v>0</v>
+      </c>
+      <c r="T192">
+        <v>0</v>
+      </c>
+      <c r="U192">
+        <v>0</v>
+      </c>
+      <c r="V192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:23">
+      <c r="A193" s="1"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D193">
+        <v>8</v>
+      </c>
+      <c r="E193">
+        <v>11</v>
+      </c>
+      <c r="F193">
+        <v>5</v>
+      </c>
+      <c r="G193">
+        <v>4</v>
+      </c>
+      <c r="H193">
+        <v>2</v>
+      </c>
+      <c r="I193">
+        <v>2</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>0</v>
+      </c>
+      <c r="L193">
+        <v>0</v>
+      </c>
+      <c r="M193">
+        <v>1</v>
+      </c>
+      <c r="N193">
+        <v>0</v>
+      </c>
+      <c r="O193">
+        <v>0</v>
+      </c>
+      <c r="P193">
+        <v>0</v>
+      </c>
+      <c r="Q193">
+        <v>0</v>
+      </c>
+      <c r="R193">
+        <v>0</v>
+      </c>
+      <c r="S193">
+        <v>0</v>
+      </c>
+      <c r="T193">
+        <v>0</v>
+      </c>
+      <c r="U193">
+        <v>0</v>
+      </c>
+      <c r="V193">
+        <v>0</v>
+      </c>
+      <c r="W193">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="194" spans="1:23">
+      <c r="A194" s="1"/>
+      <c r="B194" s="1"/>
+      <c r="C194" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D194">
+        <v>17</v>
+      </c>
+      <c r="E194">
+        <v>11</v>
+      </c>
+      <c r="F194">
+        <v>9</v>
+      </c>
+      <c r="G194">
+        <v>7</v>
+      </c>
+      <c r="H194">
+        <v>3</v>
+      </c>
+      <c r="I194">
+        <v>2</v>
+      </c>
+      <c r="J194">
+        <v>1</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>1</v>
+      </c>
+      <c r="M194">
+        <v>0</v>
+      </c>
+      <c r="N194">
+        <v>0</v>
+      </c>
+      <c r="O194">
+        <v>0</v>
+      </c>
+      <c r="P194">
+        <v>0</v>
+      </c>
+      <c r="Q194">
+        <v>0</v>
+      </c>
+      <c r="R194">
+        <v>0</v>
+      </c>
+      <c r="S194">
+        <v>0</v>
+      </c>
+      <c r="T194">
+        <v>0</v>
+      </c>
+      <c r="U194">
+        <v>0</v>
+      </c>
+      <c r="V194">
+        <v>0</v>
+      </c>
+      <c r="W194">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="195" spans="1:23">
+      <c r="A195" s="1"/>
+      <c r="B195" s="1"/>
+      <c r="C195" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D195">
+        <v>9</v>
+      </c>
+      <c r="E195">
+        <v>24</v>
+      </c>
+      <c r="F195">
+        <v>22</v>
+      </c>
+      <c r="G195">
+        <v>17</v>
+      </c>
+      <c r="H195">
+        <v>5</v>
+      </c>
+      <c r="I195">
+        <v>6</v>
+      </c>
+      <c r="J195">
+        <v>3</v>
+      </c>
+      <c r="K195">
+        <v>4</v>
+      </c>
+      <c r="L195">
+        <v>2</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+      <c r="N195">
+        <v>0</v>
+      </c>
+      <c r="O195">
+        <v>0</v>
+      </c>
+      <c r="P195">
+        <v>0</v>
+      </c>
+      <c r="Q195">
+        <v>0</v>
+      </c>
+      <c r="R195">
+        <v>0</v>
+      </c>
+      <c r="S195">
+        <v>0</v>
+      </c>
+      <c r="T195">
+        <v>0</v>
+      </c>
+      <c r="U195">
+        <v>0</v>
+      </c>
+      <c r="V195">
+        <v>0</v>
+      </c>
+      <c r="W195">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="196" spans="1:23">
+      <c r="A196" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D196">
+        <v>6</v>
+      </c>
+      <c r="E196">
+        <v>5</v>
+      </c>
+      <c r="F196">
+        <v>1</v>
+      </c>
+      <c r="G196">
+        <v>2</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="J196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>0</v>
+      </c>
+      <c r="L196">
+        <v>0</v>
+      </c>
+      <c r="M196">
+        <v>0</v>
+      </c>
+      <c r="N196">
+        <v>0</v>
+      </c>
+      <c r="O196">
+        <v>0</v>
+      </c>
+      <c r="P196">
+        <v>0</v>
+      </c>
+      <c r="Q196">
+        <v>0</v>
+      </c>
+      <c r="R196">
+        <v>0</v>
+      </c>
+      <c r="S196">
+        <v>0</v>
+      </c>
+      <c r="T196">
+        <v>0</v>
+      </c>
+      <c r="U196">
+        <v>0</v>
+      </c>
+      <c r="V196">
+        <v>0</v>
+      </c>
+      <c r="W196">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="197" spans="1:23">
+      <c r="A197" s="1"/>
+      <c r="B197" s="1"/>
+      <c r="C197" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D197">
+        <v>13</v>
+      </c>
+      <c r="E197">
+        <v>14</v>
+      </c>
+      <c r="F197">
+        <v>10</v>
+      </c>
+      <c r="G197">
+        <v>4</v>
+      </c>
+      <c r="H197">
+        <v>2</v>
+      </c>
+      <c r="I197">
+        <v>4</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>0</v>
+      </c>
+      <c r="L197">
+        <v>1</v>
+      </c>
+      <c r="M197">
+        <v>0</v>
+      </c>
+      <c r="N197">
+        <v>0</v>
+      </c>
+      <c r="O197">
+        <v>0</v>
+      </c>
+      <c r="P197">
+        <v>0</v>
+      </c>
+      <c r="Q197">
+        <v>0</v>
+      </c>
+      <c r="R197">
+        <v>0</v>
+      </c>
+      <c r="S197">
+        <v>0</v>
+      </c>
+      <c r="T197">
+        <v>0</v>
+      </c>
+      <c r="U197">
+        <v>0</v>
+      </c>
+      <c r="V197">
+        <v>0</v>
+      </c>
+      <c r="W197">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="198" spans="1:23">
+      <c r="A198" s="1"/>
+      <c r="B198" s="1"/>
+      <c r="C198" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D198">
+        <v>60</v>
+      </c>
+      <c r="E198">
+        <v>27</v>
+      </c>
+      <c r="F198">
+        <v>7</v>
+      </c>
+      <c r="G198">
+        <v>1</v>
+      </c>
+      <c r="H198">
+        <v>1</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="J198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>0</v>
+      </c>
+      <c r="L198">
+        <v>0</v>
+      </c>
+      <c r="M198">
+        <v>0</v>
+      </c>
+      <c r="N198">
+        <v>0</v>
+      </c>
+      <c r="O198">
+        <v>0</v>
+      </c>
+      <c r="P198">
+        <v>0</v>
+      </c>
+      <c r="Q198">
+        <v>0</v>
+      </c>
+      <c r="R198">
+        <v>0</v>
+      </c>
+      <c r="S198">
+        <v>0</v>
+      </c>
+      <c r="T198">
+        <v>0</v>
+      </c>
+      <c r="U198">
+        <v>0</v>
+      </c>
+      <c r="V198">
+        <v>0</v>
+      </c>
+      <c r="W198">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="199" spans="1:23">
+      <c r="A199" s="1"/>
+      <c r="B199" s="1"/>
+      <c r="C199" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="E199">
+        <v>0</v>
+      </c>
+      <c r="F199">
+        <v>0</v>
+      </c>
+      <c r="G199">
+        <v>0</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+      <c r="M199">
+        <v>0</v>
+      </c>
+      <c r="N199">
+        <v>0</v>
+      </c>
+      <c r="O199">
+        <v>0</v>
+      </c>
+      <c r="P199">
+        <v>0</v>
+      </c>
+      <c r="Q199">
+        <v>0</v>
+      </c>
+      <c r="R199">
+        <v>0</v>
+      </c>
+      <c r="S199">
+        <v>0</v>
+      </c>
+      <c r="T199">
+        <v>0</v>
+      </c>
+      <c r="U199">
+        <v>0</v>
+      </c>
+      <c r="V199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:23">
+      <c r="A200" s="1"/>
+      <c r="B200" s="1"/>
+      <c r="C200" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D200">
+        <v>92</v>
+      </c>
+      <c r="E200">
+        <v>88</v>
+      </c>
+      <c r="F200">
+        <v>25</v>
+      </c>
+      <c r="G200">
+        <v>5</v>
+      </c>
+      <c r="H200">
+        <v>1</v>
+      </c>
+      <c r="I200">
+        <v>1</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>0</v>
+      </c>
+      <c r="L200">
+        <v>0</v>
+      </c>
+      <c r="M200">
+        <v>0</v>
+      </c>
+      <c r="N200">
+        <v>0</v>
+      </c>
+      <c r="O200">
+        <v>0</v>
+      </c>
+      <c r="P200">
+        <v>0</v>
+      </c>
+      <c r="Q200">
+        <v>0</v>
+      </c>
+      <c r="R200">
+        <v>0</v>
+      </c>
+      <c r="S200">
+        <v>0</v>
+      </c>
+      <c r="T200">
+        <v>0</v>
+      </c>
+      <c r="U200">
+        <v>0</v>
+      </c>
+      <c r="V200">
+        <v>0</v>
+      </c>
+      <c r="W200">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="201" spans="1:23">
+      <c r="A201" s="1"/>
+      <c r="B201" s="1"/>
+      <c r="C201" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D201">
+        <v>166</v>
+      </c>
+      <c r="E201">
+        <v>141</v>
+      </c>
+      <c r="F201">
+        <v>28</v>
+      </c>
+      <c r="G201">
+        <v>3</v>
+      </c>
+      <c r="H201">
+        <v>0</v>
+      </c>
+      <c r="I201">
+        <v>2</v>
+      </c>
+      <c r="J201">
+        <v>2</v>
+      </c>
+      <c r="K201">
+        <v>0</v>
+      </c>
+      <c r="L201">
+        <v>0</v>
+      </c>
+      <c r="M201">
+        <v>0</v>
+      </c>
+      <c r="N201">
+        <v>0</v>
+      </c>
+      <c r="O201">
+        <v>0</v>
+      </c>
+      <c r="P201">
+        <v>0</v>
+      </c>
+      <c r="Q201">
+        <v>0</v>
+      </c>
+      <c r="R201">
+        <v>0</v>
+      </c>
+      <c r="S201">
+        <v>0</v>
+      </c>
+      <c r="T201">
+        <v>0</v>
+      </c>
+      <c r="U201">
+        <v>0</v>
+      </c>
+      <c r="V201">
+        <v>0</v>
+      </c>
+      <c r="W201">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="202" spans="1:23">
+      <c r="A202" s="1"/>
+      <c r="B202" s="1"/>
+      <c r="C202" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D202">
+        <v>19</v>
+      </c>
+      <c r="E202">
+        <v>14</v>
+      </c>
+      <c r="F202">
+        <v>5</v>
+      </c>
+      <c r="G202">
+        <v>1</v>
+      </c>
+      <c r="H202">
+        <v>2</v>
+      </c>
+      <c r="I202">
+        <v>1</v>
+      </c>
+      <c r="J202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>0</v>
+      </c>
+      <c r="L202">
+        <v>0</v>
+      </c>
+      <c r="M202">
+        <v>0</v>
+      </c>
+      <c r="N202">
+        <v>0</v>
+      </c>
+      <c r="O202">
+        <v>0</v>
+      </c>
+      <c r="P202">
+        <v>0</v>
+      </c>
+      <c r="Q202">
+        <v>0</v>
+      </c>
+      <c r="R202">
+        <v>0</v>
+      </c>
+      <c r="S202">
+        <v>0</v>
+      </c>
+      <c r="T202">
+        <v>0</v>
+      </c>
+      <c r="U202">
+        <v>0</v>
+      </c>
+      <c r="V202">
+        <v>0</v>
+      </c>
+      <c r="W202">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="203" spans="1:23">
+      <c r="A203" s="1"/>
+      <c r="B203" s="1"/>
+      <c r="C203" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D203">
+        <v>85</v>
+      </c>
+      <c r="E203">
+        <v>66</v>
+      </c>
+      <c r="F203">
+        <v>14</v>
+      </c>
+      <c r="G203">
+        <v>1</v>
+      </c>
+      <c r="H203">
+        <v>2</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="L203">
+        <v>0</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
+      </c>
+      <c r="N203">
+        <v>0</v>
+      </c>
+      <c r="O203">
+        <v>0</v>
+      </c>
+      <c r="P203">
+        <v>0</v>
+      </c>
+      <c r="Q203">
+        <v>0</v>
+      </c>
+      <c r="R203">
+        <v>0</v>
+      </c>
+      <c r="S203">
+        <v>0</v>
+      </c>
+      <c r="T203">
+        <v>0</v>
+      </c>
+      <c r="U203">
+        <v>0</v>
+      </c>
+      <c r="V203">
+        <v>0</v>
+      </c>
+      <c r="W203">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="204" spans="1:23">
+      <c r="A204" s="1"/>
+      <c r="B204" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D204">
+        <v>0</v>
+      </c>
+      <c r="E204">
+        <v>0</v>
+      </c>
+      <c r="F204">
+        <v>1</v>
+      </c>
+      <c r="G204">
+        <v>0</v>
+      </c>
+      <c r="H204">
+        <v>0</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>1</v>
+      </c>
+      <c r="L204">
+        <v>0</v>
+      </c>
+      <c r="M204">
+        <v>0</v>
+      </c>
+      <c r="N204">
+        <v>0</v>
+      </c>
+      <c r="O204">
+        <v>0</v>
+      </c>
+      <c r="P204">
+        <v>0</v>
+      </c>
+      <c r="Q204">
+        <v>0</v>
+      </c>
+      <c r="R204">
+        <v>0</v>
+      </c>
+      <c r="S204">
+        <v>0</v>
+      </c>
+      <c r="T204">
+        <v>0</v>
+      </c>
+      <c r="U204">
+        <v>0</v>
+      </c>
+      <c r="V204">
+        <v>0</v>
+      </c>
+      <c r="W204">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:23">
+      <c r="A205" s="1"/>
+      <c r="B205" s="1"/>
+      <c r="C205" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D205">
+        <v>8</v>
+      </c>
+      <c r="E205">
+        <v>23</v>
+      </c>
+      <c r="F205">
+        <v>24</v>
+      </c>
+      <c r="G205">
+        <v>13</v>
+      </c>
+      <c r="H205">
+        <v>8</v>
+      </c>
+      <c r="I205">
+        <v>5</v>
+      </c>
+      <c r="J205">
+        <v>3</v>
+      </c>
+      <c r="K205">
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="M205">
+        <v>0</v>
+      </c>
+      <c r="N205">
+        <v>0</v>
+      </c>
+      <c r="O205">
+        <v>0</v>
+      </c>
+      <c r="P205">
+        <v>0</v>
+      </c>
+      <c r="Q205">
+        <v>0</v>
+      </c>
+      <c r="R205">
+        <v>0</v>
+      </c>
+      <c r="S205">
+        <v>0</v>
+      </c>
+      <c r="T205">
+        <v>0</v>
+      </c>
+      <c r="U205">
+        <v>0</v>
+      </c>
+      <c r="V205">
+        <v>0</v>
+      </c>
+      <c r="W205">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="206" spans="1:23">
+      <c r="A206" s="1"/>
+      <c r="B206" s="1"/>
+      <c r="C206" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D206">
+        <v>7</v>
+      </c>
+      <c r="E206">
+        <v>9</v>
+      </c>
+      <c r="F206">
+        <v>5</v>
+      </c>
+      <c r="G206">
+        <v>2</v>
+      </c>
+      <c r="H206">
+        <v>2</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>0</v>
+      </c>
+      <c r="L206">
+        <v>0</v>
+      </c>
+      <c r="M206">
+        <v>0</v>
+      </c>
+      <c r="N206">
+        <v>0</v>
+      </c>
+      <c r="O206">
+        <v>0</v>
+      </c>
+      <c r="P206">
+        <v>0</v>
+      </c>
+      <c r="Q206">
+        <v>0</v>
+      </c>
+      <c r="R206">
+        <v>0</v>
+      </c>
+      <c r="S206">
+        <v>0</v>
+      </c>
+      <c r="T206">
+        <v>0</v>
+      </c>
+      <c r="U206">
+        <v>0</v>
+      </c>
+      <c r="V206">
+        <v>0</v>
+      </c>
+      <c r="W206">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="207" spans="1:23">
+      <c r="A207" s="1"/>
+      <c r="B207" s="1"/>
+      <c r="C207" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D207">
+        <v>60</v>
+      </c>
+      <c r="E207">
+        <v>43</v>
+      </c>
+      <c r="F207">
+        <v>16</v>
+      </c>
+      <c r="G207">
+        <v>5</v>
+      </c>
+      <c r="H207">
+        <v>1</v>
+      </c>
+      <c r="I207">
+        <v>1</v>
+      </c>
+      <c r="J207">
+        <v>1</v>
+      </c>
+      <c r="K207">
+        <v>0</v>
+      </c>
+      <c r="L207">
+        <v>1</v>
+      </c>
+      <c r="M207">
+        <v>0</v>
+      </c>
+      <c r="N207">
+        <v>0</v>
+      </c>
+      <c r="O207">
+        <v>0</v>
+      </c>
+      <c r="P207">
+        <v>0</v>
+      </c>
+      <c r="Q207">
+        <v>0</v>
+      </c>
+      <c r="R207">
+        <v>0</v>
+      </c>
+      <c r="S207">
+        <v>0</v>
+      </c>
+      <c r="T207">
+        <v>0</v>
+      </c>
+      <c r="U207">
+        <v>0</v>
+      </c>
+      <c r="V207">
+        <v>0</v>
+      </c>
+      <c r="W207">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="208" spans="1:23">
+      <c r="A208" s="1"/>
+      <c r="B208" s="1"/>
+      <c r="C208" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D208">
+        <v>1</v>
+      </c>
+      <c r="E208">
+        <v>12</v>
+      </c>
+      <c r="F208">
+        <v>7</v>
+      </c>
+      <c r="G208">
+        <v>10</v>
+      </c>
+      <c r="H208">
+        <v>4</v>
+      </c>
+      <c r="I208">
+        <v>1</v>
+      </c>
+      <c r="J208">
+        <v>2</v>
+      </c>
+      <c r="K208">
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <v>0</v>
+      </c>
+      <c r="M208">
+        <v>0</v>
+      </c>
+      <c r="N208">
+        <v>0</v>
+      </c>
+      <c r="O208">
+        <v>0</v>
+      </c>
+      <c r="P208">
+        <v>0</v>
+      </c>
+      <c r="Q208">
+        <v>0</v>
+      </c>
+      <c r="R208">
+        <v>0</v>
+      </c>
+      <c r="S208">
+        <v>0</v>
+      </c>
+      <c r="T208">
+        <v>0</v>
+      </c>
+      <c r="U208">
+        <v>0</v>
+      </c>
+      <c r="V208">
+        <v>0</v>
+      </c>
+      <c r="W208">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="209" spans="1:23">
+      <c r="A209" s="1"/>
+      <c r="B209" s="1"/>
+      <c r="C209" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D209">
+        <v>1</v>
+      </c>
+      <c r="E209">
+        <v>3</v>
+      </c>
+      <c r="F209">
+        <v>0</v>
+      </c>
+      <c r="G209">
+        <v>0</v>
+      </c>
+      <c r="H209">
+        <v>0</v>
+      </c>
+      <c r="I209">
+        <v>0</v>
+      </c>
+      <c r="J209">
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <v>0</v>
+      </c>
+      <c r="L209">
+        <v>0</v>
+      </c>
+      <c r="M209">
+        <v>0</v>
+      </c>
+      <c r="N209">
+        <v>0</v>
+      </c>
+      <c r="O209">
+        <v>0</v>
+      </c>
+      <c r="P209">
+        <v>0</v>
+      </c>
+      <c r="Q209">
+        <v>0</v>
+      </c>
+      <c r="R209">
+        <v>0</v>
+      </c>
+      <c r="S209">
+        <v>0</v>
+      </c>
+      <c r="T209">
+        <v>0</v>
+      </c>
+      <c r="U209">
+        <v>0</v>
+      </c>
+      <c r="V209">
+        <v>0</v>
+      </c>
+      <c r="W209">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:23">
+      <c r="A210" s="1"/>
+      <c r="B210" s="1"/>
+      <c r="C210" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D210">
+        <v>5</v>
+      </c>
+      <c r="E210">
+        <v>5</v>
+      </c>
+      <c r="F210">
+        <v>1</v>
+      </c>
+      <c r="G210">
+        <v>1</v>
+      </c>
+      <c r="H210">
+        <v>2</v>
+      </c>
+      <c r="I210">
+        <v>1</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <v>0</v>
+      </c>
+      <c r="M210">
+        <v>0</v>
+      </c>
+      <c r="N210">
+        <v>0</v>
+      </c>
+      <c r="O210">
+        <v>0</v>
+      </c>
+      <c r="P210">
+        <v>0</v>
+      </c>
+      <c r="Q210">
+        <v>0</v>
+      </c>
+      <c r="R210">
+        <v>0</v>
+      </c>
+      <c r="S210">
+        <v>0</v>
+      </c>
+      <c r="T210">
+        <v>0</v>
+      </c>
+      <c r="U210">
+        <v>0</v>
+      </c>
+      <c r="V210">
+        <v>0</v>
+      </c>
+      <c r="W210">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="211" spans="1:23">
+      <c r="A211" s="1"/>
+      <c r="B211" s="1"/>
+      <c r="C211" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D211">
+        <v>8</v>
+      </c>
+      <c r="E211">
+        <v>9</v>
+      </c>
+      <c r="F211">
+        <v>1</v>
+      </c>
+      <c r="G211">
+        <v>1</v>
+      </c>
+      <c r="H211">
+        <v>0</v>
+      </c>
+      <c r="I211">
+        <v>2</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>0</v>
+      </c>
+      <c r="L211">
+        <v>0</v>
+      </c>
+      <c r="M211">
+        <v>0</v>
+      </c>
+      <c r="N211">
+        <v>0</v>
+      </c>
+      <c r="O211">
+        <v>0</v>
+      </c>
+      <c r="P211">
+        <v>0</v>
+      </c>
+      <c r="Q211">
+        <v>0</v>
+      </c>
+      <c r="R211">
+        <v>0</v>
+      </c>
+      <c r="S211">
+        <v>0</v>
+      </c>
+      <c r="T211">
+        <v>0</v>
+      </c>
+      <c r="U211">
+        <v>0</v>
+      </c>
+      <c r="V211">
+        <v>0</v>
+      </c>
+      <c r="W211">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="212" spans="1:23">
+      <c r="A212" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B212" s="1"/>
+      <c r="C212" s="1"/>
+      <c r="D212">
         <v>1965</v>
       </c>
-      <c r="C146">
+      <c r="E212">
         <v>2113</v>
       </c>
-      <c r="D146">
+      <c r="F212">
         <v>1012</v>
       </c>
-      <c r="E146">
+      <c r="G212">
         <v>540</v>
       </c>
-      <c r="F146">
+      <c r="H212">
         <v>269</v>
       </c>
-      <c r="G146">
+      <c r="I212">
         <v>186</v>
       </c>
-      <c r="H146">
+      <c r="J212">
         <v>88</v>
       </c>
-      <c r="I146">
+      <c r="K212">
         <v>52</v>
       </c>
-      <c r="J146">
+      <c r="L212">
         <v>36</v>
       </c>
-      <c r="K146">
+      <c r="M212">
         <v>13</v>
       </c>
-      <c r="L146">
+      <c r="N212">
         <v>8</v>
       </c>
-      <c r="M146">
+      <c r="O212">
         <v>7</v>
       </c>
-      <c r="N146">
+      <c r="P212">
         <v>5</v>
       </c>
-      <c r="O146">
+      <c r="Q212">
         <v>3</v>
       </c>
-      <c r="P146">
+      <c r="R212">
         <v>2</v>
       </c>
-      <c r="Q146">
+      <c r="S212">
         <v>1</v>
       </c>
-      <c r="R146">
+      <c r="T212">
         <v>1</v>
       </c>
-      <c r="S146">
+      <c r="U212">
         <v>1</v>
       </c>
-      <c r="T146">
+      <c r="V212">
         <v>1</v>
       </c>
-      <c r="U146">
+      <c r="W212">
         <v>6303</v>
       </c>
     </row>
+    <row r="214" spans="1:23">
+      <c r="A214" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="215" spans="1:23">
+      <c r="A215" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D215" s="1">
+        <v>0</v>
+      </c>
+      <c r="E215" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F215" s="1">
+        <v>1</v>
+      </c>
+      <c r="G215" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H215" s="1">
+        <v>2</v>
+      </c>
+      <c r="I215" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="J215" s="1">
+        <v>3</v>
+      </c>
+      <c r="K215" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="L215" s="1">
+        <v>4</v>
+      </c>
+      <c r="M215" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="N215" s="1">
+        <v>5</v>
+      </c>
+      <c r="O215" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="P215" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q215" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="R215" s="1">
+        <v>7</v>
+      </c>
+      <c r="S215" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="T215" s="1">
+        <v>8</v>
+      </c>
+      <c r="U215" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="V215" s="1">
+        <v>20</v>
+      </c>
+      <c r="W215" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="216" spans="1:23">
+      <c r="A216" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D216">
+        <v>0.7</v>
+      </c>
+      <c r="E216">
+        <v>0.8</v>
+      </c>
+      <c r="F216">
+        <v>1.6</v>
+      </c>
+      <c r="G216">
+        <v>0.6</v>
+      </c>
+      <c r="H216">
+        <v>0</v>
+      </c>
+      <c r="I216">
+        <v>0</v>
+      </c>
+      <c r="J216">
+        <v>0</v>
+      </c>
+      <c r="K216">
+        <v>0</v>
+      </c>
+      <c r="L216">
+        <v>0</v>
+      </c>
+      <c r="M216">
+        <v>0</v>
+      </c>
+      <c r="N216">
+        <v>0</v>
+      </c>
+      <c r="O216">
+        <v>0</v>
+      </c>
+      <c r="P216">
+        <v>0</v>
+      </c>
+      <c r="Q216">
+        <v>0</v>
+      </c>
+      <c r="R216">
+        <v>0</v>
+      </c>
+      <c r="S216">
+        <v>0</v>
+      </c>
+      <c r="T216">
+        <v>0</v>
+      </c>
+      <c r="U216">
+        <v>0</v>
+      </c>
+      <c r="V216">
+        <v>0</v>
+      </c>
+      <c r="W216">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="217" spans="1:23">
+      <c r="A217" s="1"/>
+      <c r="B217" s="1"/>
+      <c r="C217" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D217">
+        <v>1.6</v>
+      </c>
+      <c r="E217">
+        <v>3</v>
+      </c>
+      <c r="F217">
+        <v>2.6</v>
+      </c>
+      <c r="G217">
+        <v>3</v>
+      </c>
+      <c r="H217">
+        <v>2.2</v>
+      </c>
+      <c r="I217">
+        <v>1.1</v>
+      </c>
+      <c r="J217">
+        <v>6.8</v>
+      </c>
+      <c r="K217">
+        <v>0</v>
+      </c>
+      <c r="L217">
+        <v>0</v>
+      </c>
+      <c r="M217">
+        <v>0</v>
+      </c>
+      <c r="N217">
+        <v>0</v>
+      </c>
+      <c r="O217">
+        <v>14.3</v>
+      </c>
+      <c r="P217">
+        <v>0</v>
+      </c>
+      <c r="Q217">
+        <v>0</v>
+      </c>
+      <c r="R217">
+        <v>0</v>
+      </c>
+      <c r="S217">
+        <v>0</v>
+      </c>
+      <c r="T217">
+        <v>0</v>
+      </c>
+      <c r="U217">
+        <v>0</v>
+      </c>
+      <c r="V217">
+        <v>0</v>
+      </c>
+      <c r="W217">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:23">
+      <c r="A218" s="1"/>
+      <c r="B218" s="1"/>
+      <c r="C218" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D218">
+        <v>6.6</v>
+      </c>
+      <c r="E218">
+        <v>4.4</v>
+      </c>
+      <c r="F218">
+        <v>3</v>
+      </c>
+      <c r="G218">
+        <v>3.3</v>
+      </c>
+      <c r="H218">
+        <v>2.6</v>
+      </c>
+      <c r="I218">
+        <v>1.6</v>
+      </c>
+      <c r="J218">
+        <v>0</v>
+      </c>
+      <c r="K218">
+        <v>3.8</v>
+      </c>
+      <c r="L218">
+        <v>2.8</v>
+      </c>
+      <c r="M218">
+        <v>0</v>
+      </c>
+      <c r="N218">
+        <v>0</v>
+      </c>
+      <c r="O218">
+        <v>0</v>
+      </c>
+      <c r="P218">
+        <v>0</v>
+      </c>
+      <c r="Q218">
+        <v>0</v>
+      </c>
+      <c r="R218">
+        <v>0</v>
+      </c>
+      <c r="S218">
+        <v>0</v>
+      </c>
+      <c r="T218">
+        <v>0</v>
+      </c>
+      <c r="U218">
+        <v>0</v>
+      </c>
+      <c r="V218">
+        <v>0</v>
+      </c>
+      <c r="W218">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:23">
+      <c r="A219" s="1"/>
+      <c r="B219" s="1"/>
+      <c r="C219" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D219">
+        <v>0</v>
+      </c>
+      <c r="E219">
+        <v>0</v>
+      </c>
+      <c r="F219">
+        <v>0</v>
+      </c>
+      <c r="G219">
+        <v>0</v>
+      </c>
+      <c r="H219">
+        <v>0</v>
+      </c>
+      <c r="I219">
+        <v>0</v>
+      </c>
+      <c r="J219">
+        <v>0</v>
+      </c>
+      <c r="K219">
+        <v>0</v>
+      </c>
+      <c r="L219">
+        <v>0</v>
+      </c>
+      <c r="M219">
+        <v>0</v>
+      </c>
+      <c r="N219">
+        <v>0</v>
+      </c>
+      <c r="O219">
+        <v>0</v>
+      </c>
+      <c r="P219">
+        <v>0</v>
+      </c>
+      <c r="Q219">
+        <v>0</v>
+      </c>
+      <c r="R219">
+        <v>0</v>
+      </c>
+      <c r="S219">
+        <v>0</v>
+      </c>
+      <c r="T219">
+        <v>0</v>
+      </c>
+      <c r="U219">
+        <v>0</v>
+      </c>
+      <c r="V219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:23">
+      <c r="A220" s="1"/>
+      <c r="B220" s="1"/>
+      <c r="C220" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D220">
+        <v>15.1</v>
+      </c>
+      <c r="E220">
+        <v>16.9</v>
+      </c>
+      <c r="F220">
+        <v>17.4</v>
+      </c>
+      <c r="G220">
+        <v>8.5</v>
+      </c>
+      <c r="H220">
+        <v>8.6</v>
+      </c>
+      <c r="I220">
+        <v>6.5</v>
+      </c>
+      <c r="J220">
+        <v>5.7</v>
+      </c>
+      <c r="K220">
+        <v>5.8</v>
+      </c>
+      <c r="L220">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M220">
+        <v>7.7</v>
+      </c>
+      <c r="N220">
+        <v>0</v>
+      </c>
+      <c r="O220">
+        <v>14.3</v>
+      </c>
+      <c r="P220">
+        <v>0</v>
+      </c>
+      <c r="Q220">
+        <v>0</v>
+      </c>
+      <c r="R220">
+        <v>0</v>
+      </c>
+      <c r="S220">
+        <v>0</v>
+      </c>
+      <c r="T220">
+        <v>0</v>
+      </c>
+      <c r="U220">
+        <v>0</v>
+      </c>
+      <c r="V220">
+        <v>0</v>
+      </c>
+      <c r="W220">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="221" spans="1:23">
+      <c r="A221" s="1"/>
+      <c r="B221" s="1"/>
+      <c r="C221" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D221">
+        <v>15.9</v>
+      </c>
+      <c r="E221">
+        <v>12.2</v>
+      </c>
+      <c r="F221">
+        <v>7.7</v>
+      </c>
+      <c r="G221">
+        <v>6.9</v>
+      </c>
+      <c r="H221">
+        <v>3.3</v>
+      </c>
+      <c r="I221">
+        <v>3.8</v>
+      </c>
+      <c r="J221">
+        <v>0</v>
+      </c>
+      <c r="K221">
+        <v>1.9</v>
+      </c>
+      <c r="L221">
+        <v>5.6</v>
+      </c>
+      <c r="M221">
+        <v>0</v>
+      </c>
+      <c r="N221">
+        <v>12.5</v>
+      </c>
+      <c r="O221">
+        <v>0</v>
+      </c>
+      <c r="P221">
+        <v>0</v>
+      </c>
+      <c r="Q221">
+        <v>0</v>
+      </c>
+      <c r="R221">
+        <v>0</v>
+      </c>
+      <c r="S221">
+        <v>0</v>
+      </c>
+      <c r="T221">
+        <v>0</v>
+      </c>
+      <c r="U221">
+        <v>0</v>
+      </c>
+      <c r="V221">
+        <v>0</v>
+      </c>
+      <c r="W221">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:23">
+      <c r="A222" s="1"/>
+      <c r="B222" s="1"/>
+      <c r="C222" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D222">
+        <v>0.9</v>
+      </c>
+      <c r="E222">
+        <v>0.7</v>
+      </c>
+      <c r="F222">
+        <v>0.7</v>
+      </c>
+      <c r="G222">
+        <v>0.6</v>
+      </c>
+      <c r="H222">
+        <v>1.1</v>
+      </c>
+      <c r="I222">
+        <v>0.5</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>0</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+      <c r="M222">
+        <v>0</v>
+      </c>
+      <c r="N222">
+        <v>0</v>
+      </c>
+      <c r="O222">
+        <v>0</v>
+      </c>
+      <c r="P222">
+        <v>0</v>
+      </c>
+      <c r="Q222">
+        <v>0</v>
+      </c>
+      <c r="R222">
+        <v>0</v>
+      </c>
+      <c r="S222">
+        <v>0</v>
+      </c>
+      <c r="T222">
+        <v>0</v>
+      </c>
+      <c r="U222">
+        <v>0</v>
+      </c>
+      <c r="V222">
+        <v>0</v>
+      </c>
+      <c r="W222">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="223" spans="1:23">
+      <c r="A223" s="1"/>
+      <c r="B223" s="1"/>
+      <c r="C223" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D223">
+        <v>8.5</v>
+      </c>
+      <c r="E223">
+        <v>6</v>
+      </c>
+      <c r="F223">
+        <v>3.5</v>
+      </c>
+      <c r="G223">
+        <v>3.5</v>
+      </c>
+      <c r="H223">
+        <v>3</v>
+      </c>
+      <c r="I223">
+        <v>1.1</v>
+      </c>
+      <c r="J223">
+        <v>2.3</v>
+      </c>
+      <c r="K223">
+        <v>0</v>
+      </c>
+      <c r="L223">
+        <v>2.8</v>
+      </c>
+      <c r="M223">
+        <v>7.7</v>
+      </c>
+      <c r="N223">
+        <v>12.5</v>
+      </c>
+      <c r="O223">
+        <v>0</v>
+      </c>
+      <c r="P223">
+        <v>0</v>
+      </c>
+      <c r="Q223">
+        <v>0</v>
+      </c>
+      <c r="R223">
+        <v>0</v>
+      </c>
+      <c r="S223">
+        <v>0</v>
+      </c>
+      <c r="T223">
+        <v>0</v>
+      </c>
+      <c r="U223">
+        <v>0</v>
+      </c>
+      <c r="V223">
+        <v>0</v>
+      </c>
+      <c r="W223">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="224" spans="1:23">
+      <c r="A224" s="1"/>
+      <c r="B224" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D224">
+        <v>0.2</v>
+      </c>
+      <c r="E224">
+        <v>0.3</v>
+      </c>
+      <c r="F224">
+        <v>0.2</v>
+      </c>
+      <c r="G224">
+        <v>0.4</v>
+      </c>
+      <c r="H224">
+        <v>1.5</v>
+      </c>
+      <c r="I224">
+        <v>0.5</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>0</v>
+      </c>
+      <c r="L224">
+        <v>0</v>
+      </c>
+      <c r="M224">
+        <v>0</v>
+      </c>
+      <c r="N224">
+        <v>0</v>
+      </c>
+      <c r="O224">
+        <v>0</v>
+      </c>
+      <c r="P224">
+        <v>0</v>
+      </c>
+      <c r="Q224">
+        <v>0</v>
+      </c>
+      <c r="R224">
+        <v>0</v>
+      </c>
+      <c r="S224">
+        <v>0</v>
+      </c>
+      <c r="T224">
+        <v>0</v>
+      </c>
+      <c r="U224">
+        <v>0</v>
+      </c>
+      <c r="V224">
+        <v>100</v>
+      </c>
+      <c r="W224">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="225" spans="1:23">
+      <c r="A225" s="1"/>
+      <c r="B225" s="1"/>
+      <c r="C225" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D225">
+        <v>1</v>
+      </c>
+      <c r="E225">
+        <v>1.5</v>
+      </c>
+      <c r="F225">
+        <v>1.2</v>
+      </c>
+      <c r="G225">
+        <v>1.9</v>
+      </c>
+      <c r="H225">
+        <v>0.7</v>
+      </c>
+      <c r="I225">
+        <v>2.2</v>
+      </c>
+      <c r="J225">
+        <v>1.1</v>
+      </c>
+      <c r="K225">
+        <v>1.9</v>
+      </c>
+      <c r="L225">
+        <v>2.8</v>
+      </c>
+      <c r="M225">
+        <v>0</v>
+      </c>
+      <c r="N225">
+        <v>0</v>
+      </c>
+      <c r="O225">
+        <v>0</v>
+      </c>
+      <c r="P225">
+        <v>0</v>
+      </c>
+      <c r="Q225">
+        <v>0</v>
+      </c>
+      <c r="R225">
+        <v>0</v>
+      </c>
+      <c r="S225">
+        <v>0</v>
+      </c>
+      <c r="T225">
+        <v>0</v>
+      </c>
+      <c r="U225">
+        <v>0</v>
+      </c>
+      <c r="V225">
+        <v>0</v>
+      </c>
+      <c r="W225">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:23">
+      <c r="A226" s="1"/>
+      <c r="B226" s="1"/>
+      <c r="C226" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D226">
+        <v>1.9</v>
+      </c>
+      <c r="E226">
+        <v>1</v>
+      </c>
+      <c r="F226">
+        <v>1.2</v>
+      </c>
+      <c r="G226">
+        <v>0.7</v>
+      </c>
+      <c r="H226">
+        <v>1.9</v>
+      </c>
+      <c r="I226">
+        <v>0.5</v>
+      </c>
+      <c r="J226">
+        <v>3.4</v>
+      </c>
+      <c r="K226">
+        <v>0</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
+      </c>
+      <c r="M226">
+        <v>0</v>
+      </c>
+      <c r="N226">
+        <v>0</v>
+      </c>
+      <c r="O226">
+        <v>0</v>
+      </c>
+      <c r="P226">
+        <v>0</v>
+      </c>
+      <c r="Q226">
+        <v>0</v>
+      </c>
+      <c r="R226">
+        <v>0</v>
+      </c>
+      <c r="S226">
+        <v>0</v>
+      </c>
+      <c r="T226">
+        <v>0</v>
+      </c>
+      <c r="U226">
+        <v>100</v>
+      </c>
+      <c r="V226">
+        <v>0</v>
+      </c>
+      <c r="W226">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="227" spans="1:23">
+      <c r="A227" s="1"/>
+      <c r="B227" s="1"/>
+      <c r="C227" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D227">
+        <v>4</v>
+      </c>
+      <c r="E227">
+        <v>3.7</v>
+      </c>
+      <c r="F227">
+        <v>3.7</v>
+      </c>
+      <c r="G227">
+        <v>1.9</v>
+      </c>
+      <c r="H227">
+        <v>2.6</v>
+      </c>
+      <c r="I227">
+        <v>1.1</v>
+      </c>
+      <c r="J227">
+        <v>2.3</v>
+      </c>
+      <c r="K227">
+        <v>1.9</v>
+      </c>
+      <c r="L227">
+        <v>5.6</v>
+      </c>
+      <c r="M227">
+        <v>0</v>
+      </c>
+      <c r="N227">
+        <v>0</v>
+      </c>
+      <c r="O227">
+        <v>0</v>
+      </c>
+      <c r="P227">
+        <v>0</v>
+      </c>
+      <c r="Q227">
+        <v>0</v>
+      </c>
+      <c r="R227">
+        <v>0</v>
+      </c>
+      <c r="S227">
+        <v>0</v>
+      </c>
+      <c r="T227">
+        <v>0</v>
+      </c>
+      <c r="U227">
+        <v>0</v>
+      </c>
+      <c r="V227">
+        <v>0</v>
+      </c>
+      <c r="W227">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="228" spans="1:23">
+      <c r="A228" s="1"/>
+      <c r="B228" s="1"/>
+      <c r="C228" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D228">
+        <v>4.2</v>
+      </c>
+      <c r="E228">
+        <v>5.9</v>
+      </c>
+      <c r="F228">
+        <v>5.1</v>
+      </c>
+      <c r="G228">
+        <v>5.4</v>
+      </c>
+      <c r="H228">
+        <v>2.6</v>
+      </c>
+      <c r="I228">
+        <v>1.6</v>
+      </c>
+      <c r="J228">
+        <v>2.3</v>
+      </c>
+      <c r="K228">
+        <v>1.9</v>
+      </c>
+      <c r="L228">
+        <v>2.8</v>
+      </c>
+      <c r="M228">
+        <v>0</v>
+      </c>
+      <c r="N228">
+        <v>0</v>
+      </c>
+      <c r="O228">
+        <v>0</v>
+      </c>
+      <c r="P228">
+        <v>0</v>
+      </c>
+      <c r="Q228">
+        <v>0</v>
+      </c>
+      <c r="R228">
+        <v>0</v>
+      </c>
+      <c r="S228">
+        <v>0</v>
+      </c>
+      <c r="T228">
+        <v>0</v>
+      </c>
+      <c r="U228">
+        <v>0</v>
+      </c>
+      <c r="V228">
+        <v>0</v>
+      </c>
+      <c r="W228">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="229" spans="1:23">
+      <c r="A229" s="1"/>
+      <c r="B229" s="1"/>
+      <c r="C229" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D229">
+        <v>1.8</v>
+      </c>
+      <c r="E229">
+        <v>1.1</v>
+      </c>
+      <c r="F229">
+        <v>0.6</v>
+      </c>
+      <c r="G229">
+        <v>0.2</v>
+      </c>
+      <c r="H229">
+        <v>0</v>
+      </c>
+      <c r="I229">
+        <v>0.5</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229">
+        <v>0</v>
+      </c>
+      <c r="L229">
+        <v>0</v>
+      </c>
+      <c r="M229">
+        <v>0</v>
+      </c>
+      <c r="N229">
+        <v>12.5</v>
+      </c>
+      <c r="O229">
+        <v>0</v>
+      </c>
+      <c r="P229">
+        <v>0</v>
+      </c>
+      <c r="Q229">
+        <v>0</v>
+      </c>
+      <c r="R229">
+        <v>0</v>
+      </c>
+      <c r="S229">
+        <v>0</v>
+      </c>
+      <c r="T229">
+        <v>0</v>
+      </c>
+      <c r="U229">
+        <v>0</v>
+      </c>
+      <c r="V229">
+        <v>0</v>
+      </c>
+      <c r="W229">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:23">
+      <c r="A230" s="1"/>
+      <c r="B230" s="1"/>
+      <c r="C230" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D230">
+        <v>0.5</v>
+      </c>
+      <c r="E230">
+        <v>0.4</v>
+      </c>
+      <c r="F230">
+        <v>0.5</v>
+      </c>
+      <c r="G230">
+        <v>0.2</v>
+      </c>
+      <c r="H230">
+        <v>0.4</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>0</v>
+      </c>
+      <c r="L230">
+        <v>0</v>
+      </c>
+      <c r="M230">
+        <v>0</v>
+      </c>
+      <c r="N230">
+        <v>12.5</v>
+      </c>
+      <c r="O230">
+        <v>0</v>
+      </c>
+      <c r="P230">
+        <v>0</v>
+      </c>
+      <c r="Q230">
+        <v>0</v>
+      </c>
+      <c r="R230">
+        <v>0</v>
+      </c>
+      <c r="S230">
+        <v>0</v>
+      </c>
+      <c r="T230">
+        <v>0</v>
+      </c>
+      <c r="U230">
+        <v>0</v>
+      </c>
+      <c r="V230">
+        <v>0</v>
+      </c>
+      <c r="W230">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:23">
+      <c r="A231" s="1"/>
+      <c r="B231" s="1"/>
+      <c r="C231" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D231">
+        <v>1.2</v>
+      </c>
+      <c r="E231">
+        <v>1.3</v>
+      </c>
+      <c r="F231">
+        <v>1.1</v>
+      </c>
+      <c r="G231">
+        <v>0.7</v>
+      </c>
+      <c r="H231">
+        <v>0</v>
+      </c>
+      <c r="I231">
+        <v>0.5</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231">
+        <v>3.8</v>
+      </c>
+      <c r="L231">
+        <v>2.8</v>
+      </c>
+      <c r="M231">
+        <v>0</v>
+      </c>
+      <c r="N231">
+        <v>0</v>
+      </c>
+      <c r="O231">
+        <v>0</v>
+      </c>
+      <c r="P231">
+        <v>0</v>
+      </c>
+      <c r="Q231">
+        <v>0</v>
+      </c>
+      <c r="R231">
+        <v>0</v>
+      </c>
+      <c r="S231">
+        <v>0</v>
+      </c>
+      <c r="T231">
+        <v>0</v>
+      </c>
+      <c r="U231">
+        <v>0</v>
+      </c>
+      <c r="V231">
+        <v>0</v>
+      </c>
+      <c r="W231">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:23">
+      <c r="A232" s="1"/>
+      <c r="B232" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D232">
+        <v>0.1</v>
+      </c>
+      <c r="E232">
+        <v>0</v>
+      </c>
+      <c r="F232">
+        <v>0.1</v>
+      </c>
+      <c r="G232">
+        <v>0.4</v>
+      </c>
+      <c r="H232">
+        <v>0.7</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>0</v>
+      </c>
+      <c r="K232">
+        <v>0</v>
+      </c>
+      <c r="L232">
+        <v>0</v>
+      </c>
+      <c r="M232">
+        <v>0</v>
+      </c>
+      <c r="N232">
+        <v>0</v>
+      </c>
+      <c r="O232">
+        <v>14.3</v>
+      </c>
+      <c r="P232">
+        <v>20</v>
+      </c>
+      <c r="Q232">
+        <v>0</v>
+      </c>
+      <c r="R232">
+        <v>50</v>
+      </c>
+      <c r="S232">
+        <v>0</v>
+      </c>
+      <c r="T232">
+        <v>0</v>
+      </c>
+      <c r="U232">
+        <v>0</v>
+      </c>
+      <c r="V232">
+        <v>0</v>
+      </c>
+      <c r="W232">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:23">
+      <c r="A233" s="1"/>
+      <c r="B233" s="1"/>
+      <c r="C233" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D233">
+        <v>0.5</v>
+      </c>
+      <c r="E233">
+        <v>1.5</v>
+      </c>
+      <c r="F233">
+        <v>2.7</v>
+      </c>
+      <c r="G233">
+        <v>4.4</v>
+      </c>
+      <c r="H233">
+        <v>3.3</v>
+      </c>
+      <c r="I233">
+        <v>5.4</v>
+      </c>
+      <c r="J233">
+        <v>4.5</v>
+      </c>
+      <c r="K233">
+        <v>1.9</v>
+      </c>
+      <c r="L233">
+        <v>2.8</v>
+      </c>
+      <c r="M233">
+        <v>0</v>
+      </c>
+      <c r="N233">
+        <v>12.5</v>
+      </c>
+      <c r="O233">
+        <v>14.3</v>
+      </c>
+      <c r="P233">
+        <v>0</v>
+      </c>
+      <c r="Q233">
+        <v>0</v>
+      </c>
+      <c r="R233">
+        <v>0</v>
+      </c>
+      <c r="S233">
+        <v>0</v>
+      </c>
+      <c r="T233">
+        <v>0</v>
+      </c>
+      <c r="U233">
+        <v>0</v>
+      </c>
+      <c r="V233">
+        <v>0</v>
+      </c>
+      <c r="W233">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="234" spans="1:23">
+      <c r="A234" s="1"/>
+      <c r="B234" s="1"/>
+      <c r="C234" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D234">
+        <v>0.2</v>
+      </c>
+      <c r="E234">
+        <v>0.6</v>
+      </c>
+      <c r="F234">
+        <v>0.4</v>
+      </c>
+      <c r="G234">
+        <v>0.9</v>
+      </c>
+      <c r="H234">
+        <v>2.2</v>
+      </c>
+      <c r="I234">
+        <v>0.5</v>
+      </c>
+      <c r="J234">
+        <v>1.1</v>
+      </c>
+      <c r="K234">
+        <v>0</v>
+      </c>
+      <c r="L234">
+        <v>2.8</v>
+      </c>
+      <c r="M234">
+        <v>0</v>
+      </c>
+      <c r="N234">
+        <v>0</v>
+      </c>
+      <c r="O234">
+        <v>0</v>
+      </c>
+      <c r="P234">
+        <v>0</v>
+      </c>
+      <c r="Q234">
+        <v>0</v>
+      </c>
+      <c r="R234">
+        <v>0</v>
+      </c>
+      <c r="S234">
+        <v>100</v>
+      </c>
+      <c r="T234">
+        <v>0</v>
+      </c>
+      <c r="U234">
+        <v>0</v>
+      </c>
+      <c r="V234">
+        <v>0</v>
+      </c>
+      <c r="W234">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="235" spans="1:23">
+      <c r="A235" s="1"/>
+      <c r="B235" s="1"/>
+      <c r="C235" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D235">
+        <v>1.1</v>
+      </c>
+      <c r="E235">
+        <v>2.1</v>
+      </c>
+      <c r="F235">
+        <v>1.6</v>
+      </c>
+      <c r="G235">
+        <v>3</v>
+      </c>
+      <c r="H235">
+        <v>1.9</v>
+      </c>
+      <c r="I235">
+        <v>1.1</v>
+      </c>
+      <c r="J235">
+        <v>2.3</v>
+      </c>
+      <c r="K235">
+        <v>7.7</v>
+      </c>
+      <c r="L235">
+        <v>2.8</v>
+      </c>
+      <c r="M235">
+        <v>15.4</v>
+      </c>
+      <c r="N235">
+        <v>0</v>
+      </c>
+      <c r="O235">
+        <v>28.6</v>
+      </c>
+      <c r="P235">
+        <v>0</v>
+      </c>
+      <c r="Q235">
+        <v>0</v>
+      </c>
+      <c r="R235">
+        <v>0</v>
+      </c>
+      <c r="S235">
+        <v>0</v>
+      </c>
+      <c r="T235">
+        <v>100</v>
+      </c>
+      <c r="U235">
+        <v>0</v>
+      </c>
+      <c r="V235">
+        <v>0</v>
+      </c>
+      <c r="W235">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="236" spans="1:23">
+      <c r="A236" s="1"/>
+      <c r="B236" s="1"/>
+      <c r="C236" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D236">
+        <v>0.5</v>
+      </c>
+      <c r="E236">
+        <v>1.5</v>
+      </c>
+      <c r="F236">
+        <v>2.1</v>
+      </c>
+      <c r="G236">
+        <v>2.2</v>
+      </c>
+      <c r="H236">
+        <v>1.5</v>
+      </c>
+      <c r="I236">
+        <v>1.6</v>
+      </c>
+      <c r="J236">
+        <v>2.3</v>
+      </c>
+      <c r="K236">
+        <v>3.8</v>
+      </c>
+      <c r="L236">
+        <v>5.6</v>
+      </c>
+      <c r="M236">
+        <v>0</v>
+      </c>
+      <c r="N236">
+        <v>0</v>
+      </c>
+      <c r="O236">
+        <v>0</v>
+      </c>
+      <c r="P236">
+        <v>20</v>
+      </c>
+      <c r="Q236">
+        <v>0</v>
+      </c>
+      <c r="R236">
+        <v>0</v>
+      </c>
+      <c r="S236">
+        <v>0</v>
+      </c>
+      <c r="T236">
+        <v>0</v>
+      </c>
+      <c r="U236">
+        <v>0</v>
+      </c>
+      <c r="V236">
+        <v>0</v>
+      </c>
+      <c r="W236">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:23">
+      <c r="A237" s="1"/>
+      <c r="B237" s="1"/>
+      <c r="C237" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D237">
+        <v>0.1</v>
+      </c>
+      <c r="E237">
+        <v>0.1</v>
+      </c>
+      <c r="F237">
+        <v>0.4</v>
+      </c>
+      <c r="G237">
+        <v>0</v>
+      </c>
+      <c r="H237">
+        <v>0.7</v>
+      </c>
+      <c r="I237">
+        <v>0.5</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>0</v>
+      </c>
+      <c r="L237">
+        <v>0</v>
+      </c>
+      <c r="M237">
+        <v>0</v>
+      </c>
+      <c r="N237">
+        <v>0</v>
+      </c>
+      <c r="O237">
+        <v>0</v>
+      </c>
+      <c r="P237">
+        <v>0</v>
+      </c>
+      <c r="Q237">
+        <v>0</v>
+      </c>
+      <c r="R237">
+        <v>0</v>
+      </c>
+      <c r="S237">
+        <v>0</v>
+      </c>
+      <c r="T237">
+        <v>0</v>
+      </c>
+      <c r="U237">
+        <v>0</v>
+      </c>
+      <c r="V237">
+        <v>0</v>
+      </c>
+      <c r="W237">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:23">
+      <c r="A238" s="1"/>
+      <c r="B238" s="1"/>
+      <c r="C238" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D238">
+        <v>0.2</v>
+      </c>
+      <c r="E238">
+        <v>0.4</v>
+      </c>
+      <c r="F238">
+        <v>0.4</v>
+      </c>
+      <c r="G238">
+        <v>0.4</v>
+      </c>
+      <c r="H238">
+        <v>0.4</v>
+      </c>
+      <c r="I238">
+        <v>0.5</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238">
+        <v>0</v>
+      </c>
+      <c r="L238">
+        <v>0</v>
+      </c>
+      <c r="M238">
+        <v>0</v>
+      </c>
+      <c r="N238">
+        <v>0</v>
+      </c>
+      <c r="O238">
+        <v>0</v>
+      </c>
+      <c r="P238">
+        <v>0</v>
+      </c>
+      <c r="Q238">
+        <v>0</v>
+      </c>
+      <c r="R238">
+        <v>0</v>
+      </c>
+      <c r="S238">
+        <v>0</v>
+      </c>
+      <c r="T238">
+        <v>0</v>
+      </c>
+      <c r="U238">
+        <v>0</v>
+      </c>
+      <c r="V238">
+        <v>0</v>
+      </c>
+      <c r="W238">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="239" spans="1:23">
+      <c r="A239" s="1"/>
+      <c r="B239" s="1"/>
+      <c r="C239" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D239">
+        <v>0.4</v>
+      </c>
+      <c r="E239">
+        <v>0.5</v>
+      </c>
+      <c r="F239">
+        <v>0.2</v>
+      </c>
+      <c r="G239">
+        <v>0.9</v>
+      </c>
+      <c r="H239">
+        <v>0.4</v>
+      </c>
+      <c r="I239">
+        <v>1.1</v>
+      </c>
+      <c r="J239">
+        <v>0</v>
+      </c>
+      <c r="K239">
+        <v>1.9</v>
+      </c>
+      <c r="L239">
+        <v>2.8</v>
+      </c>
+      <c r="M239">
+        <v>0</v>
+      </c>
+      <c r="N239">
+        <v>0</v>
+      </c>
+      <c r="O239">
+        <v>0</v>
+      </c>
+      <c r="P239">
+        <v>0</v>
+      </c>
+      <c r="Q239">
+        <v>0</v>
+      </c>
+      <c r="R239">
+        <v>0</v>
+      </c>
+      <c r="S239">
+        <v>0</v>
+      </c>
+      <c r="T239">
+        <v>0</v>
+      </c>
+      <c r="U239">
+        <v>0</v>
+      </c>
+      <c r="V239">
+        <v>0</v>
+      </c>
+      <c r="W239">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="240" spans="1:23">
+      <c r="A240" s="1"/>
+      <c r="B240" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D240">
+        <v>0.2</v>
+      </c>
+      <c r="E240">
+        <v>0.2</v>
+      </c>
+      <c r="F240">
+        <v>0.5</v>
+      </c>
+      <c r="G240">
+        <v>0.6</v>
+      </c>
+      <c r="H240">
+        <v>0.7</v>
+      </c>
+      <c r="I240">
+        <v>1.1</v>
+      </c>
+      <c r="J240">
+        <v>3.4</v>
+      </c>
+      <c r="K240">
+        <v>0</v>
+      </c>
+      <c r="L240">
+        <v>0</v>
+      </c>
+      <c r="M240">
+        <v>0</v>
+      </c>
+      <c r="N240">
+        <v>0</v>
+      </c>
+      <c r="O240">
+        <v>0</v>
+      </c>
+      <c r="P240">
+        <v>0</v>
+      </c>
+      <c r="Q240">
+        <v>0</v>
+      </c>
+      <c r="R240">
+        <v>0</v>
+      </c>
+      <c r="S240">
+        <v>0</v>
+      </c>
+      <c r="T240">
+        <v>0</v>
+      </c>
+      <c r="U240">
+        <v>0</v>
+      </c>
+      <c r="V240">
+        <v>0</v>
+      </c>
+      <c r="W240">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:23">
+      <c r="A241" s="1"/>
+      <c r="B241" s="1"/>
+      <c r="C241" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D241">
+        <v>2.4</v>
+      </c>
+      <c r="E241">
+        <v>5.2</v>
+      </c>
+      <c r="F241">
+        <v>17.6</v>
+      </c>
+      <c r="G241">
+        <v>28</v>
+      </c>
+      <c r="H241">
+        <v>36.1</v>
+      </c>
+      <c r="I241">
+        <v>41.9</v>
+      </c>
+      <c r="J241">
+        <v>36.4</v>
+      </c>
+      <c r="K241">
+        <v>42.3</v>
+      </c>
+      <c r="L241">
+        <v>25</v>
+      </c>
+      <c r="M241">
+        <v>53.8</v>
+      </c>
+      <c r="N241">
+        <v>25</v>
+      </c>
+      <c r="O241">
+        <v>14.3</v>
+      </c>
+      <c r="P241">
+        <v>60</v>
+      </c>
+      <c r="Q241">
+        <v>33.3</v>
+      </c>
+      <c r="R241">
+        <v>50</v>
+      </c>
+      <c r="S241">
+        <v>0</v>
+      </c>
+      <c r="T241">
+        <v>0</v>
+      </c>
+      <c r="U241">
+        <v>0</v>
+      </c>
+      <c r="V241">
+        <v>0</v>
+      </c>
+      <c r="W241">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="242" spans="1:23">
+      <c r="A242" s="1"/>
+      <c r="B242" s="1"/>
+      <c r="C242" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D242">
+        <v>0.7</v>
+      </c>
+      <c r="E242">
+        <v>2.2</v>
+      </c>
+      <c r="F242">
+        <v>1.7</v>
+      </c>
+      <c r="G242">
+        <v>2.2</v>
+      </c>
+      <c r="H242">
+        <v>4.1</v>
+      </c>
+      <c r="I242">
+        <v>3.2</v>
+      </c>
+      <c r="J242">
+        <v>4.5</v>
+      </c>
+      <c r="K242">
+        <v>5.8</v>
+      </c>
+      <c r="L242">
+        <v>0</v>
+      </c>
+      <c r="M242">
+        <v>0</v>
+      </c>
+      <c r="N242">
+        <v>0</v>
+      </c>
+      <c r="O242">
+        <v>0</v>
+      </c>
+      <c r="P242">
+        <v>0</v>
+      </c>
+      <c r="Q242">
+        <v>0</v>
+      </c>
+      <c r="R242">
+        <v>0</v>
+      </c>
+      <c r="S242">
+        <v>0</v>
+      </c>
+      <c r="T242">
+        <v>0</v>
+      </c>
+      <c r="U242">
+        <v>0</v>
+      </c>
+      <c r="V242">
+        <v>0</v>
+      </c>
+      <c r="W242">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="243" spans="1:23">
+      <c r="A243" s="1"/>
+      <c r="B243" s="1"/>
+      <c r="C243" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D243">
+        <v>1.1</v>
+      </c>
+      <c r="E243">
+        <v>2.5</v>
+      </c>
+      <c r="F243">
+        <v>4.6</v>
+      </c>
+      <c r="G243">
+        <v>5.2</v>
+      </c>
+      <c r="H243">
+        <v>4.5</v>
+      </c>
+      <c r="I243">
+        <v>6.5</v>
+      </c>
+      <c r="J243">
+        <v>8</v>
+      </c>
+      <c r="K243">
+        <v>5.8</v>
+      </c>
+      <c r="L243">
+        <v>11.1</v>
+      </c>
+      <c r="M243">
+        <v>7.7</v>
+      </c>
+      <c r="N243">
+        <v>12.5</v>
+      </c>
+      <c r="O243">
+        <v>0</v>
+      </c>
+      <c r="P243">
+        <v>0</v>
+      </c>
+      <c r="Q243">
+        <v>66.7</v>
+      </c>
+      <c r="R243">
+        <v>0</v>
+      </c>
+      <c r="S243">
+        <v>0</v>
+      </c>
+      <c r="T243">
+        <v>0</v>
+      </c>
+      <c r="U243">
+        <v>0</v>
+      </c>
+      <c r="V243">
+        <v>0</v>
+      </c>
+      <c r="W243">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="244" spans="1:23">
+      <c r="A244" s="1"/>
+      <c r="B244" s="1"/>
+      <c r="C244" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D244">
+        <v>0</v>
+      </c>
+      <c r="E244">
+        <v>0</v>
+      </c>
+      <c r="F244">
+        <v>0</v>
+      </c>
+      <c r="G244">
+        <v>0</v>
+      </c>
+      <c r="H244">
+        <v>0</v>
+      </c>
+      <c r="I244">
+        <v>0</v>
+      </c>
+      <c r="J244">
+        <v>0</v>
+      </c>
+      <c r="K244">
+        <v>0</v>
+      </c>
+      <c r="L244">
+        <v>0</v>
+      </c>
+      <c r="M244">
+        <v>0</v>
+      </c>
+      <c r="N244">
+        <v>0</v>
+      </c>
+      <c r="O244">
+        <v>0</v>
+      </c>
+      <c r="P244">
+        <v>0</v>
+      </c>
+      <c r="Q244">
+        <v>0</v>
+      </c>
+      <c r="R244">
+        <v>0</v>
+      </c>
+      <c r="S244">
+        <v>0</v>
+      </c>
+      <c r="T244">
+        <v>0</v>
+      </c>
+      <c r="U244">
+        <v>0</v>
+      </c>
+      <c r="V244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:23">
+      <c r="A245" s="1"/>
+      <c r="B245" s="1"/>
+      <c r="C245" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D245">
+        <v>0.4</v>
+      </c>
+      <c r="E245">
+        <v>0.5</v>
+      </c>
+      <c r="F245">
+        <v>0.5</v>
+      </c>
+      <c r="G245">
+        <v>0.7</v>
+      </c>
+      <c r="H245">
+        <v>0.7</v>
+      </c>
+      <c r="I245">
+        <v>1.1</v>
+      </c>
+      <c r="J245">
+        <v>0</v>
+      </c>
+      <c r="K245">
+        <v>0</v>
+      </c>
+      <c r="L245">
+        <v>0</v>
+      </c>
+      <c r="M245">
+        <v>7.7</v>
+      </c>
+      <c r="N245">
+        <v>0</v>
+      </c>
+      <c r="O245">
+        <v>0</v>
+      </c>
+      <c r="P245">
+        <v>0</v>
+      </c>
+      <c r="Q245">
+        <v>0</v>
+      </c>
+      <c r="R245">
+        <v>0</v>
+      </c>
+      <c r="S245">
+        <v>0</v>
+      </c>
+      <c r="T245">
+        <v>0</v>
+      </c>
+      <c r="U245">
+        <v>0</v>
+      </c>
+      <c r="V245">
+        <v>0</v>
+      </c>
+      <c r="W245">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="246" spans="1:23">
+      <c r="A246" s="1"/>
+      <c r="B246" s="1"/>
+      <c r="C246" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D246">
+        <v>0.9</v>
+      </c>
+      <c r="E246">
+        <v>0.5</v>
+      </c>
+      <c r="F246">
+        <v>0.9</v>
+      </c>
+      <c r="G246">
+        <v>1.3</v>
+      </c>
+      <c r="H246">
+        <v>1.1</v>
+      </c>
+      <c r="I246">
+        <v>1.1</v>
+      </c>
+      <c r="J246">
+        <v>1.1</v>
+      </c>
+      <c r="K246">
+        <v>0</v>
+      </c>
+      <c r="L246">
+        <v>2.8</v>
+      </c>
+      <c r="M246">
+        <v>0</v>
+      </c>
+      <c r="N246">
+        <v>0</v>
+      </c>
+      <c r="O246">
+        <v>0</v>
+      </c>
+      <c r="P246">
+        <v>0</v>
+      </c>
+      <c r="Q246">
+        <v>0</v>
+      </c>
+      <c r="R246">
+        <v>0</v>
+      </c>
+      <c r="S246">
+        <v>0</v>
+      </c>
+      <c r="T246">
+        <v>0</v>
+      </c>
+      <c r="U246">
+        <v>0</v>
+      </c>
+      <c r="V246">
+        <v>0</v>
+      </c>
+      <c r="W246">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="247" spans="1:23">
+      <c r="A247" s="1"/>
+      <c r="B247" s="1"/>
+      <c r="C247" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D247">
+        <v>0.5</v>
+      </c>
+      <c r="E247">
+        <v>1.1</v>
+      </c>
+      <c r="F247">
+        <v>2.2</v>
+      </c>
+      <c r="G247">
+        <v>3.1</v>
+      </c>
+      <c r="H247">
+        <v>1.9</v>
+      </c>
+      <c r="I247">
+        <v>3.2</v>
+      </c>
+      <c r="J247">
+        <v>3.4</v>
+      </c>
+      <c r="K247">
+        <v>7.7</v>
+      </c>
+      <c r="L247">
+        <v>5.6</v>
+      </c>
+      <c r="M247">
+        <v>0</v>
+      </c>
+      <c r="N247">
+        <v>0</v>
+      </c>
+      <c r="O247">
+        <v>0</v>
+      </c>
+      <c r="P247">
+        <v>0</v>
+      </c>
+      <c r="Q247">
+        <v>0</v>
+      </c>
+      <c r="R247">
+        <v>0</v>
+      </c>
+      <c r="S247">
+        <v>0</v>
+      </c>
+      <c r="T247">
+        <v>0</v>
+      </c>
+      <c r="U247">
+        <v>0</v>
+      </c>
+      <c r="V247">
+        <v>0</v>
+      </c>
+      <c r="W247">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="248" spans="1:23">
+      <c r="A248" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D248">
+        <v>0.3</v>
+      </c>
+      <c r="E248">
+        <v>0.2</v>
+      </c>
+      <c r="F248">
+        <v>0.1</v>
+      </c>
+      <c r="G248">
+        <v>0.4</v>
+      </c>
+      <c r="H248">
+        <v>0</v>
+      </c>
+      <c r="I248">
+        <v>0</v>
+      </c>
+      <c r="J248">
+        <v>0</v>
+      </c>
+      <c r="K248">
+        <v>0</v>
+      </c>
+      <c r="L248">
+        <v>0</v>
+      </c>
+      <c r="M248">
+        <v>0</v>
+      </c>
+      <c r="N248">
+        <v>0</v>
+      </c>
+      <c r="O248">
+        <v>0</v>
+      </c>
+      <c r="P248">
+        <v>0</v>
+      </c>
+      <c r="Q248">
+        <v>0</v>
+      </c>
+      <c r="R248">
+        <v>0</v>
+      </c>
+      <c r="S248">
+        <v>0</v>
+      </c>
+      <c r="T248">
+        <v>0</v>
+      </c>
+      <c r="U248">
+        <v>0</v>
+      </c>
+      <c r="V248">
+        <v>0</v>
+      </c>
+      <c r="W248">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="249" spans="1:23">
+      <c r="A249" s="1"/>
+      <c r="B249" s="1"/>
+      <c r="C249" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D249">
+        <v>0.7</v>
+      </c>
+      <c r="E249">
+        <v>0.7</v>
+      </c>
+      <c r="F249">
+        <v>1</v>
+      </c>
+      <c r="G249">
+        <v>0.7</v>
+      </c>
+      <c r="H249">
+        <v>0.7</v>
+      </c>
+      <c r="I249">
+        <v>2.2</v>
+      </c>
+      <c r="J249">
+        <v>0</v>
+      </c>
+      <c r="K249">
+        <v>0</v>
+      </c>
+      <c r="L249">
+        <v>2.8</v>
+      </c>
+      <c r="M249">
+        <v>0</v>
+      </c>
+      <c r="N249">
+        <v>0</v>
+      </c>
+      <c r="O249">
+        <v>0</v>
+      </c>
+      <c r="P249">
+        <v>0</v>
+      </c>
+      <c r="Q249">
+        <v>0</v>
+      </c>
+      <c r="R249">
+        <v>0</v>
+      </c>
+      <c r="S249">
+        <v>0</v>
+      </c>
+      <c r="T249">
+        <v>0</v>
+      </c>
+      <c r="U249">
+        <v>0</v>
+      </c>
+      <c r="V249">
+        <v>0</v>
+      </c>
+      <c r="W249">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="250" spans="1:23">
+      <c r="A250" s="1"/>
+      <c r="B250" s="1"/>
+      <c r="C250" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D250">
+        <v>3.1</v>
+      </c>
+      <c r="E250">
+        <v>1.3</v>
+      </c>
+      <c r="F250">
+        <v>0.7</v>
+      </c>
+      <c r="G250">
+        <v>0.2</v>
+      </c>
+      <c r="H250">
+        <v>0.4</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250">
+        <v>0</v>
+      </c>
+      <c r="L250">
+        <v>0</v>
+      </c>
+      <c r="M250">
+        <v>0</v>
+      </c>
+      <c r="N250">
+        <v>0</v>
+      </c>
+      <c r="O250">
+        <v>0</v>
+      </c>
+      <c r="P250">
+        <v>0</v>
+      </c>
+      <c r="Q250">
+        <v>0</v>
+      </c>
+      <c r="R250">
+        <v>0</v>
+      </c>
+      <c r="S250">
+        <v>0</v>
+      </c>
+      <c r="T250">
+        <v>0</v>
+      </c>
+      <c r="U250">
+        <v>0</v>
+      </c>
+      <c r="V250">
+        <v>0</v>
+      </c>
+      <c r="W250">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="251" spans="1:23">
+      <c r="A251" s="1"/>
+      <c r="B251" s="1"/>
+      <c r="C251" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D251">
+        <v>0</v>
+      </c>
+      <c r="E251">
+        <v>0</v>
+      </c>
+      <c r="F251">
+        <v>0</v>
+      </c>
+      <c r="G251">
+        <v>0</v>
+      </c>
+      <c r="H251">
+        <v>0</v>
+      </c>
+      <c r="I251">
+        <v>0</v>
+      </c>
+      <c r="J251">
+        <v>0</v>
+      </c>
+      <c r="K251">
+        <v>0</v>
+      </c>
+      <c r="L251">
+        <v>0</v>
+      </c>
+      <c r="M251">
+        <v>0</v>
+      </c>
+      <c r="N251">
+        <v>0</v>
+      </c>
+      <c r="O251">
+        <v>0</v>
+      </c>
+      <c r="P251">
+        <v>0</v>
+      </c>
+      <c r="Q251">
+        <v>0</v>
+      </c>
+      <c r="R251">
+        <v>0</v>
+      </c>
+      <c r="S251">
+        <v>0</v>
+      </c>
+      <c r="T251">
+        <v>0</v>
+      </c>
+      <c r="U251">
+        <v>0</v>
+      </c>
+      <c r="V251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:23">
+      <c r="A252" s="1"/>
+      <c r="B252" s="1"/>
+      <c r="C252" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D252">
+        <v>4.7</v>
+      </c>
+      <c r="E252">
+        <v>4.2</v>
+      </c>
+      <c r="F252">
+        <v>2.5</v>
+      </c>
+      <c r="G252">
+        <v>0.9</v>
+      </c>
+      <c r="H252">
+        <v>0.4</v>
+      </c>
+      <c r="I252">
+        <v>0.5</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252">
+        <v>0</v>
+      </c>
+      <c r="L252">
+        <v>0</v>
+      </c>
+      <c r="M252">
+        <v>0</v>
+      </c>
+      <c r="N252">
+        <v>0</v>
+      </c>
+      <c r="O252">
+        <v>0</v>
+      </c>
+      <c r="P252">
+        <v>0</v>
+      </c>
+      <c r="Q252">
+        <v>0</v>
+      </c>
+      <c r="R252">
+        <v>0</v>
+      </c>
+      <c r="S252">
+        <v>0</v>
+      </c>
+      <c r="T252">
+        <v>0</v>
+      </c>
+      <c r="U252">
+        <v>0</v>
+      </c>
+      <c r="V252">
+        <v>0</v>
+      </c>
+      <c r="W252">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:23">
+      <c r="A253" s="1"/>
+      <c r="B253" s="1"/>
+      <c r="C253" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D253">
+        <v>8.4</v>
+      </c>
+      <c r="E253">
+        <v>6.7</v>
+      </c>
+      <c r="F253">
+        <v>2.8</v>
+      </c>
+      <c r="G253">
+        <v>0.6</v>
+      </c>
+      <c r="H253">
+        <v>0</v>
+      </c>
+      <c r="I253">
+        <v>1.1</v>
+      </c>
+      <c r="J253">
+        <v>2.3</v>
+      </c>
+      <c r="K253">
+        <v>0</v>
+      </c>
+      <c r="L253">
+        <v>0</v>
+      </c>
+      <c r="M253">
+        <v>0</v>
+      </c>
+      <c r="N253">
+        <v>0</v>
+      </c>
+      <c r="O253">
+        <v>0</v>
+      </c>
+      <c r="P253">
+        <v>0</v>
+      </c>
+      <c r="Q253">
+        <v>0</v>
+      </c>
+      <c r="R253">
+        <v>0</v>
+      </c>
+      <c r="S253">
+        <v>0</v>
+      </c>
+      <c r="T253">
+        <v>0</v>
+      </c>
+      <c r="U253">
+        <v>0</v>
+      </c>
+      <c r="V253">
+        <v>0</v>
+      </c>
+      <c r="W253">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:23">
+      <c r="A254" s="1"/>
+      <c r="B254" s="1"/>
+      <c r="C254" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D254">
+        <v>1</v>
+      </c>
+      <c r="E254">
+        <v>0.7</v>
+      </c>
+      <c r="F254">
+        <v>0.5</v>
+      </c>
+      <c r="G254">
+        <v>0.2</v>
+      </c>
+      <c r="H254">
+        <v>0.7</v>
+      </c>
+      <c r="I254">
+        <v>0.5</v>
+      </c>
+      <c r="J254">
+        <v>0</v>
+      </c>
+      <c r="K254">
+        <v>0</v>
+      </c>
+      <c r="L254">
+        <v>0</v>
+      </c>
+      <c r="M254">
+        <v>0</v>
+      </c>
+      <c r="N254">
+        <v>0</v>
+      </c>
+      <c r="O254">
+        <v>0</v>
+      </c>
+      <c r="P254">
+        <v>0</v>
+      </c>
+      <c r="Q254">
+        <v>0</v>
+      </c>
+      <c r="R254">
+        <v>0</v>
+      </c>
+      <c r="S254">
+        <v>0</v>
+      </c>
+      <c r="T254">
+        <v>0</v>
+      </c>
+      <c r="U254">
+        <v>0</v>
+      </c>
+      <c r="V254">
+        <v>0</v>
+      </c>
+      <c r="W254">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="255" spans="1:23">
+      <c r="A255" s="1"/>
+      <c r="B255" s="1"/>
+      <c r="C255" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D255">
+        <v>4.3</v>
+      </c>
+      <c r="E255">
+        <v>3.1</v>
+      </c>
+      <c r="F255">
+        <v>1.4</v>
+      </c>
+      <c r="G255">
+        <v>0.2</v>
+      </c>
+      <c r="H255">
+        <v>0.7</v>
+      </c>
+      <c r="I255">
+        <v>0</v>
+      </c>
+      <c r="J255">
+        <v>0</v>
+      </c>
+      <c r="K255">
+        <v>0</v>
+      </c>
+      <c r="L255">
+        <v>0</v>
+      </c>
+      <c r="M255">
+        <v>0</v>
+      </c>
+      <c r="N255">
+        <v>0</v>
+      </c>
+      <c r="O255">
+        <v>0</v>
+      </c>
+      <c r="P255">
+        <v>0</v>
+      </c>
+      <c r="Q255">
+        <v>0</v>
+      </c>
+      <c r="R255">
+        <v>0</v>
+      </c>
+      <c r="S255">
+        <v>0</v>
+      </c>
+      <c r="T255">
+        <v>0</v>
+      </c>
+      <c r="U255">
+        <v>0</v>
+      </c>
+      <c r="V255">
+        <v>0</v>
+      </c>
+      <c r="W255">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23">
+      <c r="A256" s="1"/>
+      <c r="B256" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D256">
+        <v>0</v>
+      </c>
+      <c r="E256">
+        <v>0</v>
+      </c>
+      <c r="F256">
+        <v>0.1</v>
+      </c>
+      <c r="G256">
+        <v>0</v>
+      </c>
+      <c r="H256">
+        <v>0</v>
+      </c>
+      <c r="I256">
+        <v>0</v>
+      </c>
+      <c r="J256">
+        <v>0</v>
+      </c>
+      <c r="K256">
+        <v>1.9</v>
+      </c>
+      <c r="L256">
+        <v>0</v>
+      </c>
+      <c r="M256">
+        <v>0</v>
+      </c>
+      <c r="N256">
+        <v>0</v>
+      </c>
+      <c r="O256">
+        <v>0</v>
+      </c>
+      <c r="P256">
+        <v>0</v>
+      </c>
+      <c r="Q256">
+        <v>0</v>
+      </c>
+      <c r="R256">
+        <v>0</v>
+      </c>
+      <c r="S256">
+        <v>0</v>
+      </c>
+      <c r="T256">
+        <v>0</v>
+      </c>
+      <c r="U256">
+        <v>0</v>
+      </c>
+      <c r="V256">
+        <v>0</v>
+      </c>
+      <c r="W256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23">
+      <c r="A257" s="1"/>
+      <c r="B257" s="1"/>
+      <c r="C257" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D257">
+        <v>0.4</v>
+      </c>
+      <c r="E257">
+        <v>1.1</v>
+      </c>
+      <c r="F257">
+        <v>2.4</v>
+      </c>
+      <c r="G257">
+        <v>2.4</v>
+      </c>
+      <c r="H257">
+        <v>3</v>
+      </c>
+      <c r="I257">
+        <v>2.7</v>
+      </c>
+      <c r="J257">
+        <v>3.4</v>
+      </c>
+      <c r="K257">
+        <v>0</v>
+      </c>
+      <c r="L257">
+        <v>0</v>
+      </c>
+      <c r="M257">
+        <v>0</v>
+      </c>
+      <c r="N257">
+        <v>0</v>
+      </c>
+      <c r="O257">
+        <v>0</v>
+      </c>
+      <c r="P257">
+        <v>0</v>
+      </c>
+      <c r="Q257">
+        <v>0</v>
+      </c>
+      <c r="R257">
+        <v>0</v>
+      </c>
+      <c r="S257">
+        <v>0</v>
+      </c>
+      <c r="T257">
+        <v>0</v>
+      </c>
+      <c r="U257">
+        <v>0</v>
+      </c>
+      <c r="V257">
+        <v>0</v>
+      </c>
+      <c r="W257">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="258" spans="1:23">
+      <c r="A258" s="1"/>
+      <c r="B258" s="1"/>
+      <c r="C258" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D258">
+        <v>0.4</v>
+      </c>
+      <c r="E258">
+        <v>0.4</v>
+      </c>
+      <c r="F258">
+        <v>0.5</v>
+      </c>
+      <c r="G258">
+        <v>0.4</v>
+      </c>
+      <c r="H258">
+        <v>0.7</v>
+      </c>
+      <c r="I258">
+        <v>0</v>
+      </c>
+      <c r="J258">
+        <v>0</v>
+      </c>
+      <c r="K258">
+        <v>0</v>
+      </c>
+      <c r="L258">
+        <v>0</v>
+      </c>
+      <c r="M258">
+        <v>0</v>
+      </c>
+      <c r="N258">
+        <v>0</v>
+      </c>
+      <c r="O258">
+        <v>0</v>
+      </c>
+      <c r="P258">
+        <v>0</v>
+      </c>
+      <c r="Q258">
+        <v>0</v>
+      </c>
+      <c r="R258">
+        <v>0</v>
+      </c>
+      <c r="S258">
+        <v>0</v>
+      </c>
+      <c r="T258">
+        <v>0</v>
+      </c>
+      <c r="U258">
+        <v>0</v>
+      </c>
+      <c r="V258">
+        <v>0</v>
+      </c>
+      <c r="W258">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="259" spans="1:23">
+      <c r="A259" s="1"/>
+      <c r="B259" s="1"/>
+      <c r="C259" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D259">
+        <v>3.1</v>
+      </c>
+      <c r="E259">
+        <v>2</v>
+      </c>
+      <c r="F259">
+        <v>1.6</v>
+      </c>
+      <c r="G259">
+        <v>0.9</v>
+      </c>
+      <c r="H259">
+        <v>0.4</v>
+      </c>
+      <c r="I259">
+        <v>0.5</v>
+      </c>
+      <c r="J259">
+        <v>1.1</v>
+      </c>
+      <c r="K259">
+        <v>0</v>
+      </c>
+      <c r="L259">
+        <v>2.8</v>
+      </c>
+      <c r="M259">
+        <v>0</v>
+      </c>
+      <c r="N259">
+        <v>0</v>
+      </c>
+      <c r="O259">
+        <v>0</v>
+      </c>
+      <c r="P259">
+        <v>0</v>
+      </c>
+      <c r="Q259">
+        <v>0</v>
+      </c>
+      <c r="R259">
+        <v>0</v>
+      </c>
+      <c r="S259">
+        <v>0</v>
+      </c>
+      <c r="T259">
+        <v>0</v>
+      </c>
+      <c r="U259">
+        <v>0</v>
+      </c>
+      <c r="V259">
+        <v>0</v>
+      </c>
+      <c r="W259">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:23">
+      <c r="A260" s="1"/>
+      <c r="B260" s="1"/>
+      <c r="C260" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D260">
+        <v>0.1</v>
+      </c>
+      <c r="E260">
+        <v>0.6</v>
+      </c>
+      <c r="F260">
+        <v>0.7</v>
+      </c>
+      <c r="G260">
+        <v>1.9</v>
+      </c>
+      <c r="H260">
+        <v>1.5</v>
+      </c>
+      <c r="I260">
+        <v>0.5</v>
+      </c>
+      <c r="J260">
+        <v>2.3</v>
+      </c>
+      <c r="K260">
+        <v>0</v>
+      </c>
+      <c r="L260">
+        <v>0</v>
+      </c>
+      <c r="M260">
+        <v>0</v>
+      </c>
+      <c r="N260">
+        <v>0</v>
+      </c>
+      <c r="O260">
+        <v>0</v>
+      </c>
+      <c r="P260">
+        <v>0</v>
+      </c>
+      <c r="Q260">
+        <v>0</v>
+      </c>
+      <c r="R260">
+        <v>0</v>
+      </c>
+      <c r="S260">
+        <v>0</v>
+      </c>
+      <c r="T260">
+        <v>0</v>
+      </c>
+      <c r="U260">
+        <v>0</v>
+      </c>
+      <c r="V260">
+        <v>0</v>
+      </c>
+      <c r="W260">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="261" spans="1:23">
+      <c r="A261" s="1"/>
+      <c r="B261" s="1"/>
+      <c r="C261" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D261">
+        <v>0.1</v>
+      </c>
+      <c r="E261">
+        <v>0.1</v>
+      </c>
+      <c r="F261">
+        <v>0</v>
+      </c>
+      <c r="G261">
+        <v>0</v>
+      </c>
+      <c r="H261">
+        <v>0</v>
+      </c>
+      <c r="I261">
+        <v>0</v>
+      </c>
+      <c r="J261">
+        <v>0</v>
+      </c>
+      <c r="K261">
+        <v>0</v>
+      </c>
+      <c r="L261">
+        <v>0</v>
+      </c>
+      <c r="M261">
+        <v>0</v>
+      </c>
+      <c r="N261">
+        <v>0</v>
+      </c>
+      <c r="O261">
+        <v>0</v>
+      </c>
+      <c r="P261">
+        <v>0</v>
+      </c>
+      <c r="Q261">
+        <v>0</v>
+      </c>
+      <c r="R261">
+        <v>0</v>
+      </c>
+      <c r="S261">
+        <v>0</v>
+      </c>
+      <c r="T261">
+        <v>0</v>
+      </c>
+      <c r="U261">
+        <v>0</v>
+      </c>
+      <c r="V261">
+        <v>0</v>
+      </c>
+      <c r="W261">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:23">
+      <c r="A262" s="1"/>
+      <c r="B262" s="1"/>
+      <c r="C262" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D262">
+        <v>0.3</v>
+      </c>
+      <c r="E262">
+        <v>0.2</v>
+      </c>
+      <c r="F262">
+        <v>0.1</v>
+      </c>
+      <c r="G262">
+        <v>0.2</v>
+      </c>
+      <c r="H262">
+        <v>0.7</v>
+      </c>
+      <c r="I262">
+        <v>0.5</v>
+      </c>
+      <c r="J262">
+        <v>0</v>
+      </c>
+      <c r="K262">
+        <v>0</v>
+      </c>
+      <c r="L262">
+        <v>0</v>
+      </c>
+      <c r="M262">
+        <v>0</v>
+      </c>
+      <c r="N262">
+        <v>0</v>
+      </c>
+      <c r="O262">
+        <v>0</v>
+      </c>
+      <c r="P262">
+        <v>0</v>
+      </c>
+      <c r="Q262">
+        <v>0</v>
+      </c>
+      <c r="R262">
+        <v>0</v>
+      </c>
+      <c r="S262">
+        <v>0</v>
+      </c>
+      <c r="T262">
+        <v>0</v>
+      </c>
+      <c r="U262">
+        <v>0</v>
+      </c>
+      <c r="V262">
+        <v>0</v>
+      </c>
+      <c r="W262">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="263" spans="1:23">
+      <c r="A263" s="1"/>
+      <c r="B263" s="1"/>
+      <c r="C263" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D263">
+        <v>0.4</v>
+      </c>
+      <c r="E263">
+        <v>0.4</v>
+      </c>
+      <c r="F263">
+        <v>0.1</v>
+      </c>
+      <c r="G263">
+        <v>0.2</v>
+      </c>
+      <c r="H263">
+        <v>0</v>
+      </c>
+      <c r="I263">
+        <v>1.1</v>
+      </c>
+      <c r="J263">
+        <v>0</v>
+      </c>
+      <c r="K263">
+        <v>0</v>
+      </c>
+      <c r="L263">
+        <v>0</v>
+      </c>
+      <c r="M263">
+        <v>0</v>
+      </c>
+      <c r="N263">
+        <v>0</v>
+      </c>
+      <c r="O263">
+        <v>0</v>
+      </c>
+      <c r="P263">
+        <v>0</v>
+      </c>
+      <c r="Q263">
+        <v>0</v>
+      </c>
+      <c r="R263">
+        <v>0</v>
+      </c>
+      <c r="S263">
+        <v>0</v>
+      </c>
+      <c r="T263">
+        <v>0</v>
+      </c>
+      <c r="U263">
+        <v>0</v>
+      </c>
+      <c r="V263">
+        <v>0</v>
+      </c>
+      <c r="W263">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="264" spans="1:23">
+      <c r="A264" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B264" s="1"/>
+      <c r="C264" s="1"/>
+      <c r="D264">
+        <v>100</v>
+      </c>
+      <c r="E264">
+        <v>100</v>
+      </c>
+      <c r="F264">
+        <v>100</v>
+      </c>
+      <c r="G264">
+        <v>100</v>
+      </c>
+      <c r="H264">
+        <v>100</v>
+      </c>
+      <c r="I264">
+        <v>100</v>
+      </c>
+      <c r="J264">
+        <v>100</v>
+      </c>
+      <c r="K264">
+        <v>100</v>
+      </c>
+      <c r="L264">
+        <v>100</v>
+      </c>
+      <c r="M264">
+        <v>100</v>
+      </c>
+      <c r="N264">
+        <v>100</v>
+      </c>
+      <c r="O264">
+        <v>100</v>
+      </c>
+      <c r="P264">
+        <v>100</v>
+      </c>
+      <c r="Q264">
+        <v>100</v>
+      </c>
+      <c r="R264">
+        <v>100</v>
+      </c>
+      <c r="S264">
+        <v>100</v>
+      </c>
+      <c r="T264">
+        <v>100</v>
+      </c>
+      <c r="U264">
+        <v>100</v>
+      </c>
+      <c r="V264">
+        <v>100</v>
+      </c>
+      <c r="W264">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="38">
     <mergeCell ref="A3:A8"/>
     <mergeCell ref="A9:A14"/>
     <mergeCell ref="B3:B6"/>
@@ -4347,10 +10956,30 @@
     <mergeCell ref="F83:I83"/>
     <mergeCell ref="J83:M83"/>
     <mergeCell ref="N83:Q83"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="E109:G109"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="E123:G123"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="F97:I97"/>
+    <mergeCell ref="J97:M97"/>
+    <mergeCell ref="N97:Q97"/>
+    <mergeCell ref="B135:D135"/>
+    <mergeCell ref="E135:G135"/>
+    <mergeCell ref="B149:D149"/>
+    <mergeCell ref="E149:G149"/>
+    <mergeCell ref="A164:A195"/>
+    <mergeCell ref="A196:A211"/>
+    <mergeCell ref="B164:B171"/>
+    <mergeCell ref="B172:B179"/>
+    <mergeCell ref="B180:B187"/>
+    <mergeCell ref="B188:B195"/>
+    <mergeCell ref="B196:B203"/>
+    <mergeCell ref="B204:B211"/>
+    <mergeCell ref="A216:A247"/>
+    <mergeCell ref="A248:A263"/>
+    <mergeCell ref="B216:B223"/>
+    <mergeCell ref="B224:B231"/>
+    <mergeCell ref="B232:B239"/>
+    <mergeCell ref="B240:B247"/>
+    <mergeCell ref="B248:B255"/>
+    <mergeCell ref="B256:B263"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets_output/04_bivariate_analysis_placements.xlsx
+++ b/assets_output/04_bivariate_analysis_placements.xlsx
@@ -1387,7 +1387,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Table 4.4: Placement outcomes by level and pathway type</t>
+          <t>Table 4.4: Placement outcomes by pathway type and level</t>
         </is>
       </c>
     </row>

--- a/assets_output/04_bivariate_analysis_placements.xlsx
+++ b/assets_output/04_bivariate_analysis_placements.xlsx
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1562</v>
+        <v>1660</v>
       </c>
       <c r="C30" t="n">
-        <v>24.6</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="31">
@@ -889,36 +889,36 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1164</v>
+        <v>865</v>
       </c>
       <c r="C32" t="n">
-        <v>18.3</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>744</v>
+        <v>854</v>
       </c>
       <c r="C33" t="n">
-        <v>11.7</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>653</v>
+        <v>744</v>
       </c>
       <c r="C34" t="n">
-        <v>10.3</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="35">
@@ -1019,17 +1019,17 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>1562</v>
+        <v>1660</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>24.6</v>
+        <v>26.1</v>
       </c>
       <c r="D42" s="1" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="F42" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="43">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>86</v>
+        <v>139</v>
       </c>
       <c r="F43" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="44">
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="F44" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="45">
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>1164</v>
+        <v>865</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>18.3</v>
+        <v>13.6</v>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>651</v>
+        <v>436</v>
       </c>
       <c r="F47" t="n">
-        <v>10.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="48">
@@ -1134,10 +1134,10 @@
       <c r="C48" s="1" t="n"/>
       <c r="D48" s="1" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="F48" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="49">
@@ -1150,54 +1150,46 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="F49" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>744</v>
+        <v>854</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
+        <v>13.4</v>
+      </c>
+      <c r="D50" s="1" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>433</v>
+      </c>
+      <c r="F50" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n"/>
+      <c r="B51" s="1" t="n"/>
+      <c r="C51" s="1" t="n"/>
+      <c r="D51" s="1" t="inlineStr">
         <is>
           <t>Unplanned</t>
         </is>
       </c>
-      <c r="E50" t="n">
-        <v>744</v>
-      </c>
-      <c r="F50" t="n">
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>Internal move: backwards</t>
-        </is>
-      </c>
-      <c r="B51" s="1" t="n">
-        <v>653</v>
-      </c>
-      <c r="C51" s="1" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="D51" s="1" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>425</v>
+        <v>318</v>
       </c>
       <c r="F51" t="n">
-        <v>6.7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -1206,30 +1198,38 @@
       <c r="C52" s="1" t="n"/>
       <c r="D52" s="1" t="inlineStr">
         <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>Returned to homelessness</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>744</v>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
           <t>Unplanned</t>
         </is>
       </c>
-      <c r="E52" t="n">
-        <v>145</v>
-      </c>
-      <c r="F52" t="n">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n"/>
-      <c r="B53" s="1" t="n"/>
-      <c r="C53" s="1" t="n"/>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
       <c r="E53" t="n">
-        <v>83</v>
+        <v>744</v>
       </c>
       <c r="F53" t="n">
-        <v>1.3</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="54">
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>924</v>
+        <v>1041</v>
       </c>
       <c r="C67" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D67" t="n">
         <v>88</v>
@@ -1493,10 +1493,10 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="G67" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>1562</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="68">
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>705</v>
+        <v>588</v>
       </c>
       <c r="C69" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D69" t="n">
         <v>12</v>
@@ -1561,10 +1561,10 @@
         <v>33</v>
       </c>
       <c r="F69" t="n">
-        <v>342</v>
+        <v>151</v>
       </c>
       <c r="G69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -1573,32 +1573,32 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>1164</v>
+        <v>865</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>362</v>
+        <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>70</v>
+        <v>205</v>
       </c>
       <c r="D70" t="n">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="E70" t="n">
-        <v>92</v>
+        <v>191</v>
       </c>
       <c r="F70" t="n">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="G70" t="n">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -1607,32 +1607,32 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>744</v>
+        <v>854</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>362</v>
       </c>
       <c r="C71" t="n">
-        <v>218</v>
+        <v>70</v>
       </c>
       <c r="D71" t="n">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="E71" t="n">
-        <v>191</v>
+        <v>92</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="G71" t="n">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -1641,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>653</v>
+        <v>744</v>
       </c>
     </row>
     <row r="72">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>36.4</v>
+        <v>41.1</v>
       </c>
       <c r="C81" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="D81" t="n">
         <v>20.1</v>
@@ -1885,15 +1885,15 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="G81" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="n">
-        <v>24.6</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="82">
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>27.8</v>
+        <v>23.2</v>
       </c>
       <c r="C83" t="n">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="D83" t="n">
         <v>2.7</v>
@@ -1945,75 +1945,75 @@
         <v>2.6</v>
       </c>
       <c r="F83" t="n">
-        <v>37</v>
+        <v>16.3</v>
       </c>
       <c r="G83" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="n">
-        <v>18.3</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>8</v>
+        <v>23.4</v>
       </c>
       <c r="D84" t="n">
-        <v>7.1</v>
+        <v>26.5</v>
       </c>
       <c r="E84" t="n">
-        <v>7.3</v>
+        <v>15.1</v>
       </c>
       <c r="F84" t="n">
-        <v>18.2</v>
+        <v>22.7</v>
       </c>
       <c r="G84" t="n">
-        <v>6.6</v>
+        <v>41.5</v>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="n">
-        <v>11.7</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="C85" t="n">
-        <v>24.9</v>
+        <v>8</v>
       </c>
       <c r="D85" t="n">
-        <v>26.5</v>
+        <v>7.1</v>
       </c>
       <c r="E85" t="n">
-        <v>15.1</v>
+        <v>7.3</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="G85" t="n">
-        <v>40.3</v>
+        <v>6.6</v>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="n">
-        <v>10.3</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="86">
@@ -2189,34 +2189,34 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C93" t="n">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="D93" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E93" t="n">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="F93" t="n">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="G93" t="n">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="H93" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I93" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="J93" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K93" t="n">
-        <v>1562</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="94">
@@ -2263,108 +2263,108 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C95" t="n">
-        <v>189</v>
+        <v>117</v>
       </c>
       <c r="D95" t="n">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="E95" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="F95" t="n">
-        <v>189</v>
+        <v>147</v>
       </c>
       <c r="G95" t="n">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="H95" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I95" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="J95" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="K95" t="n">
-        <v>1164</v>
+        <v>865</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C96" t="n">
-        <v>51</v>
+        <v>171</v>
       </c>
       <c r="D96" t="n">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="E96" t="n">
+        <v>110</v>
+      </c>
+      <c r="F96" t="n">
+        <v>101</v>
+      </c>
+      <c r="G96" t="n">
+        <v>88</v>
+      </c>
+      <c r="H96" t="n">
+        <v>94</v>
+      </c>
+      <c r="I96" t="n">
         <v>72</v>
       </c>
-      <c r="F96" t="n">
-        <v>95</v>
-      </c>
-      <c r="G96" t="n">
-        <v>114</v>
-      </c>
-      <c r="H96" t="n">
-        <v>127</v>
-      </c>
-      <c r="I96" t="n">
-        <v>137</v>
-      </c>
       <c r="J96" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="K96" t="n">
-        <v>744</v>
+        <v>854</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C97" t="n">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="D97" t="n">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="E97" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F97" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="G97" t="n">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="H97" t="n">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="I97" t="n">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="J97" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="K97" t="n">
-        <v>653</v>
+        <v>744</v>
       </c>
     </row>
     <row r="98">
@@ -2568,34 +2568,34 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>30.6</v>
+        <v>31.6</v>
       </c>
       <c r="C105" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="D105" t="n">
-        <v>29</v>
+        <v>29.6</v>
       </c>
       <c r="E105" t="n">
-        <v>25.3</v>
+        <v>26.6</v>
       </c>
       <c r="F105" t="n">
-        <v>22.5</v>
+        <v>24.7</v>
       </c>
       <c r="G105" t="n">
-        <v>22</v>
+        <v>23.9</v>
       </c>
       <c r="H105" t="n">
-        <v>17.2</v>
+        <v>18.6</v>
       </c>
       <c r="I105" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="J105" t="n">
-        <v>17.6</v>
+        <v>18</v>
       </c>
       <c r="K105" t="n">
-        <v>24.6</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="106">
@@ -2642,108 +2642,108 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>16.8</v>
+        <v>13.8</v>
       </c>
       <c r="C107" t="n">
-        <v>17.8</v>
+        <v>11</v>
       </c>
       <c r="D107" t="n">
-        <v>20</v>
+        <v>15.7</v>
       </c>
       <c r="E107" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="F107" t="n">
-        <v>21.7</v>
+        <v>16.9</v>
       </c>
       <c r="G107" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="H107" t="n">
-        <v>19.9</v>
+        <v>15.3</v>
       </c>
       <c r="I107" t="n">
-        <v>15.2</v>
+        <v>12</v>
       </c>
       <c r="J107" t="n">
-        <v>13.3</v>
+        <v>10.3</v>
       </c>
       <c r="K107" t="n">
-        <v>18.3</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>7.1</v>
+        <v>16.3</v>
       </c>
       <c r="C108" t="n">
-        <v>4.8</v>
+        <v>16.1</v>
       </c>
       <c r="D108" t="n">
-        <v>8.300000000000001</v>
+        <v>16.1</v>
       </c>
       <c r="E108" t="n">
-        <v>8</v>
+        <v>12.2</v>
       </c>
       <c r="F108" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G108" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H108" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I108" t="n">
         <v>10.9</v>
       </c>
-      <c r="G108" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="H108" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="I108" t="n">
-        <v>20.8</v>
-      </c>
       <c r="J108" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K108" t="n">
-        <v>11.7</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>14.3</v>
+        <v>7.1</v>
       </c>
       <c r="C109" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D109" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E109" t="n">
+        <v>8</v>
+      </c>
+      <c r="F109" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G109" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H109" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I109" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="J109" t="n">
+        <v>21</v>
+      </c>
+      <c r="K109" t="n">
         <v>11.7</v>
-      </c>
-      <c r="D109" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="E109" t="n">
-        <v>9</v>
-      </c>
-      <c r="F109" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="G109" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H109" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="I109" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J109" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K109" t="n">
-        <v>10.3</v>
       </c>
     </row>
     <row r="110">
@@ -2940,19 +2940,19 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="C117" t="n">
-        <v>594</v>
+        <v>657</v>
       </c>
       <c r="D117" t="n">
-        <v>412</v>
+        <v>456</v>
       </c>
       <c r="E117" t="n">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="F117" t="n">
-        <v>1562</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="118">
@@ -2984,63 +2984,63 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C119" t="n">
-        <v>354</v>
+        <v>294</v>
       </c>
       <c r="D119" t="n">
-        <v>341</v>
+        <v>300</v>
       </c>
       <c r="E119" t="n">
-        <v>346</v>
+        <v>152</v>
       </c>
       <c r="F119" t="n">
-        <v>1164</v>
+        <v>865</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="C120" t="n">
-        <v>298</v>
+        <v>206</v>
       </c>
       <c r="D120" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E120" t="n">
-        <v>189</v>
+        <v>342</v>
       </c>
       <c r="F120" t="n">
-        <v>744</v>
+        <v>854</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>166</v>
+        <v>109</v>
       </c>
       <c r="C121" t="n">
-        <v>209</v>
+        <v>298</v>
       </c>
       <c r="D121" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E121" t="n">
-        <v>128</v>
+        <v>189</v>
       </c>
       <c r="F121" t="n">
-        <v>653</v>
+        <v>744</v>
       </c>
     </row>
     <row r="122">
@@ -3177,19 +3177,19 @@
         </is>
       </c>
       <c r="B129" t="n">
+        <v>27</v>
+      </c>
+      <c r="C129" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D129" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E129" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F129" t="n">
         <v>26.1</v>
-      </c>
-      <c r="C129" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="D129" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E129" t="n">
-        <v>20</v>
-      </c>
-      <c r="F129" t="n">
-        <v>24.6</v>
       </c>
     </row>
     <row r="130">
@@ -3221,63 +3221,63 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="C131" t="n">
-        <v>15.2</v>
+        <v>12.6</v>
       </c>
       <c r="D131" t="n">
-        <v>21.2</v>
+        <v>18.6</v>
       </c>
       <c r="E131" t="n">
-        <v>27.8</v>
+        <v>12.2</v>
       </c>
       <c r="F131" t="n">
-        <v>18.3</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>9.300000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="C132" t="n">
-        <v>12.8</v>
+        <v>8.9</v>
       </c>
       <c r="D132" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="E132" t="n">
-        <v>15.2</v>
+        <v>27.5</v>
       </c>
       <c r="F132" t="n">
-        <v>11.7</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>14.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C133" t="n">
-        <v>9</v>
+        <v>12.8</v>
       </c>
       <c r="D133" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E133" t="n">
-        <v>10.3</v>
+        <v>15.2</v>
       </c>
       <c r="F133" t="n">
-        <v>10.3</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="134">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>924</v>
+        <v>1041</v>
       </c>
       <c r="C143" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D143" t="n">
         <v>88</v>
@@ -3477,10 +3477,10 @@
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="G143" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>1562</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="144">
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>705</v>
+        <v>588</v>
       </c>
       <c r="C145" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D145" t="n">
         <v>12</v>
@@ -3545,10 +3545,10 @@
         <v>33</v>
       </c>
       <c r="F145" t="n">
-        <v>342</v>
+        <v>151</v>
       </c>
       <c r="G145" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -3557,32 +3557,32 @@
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>1164</v>
+        <v>865</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>362</v>
+        <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>70</v>
+        <v>205</v>
       </c>
       <c r="D146" t="n">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="E146" t="n">
-        <v>92</v>
+        <v>191</v>
       </c>
       <c r="F146" t="n">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="G146" t="n">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -3591,32 +3591,32 @@
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>744</v>
+        <v>854</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>362</v>
       </c>
       <c r="C147" t="n">
-        <v>218</v>
+        <v>70</v>
       </c>
       <c r="D147" t="n">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="E147" t="n">
-        <v>191</v>
+        <v>92</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="G147" t="n">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>653</v>
+        <v>744</v>
       </c>
     </row>
     <row r="148">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>36.4</v>
+        <v>41.1</v>
       </c>
       <c r="C157" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="D157" t="n">
         <v>20.1</v>
@@ -3869,15 +3869,15 @@
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="G157" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="n">
-        <v>24.6</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="158">
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>27.8</v>
+        <v>23.2</v>
       </c>
       <c r="C159" t="n">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="D159" t="n">
         <v>2.7</v>
@@ -3929,75 +3929,75 @@
         <v>2.6</v>
       </c>
       <c r="F159" t="n">
-        <v>37</v>
+        <v>16.3</v>
       </c>
       <c r="G159" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="n">
-        <v>18.3</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="C160" t="n">
-        <v>8</v>
+        <v>23.4</v>
       </c>
       <c r="D160" t="n">
-        <v>7.1</v>
+        <v>26.5</v>
       </c>
       <c r="E160" t="n">
-        <v>7.3</v>
+        <v>15.1</v>
       </c>
       <c r="F160" t="n">
-        <v>18.2</v>
+        <v>22.7</v>
       </c>
       <c r="G160" t="n">
-        <v>6.6</v>
+        <v>41.5</v>
       </c>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="n">
-        <v>11.7</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="C161" t="n">
-        <v>24.9</v>
+        <v>8</v>
       </c>
       <c r="D161" t="n">
-        <v>26.5</v>
+        <v>7.1</v>
       </c>
       <c r="E161" t="n">
-        <v>15.1</v>
+        <v>7.3</v>
       </c>
       <c r="F161" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="G161" t="n">
-        <v>40.3</v>
+        <v>6.6</v>
       </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="n">
-        <v>10.3</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="162">
@@ -4273,16 +4273,16 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="C171" t="n">
-        <v>462</v>
+        <v>525</v>
       </c>
       <c r="D171" t="n">
-        <v>323</v>
+        <v>366</v>
       </c>
       <c r="E171" t="n">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="F171" t="n">
         <v>140</v>
@@ -4291,10 +4291,10 @@
         <v>84</v>
       </c>
       <c r="H171" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I171" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J171" t="n">
         <v>28</v>
@@ -4321,7 +4321,7 @@
         <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>1562</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="172">
@@ -4389,28 +4389,28 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C173" t="n">
-        <v>326</v>
+        <v>263</v>
       </c>
       <c r="D173" t="n">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="E173" t="n">
-        <v>342</v>
+        <v>151</v>
       </c>
       <c r="F173" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G173" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H173" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I173" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
         <v>7</v>
@@ -4437,123 +4437,123 @@
         <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>1164</v>
+        <v>865</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="E174" t="n">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="F174" t="n">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="G174" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="H174" t="n">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="I174" t="n">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="J174" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="K174" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="L174" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="M174" t="n">
         <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="O174" t="n">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="P174" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="Q174" t="n">
         <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>744</v>
+        <v>854</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="D175" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="E175" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="F175" t="n">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="G175" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="H175" t="n">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="I175" t="n">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="J175" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="K175" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="L175" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="M175" t="n">
         <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="O175" t="n">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="P175" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="Q175" t="n">
         <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>653</v>
+        <v>744</v>
       </c>
     </row>
     <row r="176">
@@ -4937,16 +4937,16 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>46.6</v>
+        <v>50.3</v>
       </c>
       <c r="C185" t="n">
-        <v>36.7</v>
+        <v>41.7</v>
       </c>
       <c r="D185" t="n">
-        <v>33.1</v>
+        <v>37.5</v>
       </c>
       <c r="E185" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="F185" t="n">
         <v>35.3</v>
@@ -4955,10 +4955,10 @@
         <v>35.6</v>
       </c>
       <c r="H185" t="n">
-        <v>31.6</v>
+        <v>32</v>
       </c>
       <c r="I185" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J185" t="n">
         <v>13</v>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="Q185" t="inlineStr"/>
       <c r="R185" t="n">
-        <v>24.6</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="186">
@@ -5045,28 +5045,28 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>23.8</v>
+        <v>20.1</v>
       </c>
       <c r="C187" t="n">
-        <v>25.9</v>
+        <v>20.9</v>
       </c>
       <c r="D187" t="n">
-        <v>31.5</v>
+        <v>27.1</v>
       </c>
       <c r="E187" t="n">
-        <v>37</v>
+        <v>16.3</v>
       </c>
       <c r="F187" t="n">
-        <v>9.300000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="G187" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="H187" t="n">
-        <v>9.4</v>
+        <v>10.2</v>
       </c>
       <c r="I187" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J187" t="n">
         <v>3.2</v>
@@ -5089,115 +5089,115 @@
       </c>
       <c r="Q187" t="inlineStr"/>
       <c r="R187" t="n">
-        <v>18.3</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="E188" t="n">
-        <v>18.2</v>
+        <v>22.7</v>
       </c>
       <c r="F188" t="n">
-        <v>9.1</v>
+        <v>20.7</v>
       </c>
       <c r="G188" t="n">
-        <v>9.300000000000001</v>
+        <v>22</v>
       </c>
       <c r="H188" t="n">
-        <v>4.9</v>
+        <v>29.1</v>
       </c>
       <c r="I188" t="n">
-        <v>6.6</v>
+        <v>41.5</v>
       </c>
       <c r="J188" t="n">
-        <v>8.800000000000001</v>
+        <v>21.3</v>
       </c>
       <c r="K188" t="n">
-        <v>5.2</v>
+        <v>28.4</v>
       </c>
       <c r="L188" t="n">
-        <v>6.1</v>
+        <v>39.4</v>
       </c>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="n">
-        <v>8.199999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="O188" t="n">
-        <v>7.9</v>
+        <v>16.3</v>
       </c>
       <c r="P188" t="n">
-        <v>5.3</v>
+        <v>15.5</v>
       </c>
       <c r="Q188" t="inlineStr"/>
       <c r="R188" t="n">
-        <v>11.7</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="C189" t="n">
-        <v>0</v>
+        <v>17.1</v>
       </c>
       <c r="D189" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="E189" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="F189" t="n">
-        <v>22.4</v>
+        <v>9.1</v>
       </c>
       <c r="G189" t="n">
-        <v>23.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H189" t="n">
-        <v>30.3</v>
+        <v>4.9</v>
       </c>
       <c r="I189" t="n">
-        <v>40.3</v>
+        <v>6.6</v>
       </c>
       <c r="J189" t="n">
-        <v>21.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K189" t="n">
-        <v>28.4</v>
+        <v>5.2</v>
       </c>
       <c r="L189" t="n">
-        <v>39.4</v>
+        <v>6.1</v>
       </c>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="n">
-        <v>11.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O189" t="n">
-        <v>16.3</v>
+        <v>7.9</v>
       </c>
       <c r="P189" t="n">
-        <v>15.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q189" t="inlineStr"/>
       <c r="R189" t="n">
-        <v>10.3</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="190">
@@ -6509,19 +6509,19 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>481</v>
+        <v>528</v>
       </c>
       <c r="C249" t="n">
-        <v>613</v>
+        <v>653</v>
       </c>
       <c r="D249" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E249" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F249" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G249" t="n">
         <v>20</v>
@@ -6552,7 +6552,7 @@
       <c r="S249" t="inlineStr"/>
       <c r="T249" t="inlineStr"/>
       <c r="U249" t="n">
-        <v>1562</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="250">
@@ -6621,16 +6621,16 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>524</v>
+        <v>369</v>
       </c>
       <c r="C251" t="n">
-        <v>440</v>
+        <v>317</v>
       </c>
       <c r="D251" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="E251" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F251" t="n">
         <v>13</v>
@@ -6639,10 +6639,10 @@
         <v>13</v>
       </c>
       <c r="H251" t="n">
+        <v>1</v>
+      </c>
+      <c r="I251" t="n">
         <v>2</v>
-      </c>
-      <c r="I251" t="n">
-        <v>1</v>
       </c>
       <c r="J251" t="n">
         <v>2</v>
@@ -6662,115 +6662,115 @@
       <c r="S251" t="inlineStr"/>
       <c r="T251" t="inlineStr"/>
       <c r="U251" t="n">
-        <v>1164</v>
+        <v>865</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B252" t="n">
+        <v>289</v>
+      </c>
+      <c r="C252" t="n">
         <v>301</v>
       </c>
-      <c r="C252" t="n">
-        <v>263</v>
-      </c>
       <c r="D252" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="E252" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F252" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G252" t="n">
+        <v>17</v>
+      </c>
+      <c r="H252" t="n">
         <v>13</v>
-      </c>
-      <c r="H252" t="n">
-        <v>5</v>
       </c>
       <c r="I252" t="n">
         <v>7</v>
       </c>
       <c r="J252" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K252" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L252" t="n">
         <v>1</v>
       </c>
-      <c r="M252" t="inlineStr"/>
+      <c r="M252" t="n">
+        <v>2</v>
+      </c>
       <c r="N252" t="inlineStr"/>
-      <c r="O252" t="inlineStr"/>
+      <c r="O252" t="n">
+        <v>2</v>
+      </c>
       <c r="P252" t="inlineStr"/>
       <c r="Q252" t="inlineStr"/>
-      <c r="R252" t="inlineStr"/>
+      <c r="R252" t="n">
+        <v>1</v>
+      </c>
       <c r="S252" t="inlineStr"/>
       <c r="T252" t="inlineStr"/>
       <c r="U252" t="n">
-        <v>744</v>
+        <v>854</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>181</v>
+        <v>301</v>
       </c>
       <c r="C253" t="n">
-        <v>218</v>
+        <v>263</v>
       </c>
       <c r="D253" t="n">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="E253" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F253" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G253" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H253" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I253" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J253" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K253" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L253" t="n">
         <v>1</v>
       </c>
-      <c r="M253" t="n">
-        <v>2</v>
-      </c>
+      <c r="M253" t="inlineStr"/>
       <c r="N253" t="inlineStr"/>
-      <c r="O253" t="n">
-        <v>2</v>
-      </c>
+      <c r="O253" t="inlineStr"/>
       <c r="P253" t="inlineStr"/>
       <c r="Q253" t="inlineStr"/>
-      <c r="R253" t="n">
-        <v>1</v>
-      </c>
+      <c r="R253" t="inlineStr"/>
       <c r="S253" t="inlineStr"/>
       <c r="T253" t="inlineStr"/>
       <c r="U253" t="n">
-        <v>653</v>
+        <v>744</v>
       </c>
     </row>
     <row r="254">
@@ -7074,19 +7074,19 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>24.2</v>
+        <v>26.5</v>
       </c>
       <c r="C261" t="n">
-        <v>28.8</v>
+        <v>30.7</v>
       </c>
       <c r="D261" t="n">
-        <v>27.6</v>
+        <v>28.1</v>
       </c>
       <c r="E261" t="n">
-        <v>18.8</v>
+        <v>19.7</v>
       </c>
       <c r="F261" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="G261" t="n">
         <v>10.7</v>
@@ -7117,7 +7117,7 @@
       <c r="S261" t="inlineStr"/>
       <c r="T261" t="inlineStr"/>
       <c r="U261" t="n">
-        <v>24.6</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="262">
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>26.3</v>
+        <v>18.5</v>
       </c>
       <c r="C263" t="n">
-        <v>20.7</v>
+        <v>14.9</v>
       </c>
       <c r="D263" t="n">
-        <v>11.9</v>
+        <v>10.5</v>
       </c>
       <c r="E263" t="n">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="F263" t="n">
         <v>4.8</v>
@@ -7204,10 +7204,10 @@
         <v>7</v>
       </c>
       <c r="H263" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="I263" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J263" t="n">
         <v>5.4</v>
@@ -7227,115 +7227,115 @@
       <c r="S263" t="inlineStr"/>
       <c r="T263" t="inlineStr"/>
       <c r="U263" t="n">
-        <v>18.3</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>Returned to homelessness</t>
+          <t>Internal move: backwards</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>15.1</v>
+        <v>14.5</v>
       </c>
       <c r="C264" t="n">
-        <v>12.4</v>
+        <v>14.1</v>
       </c>
       <c r="D264" t="n">
-        <v>8.4</v>
+        <v>12.3</v>
       </c>
       <c r="E264" t="n">
-        <v>8.699999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="F264" t="n">
-        <v>5.9</v>
+        <v>8.9</v>
       </c>
       <c r="G264" t="n">
-        <v>7</v>
+        <v>9.1</v>
       </c>
       <c r="H264" t="n">
-        <v>5.7</v>
+        <v>14.8</v>
       </c>
       <c r="I264" t="n">
         <v>13.5</v>
       </c>
       <c r="J264" t="n">
-        <v>13.5</v>
+        <v>21.6</v>
       </c>
       <c r="K264" t="n">
-        <v>7.7</v>
+        <v>23.1</v>
       </c>
       <c r="L264" t="n">
         <v>12.5</v>
       </c>
-      <c r="M264" t="inlineStr"/>
+      <c r="M264" t="n">
+        <v>28.6</v>
+      </c>
       <c r="N264" t="inlineStr"/>
-      <c r="O264" t="inlineStr"/>
+      <c r="O264" t="n">
+        <v>66.7</v>
+      </c>
       <c r="P264" t="inlineStr"/>
       <c r="Q264" t="inlineStr"/>
-      <c r="R264" t="inlineStr"/>
+      <c r="R264" t="n">
+        <v>100</v>
+      </c>
       <c r="S264" t="inlineStr"/>
       <c r="T264" t="inlineStr"/>
       <c r="U264" t="n">
-        <v>11.7</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>Internal move: backwards</t>
+          <t>Returned to homelessness</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>9.1</v>
+        <v>15.1</v>
       </c>
       <c r="C265" t="n">
-        <v>10.2</v>
+        <v>12.4</v>
       </c>
       <c r="D265" t="n">
-        <v>11.4</v>
+        <v>8.4</v>
       </c>
       <c r="E265" t="n">
-        <v>10.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F265" t="n">
-        <v>9.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="G265" t="n">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="H265" t="n">
-        <v>13.6</v>
+        <v>5.7</v>
       </c>
       <c r="I265" t="n">
-        <v>15.4</v>
+        <v>13.5</v>
       </c>
       <c r="J265" t="n">
-        <v>21.6</v>
+        <v>13.5</v>
       </c>
       <c r="K265" t="n">
-        <v>23.1</v>
+        <v>7.7</v>
       </c>
       <c r="L265" t="n">
         <v>12.5</v>
       </c>
-      <c r="M265" t="n">
-        <v>28.6</v>
-      </c>
+      <c r="M265" t="inlineStr"/>
       <c r="N265" t="inlineStr"/>
-      <c r="O265" t="n">
-        <v>66.7</v>
-      </c>
+      <c r="O265" t="inlineStr"/>
       <c r="P265" t="inlineStr"/>
       <c r="Q265" t="inlineStr"/>
-      <c r="R265" t="n">
-        <v>100</v>
-      </c>
+      <c r="R265" t="inlineStr"/>
       <c r="S265" t="inlineStr"/>
       <c r="T265" t="inlineStr"/>
       <c r="U265" t="n">
-        <v>10.3</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="266">
@@ -7933,19 +7933,19 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>297</v>
+        <v>354</v>
       </c>
       <c r="E277" t="n">
-        <v>357</v>
+        <v>403</v>
       </c>
       <c r="F277" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="G277" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H277" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I277" t="n">
         <v>12</v>
@@ -7990,7 +7990,7 @@
         <v>0</v>
       </c>
       <c r="W277" t="n">
-        <v>924</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="278">
@@ -8002,19 +8002,19 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>312</v>
+        <v>255</v>
       </c>
       <c r="E278" t="n">
-        <v>258</v>
+        <v>212</v>
       </c>
       <c r="F278" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G278" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H278" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I278" t="n">
         <v>7</v>
@@ -8059,7 +8059,7 @@
         <v>0</v>
       </c>
       <c r="W278" t="n">
-        <v>705</v>
+        <v>588</v>
       </c>
     </row>
     <row r="279">
@@ -8420,19 +8420,19 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E284" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F284" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G284" t="n">
         <v>10</v>
       </c>
       <c r="H284" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I284" t="n">
         <v>2</v>
@@ -8441,7 +8441,7 @@
         <v>2</v>
       </c>
       <c r="K284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L284" t="n">
         <v>2</v>
@@ -8477,7 +8477,7 @@
         <v>0</v>
       </c>
       <c r="W284" t="n">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="285">
@@ -8489,7 +8489,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E285" t="n">
         <v>124</v>
@@ -8546,7 +8546,7 @@
         <v>0</v>
       </c>
       <c r="W285" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="286">
@@ -8558,19 +8558,19 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E286" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F286" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G286" t="n">
         <v>1</v>
       </c>
       <c r="H286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I286" t="n">
         <v>1</v>
@@ -8579,7 +8579,7 @@
         <v>0</v>
       </c>
       <c r="K286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L286" t="n">
         <v>0</v>
@@ -8615,7 +8615,7 @@
         <v>0</v>
       </c>
       <c r="W286" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="287">
@@ -10090,16 +10090,16 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="E308" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F308" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G308" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -10108,7 +10108,7 @@
         <v>0</v>
       </c>
       <c r="J308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K308" t="n">
         <v>0</v>
@@ -10146,7 +10146,9 @@
       <c r="V308" t="n">
         <v>0</v>
       </c>
-      <c r="W308" t="inlineStr"/>
+      <c r="W308" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n"/>
@@ -10157,13 +10159,13 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E309" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F309" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G309" t="n">
         <v>5</v>
@@ -10214,7 +10216,7 @@
         <v>0</v>
       </c>
       <c r="W309" t="n">
-        <v>212</v>
+        <v>193</v>
       </c>
     </row>
     <row r="310">
@@ -10226,16 +10228,16 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>166</v>
+        <v>68</v>
       </c>
       <c r="E310" t="n">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="F310" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -10244,7 +10246,7 @@
         <v>2</v>
       </c>
       <c r="J310" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -10283,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="W310" t="n">
-        <v>342</v>
+        <v>151</v>
       </c>
     </row>
     <row r="311">
@@ -10644,10 +10646,10 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E316" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F316" t="n">
         <v>16</v>
@@ -10701,7 +10703,7 @@
         <v>0</v>
       </c>
       <c r="W316" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="317">
@@ -10716,7 +10718,7 @@
         <v>1</v>
       </c>
       <c r="E317" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F317" t="n">
         <v>7</v>
@@ -10770,7 +10772,7 @@
         <v>0</v>
       </c>
       <c r="W317" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="318">
@@ -10782,11 +10784,11 @@
         </is>
       </c>
       <c r="D318" t="n">
+        <v>0</v>
+      </c>
+      <c r="E318" t="n">
         <v>1</v>
       </c>
-      <c r="E318" t="n">
-        <v>3</v>
-      </c>
       <c r="F318" t="n">
         <v>0</v>
       </c>
@@ -10839,7 +10841,7 @@
         <v>0</v>
       </c>
       <c r="W318" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -11426,19 +11428,19 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>14.9</v>
+        <v>17.8</v>
       </c>
       <c r="E329" t="n">
-        <v>16.8</v>
+        <v>18.9</v>
       </c>
       <c r="F329" t="n">
-        <v>17.3</v>
+        <v>18.1</v>
       </c>
       <c r="G329" t="n">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="H329" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="I329" t="n">
         <v>6.4</v>
@@ -11483,7 +11485,7 @@
         <v>0</v>
       </c>
       <c r="W329" t="n">
-        <v>14.5</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="330">
@@ -11495,19 +11497,19 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>15.7</v>
+        <v>12.8</v>
       </c>
       <c r="E330" t="n">
-        <v>12.1</v>
+        <v>10</v>
       </c>
       <c r="F330" t="n">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
       <c r="G330" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="H330" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="I330" t="n">
         <v>3.7</v>
@@ -11552,7 +11554,7 @@
         <v>0</v>
       </c>
       <c r="W330" t="n">
-        <v>11.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="331">
@@ -11913,19 +11915,19 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="E336" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="F336" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G336" t="n">
         <v>1.8</v>
       </c>
       <c r="H336" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="I336" t="n">
         <v>1.1</v>
@@ -11934,7 +11936,7 @@
         <v>2.3</v>
       </c>
       <c r="K336" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="L336" t="n">
         <v>5.4</v>
@@ -11970,7 +11972,7 @@
         <v>0</v>
       </c>
       <c r="W336" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="337">
@@ -11982,7 +11984,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="E337" t="n">
         <v>5.8</v>
@@ -12039,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="W337" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="338">
@@ -12054,16 +12056,16 @@
         <v>1.8</v>
       </c>
       <c r="E338" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="F338" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G338" t="n">
         <v>0.2</v>
       </c>
       <c r="H338" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I338" t="n">
         <v>0.5</v>
@@ -12072,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="K338" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="L338" t="n">
         <v>0</v>
@@ -12108,7 +12110,7 @@
         <v>0</v>
       </c>
       <c r="W338" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="339">
@@ -13583,16 +13585,16 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="E360" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F360" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="G360" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -13601,7 +13603,7 @@
         <v>0</v>
       </c>
       <c r="J360" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="K360" t="n">
         <v>0</v>
@@ -13639,7 +13641,9 @@
       <c r="V360" t="n">
         <v>0</v>
       </c>
-      <c r="W360" t="inlineStr"/>
+      <c r="W360" t="n">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n"/>
@@ -13650,13 +13654,13 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="E361" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="F361" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G361" t="n">
         <v>0.9</v>
@@ -13707,7 +13711,7 @@
         <v>0</v>
       </c>
       <c r="W361" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="362">
@@ -13719,16 +13723,16 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>8.300000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="E362" t="n">
-        <v>6.6</v>
+        <v>2.9</v>
       </c>
       <c r="F362" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="G362" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -13737,7 +13741,7 @@
         <v>1.1</v>
       </c>
       <c r="J362" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="K362" t="n">
         <v>0</v>
@@ -13776,7 +13780,7 @@
         <v>0</v>
       </c>
       <c r="W362" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="363">
@@ -14137,10 +14141,10 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="E368" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="F368" t="n">
         <v>1.6</v>
@@ -14194,7 +14198,7 @@
         <v>0</v>
       </c>
       <c r="W368" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="369">
@@ -14209,7 +14213,7 @@
         <v>0.1</v>
       </c>
       <c r="E369" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F369" t="n">
         <v>0.7</v>
@@ -14275,10 +14279,10 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E370" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F370" t="n">
         <v>0</v>
@@ -14332,7 +14336,7 @@
         <v>0</v>
       </c>
       <c r="W370" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371">
@@ -14550,7 +14554,6 @@
     <mergeCell ref="F140:I140"/>
     <mergeCell ref="A57:A59"/>
     <mergeCell ref="B281:B288"/>
-    <mergeCell ref="C51:C53"/>
     <mergeCell ref="C57:C59"/>
     <mergeCell ref="E220:G220"/>
     <mergeCell ref="B64:E64"/>
@@ -14566,7 +14569,6 @@
     <mergeCell ref="B154:E154"/>
     <mergeCell ref="B273:B280"/>
     <mergeCell ref="F64:I64"/>
-    <mergeCell ref="B51:B53"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B365:B372"/>
     <mergeCell ref="B341:B348"/>
@@ -14576,19 +14578,21 @@
     <mergeCell ref="A357:A372"/>
     <mergeCell ref="B47:B49"/>
     <mergeCell ref="C42:C44"/>
+    <mergeCell ref="B50:B52"/>
     <mergeCell ref="A325:A356"/>
     <mergeCell ref="F168:I168"/>
     <mergeCell ref="C54:C56"/>
     <mergeCell ref="B140:E140"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="A3:A8"/>
-    <mergeCell ref="A51:A53"/>
     <mergeCell ref="B333:B340"/>
     <mergeCell ref="B289:B296"/>
     <mergeCell ref="B349:B356"/>
     <mergeCell ref="A54:A56"/>
+    <mergeCell ref="A50:A52"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="A273:A304"/>
+    <mergeCell ref="C50:C52"/>
     <mergeCell ref="B45:B46"/>
     <mergeCell ref="J182:M182"/>
     <mergeCell ref="F154:I154"/>

--- a/assets_output/04_bivariate_analysis_placements.xlsx
+++ b/assets_output/04_bivariate_analysis_placements.xlsx
@@ -5765,7 +5765,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Table 4.16: Placement outcomes from level 3-4 by shared vs. self-contained</t>
+          <t>Table 4.16: Placement outcomes from level 3-4 by shared vs. self-contained and age categories</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Table 4.17: Placement outcomes (as column percentages) from level 3-4 by shared vs. self-contained</t>
+          <t>Table 4.17: Placement outcomes (as column percentages) from level 3-4 by shared vs. self-contained and age categories</t>
         </is>
       </c>
     </row>
